--- a/docs/working_documents/Research_Overview.xlsx
+++ b/docs/working_documents/Research_Overview.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/janlinzner/Projects/Master-Thesis-Spatial-Proximity-Venture-Capital/docs/working_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E8D661E-45E6-9249-9338-A2E40A3A83E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DECA84-FB94-A046-A54A-219CA9075CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{AB2802A1-B2D6-D448-8853-2C20DC0DE37E}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{AB2802A1-B2D6-D448-8853-2C20DC0DE37E}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximity" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="637">
   <si>
     <t>Abstract</t>
   </si>
@@ -68,22 +68,6 @@
   </si>
   <si>
     <t>Relevance</t>
-  </si>
-  <si>
-    <t>Research on Schumpeterian entrepreneurship identi es new high-growth startup companies as key factors in
-technological innovation and economic growth. While economists have tended to focus on high-growth, high-
-tech startup rms as the unit of analysis, economic geographers and urbanists have examined the geographic
-dimensions of entrepreneurship, particularly the rise of entrepreneurial clusters and eco systems. We focus here
-on a particular type of Schumpeterian entrepreneurship associated with high-tech startup companies, or what we
-refer to as“tech-startup entrepreneurship.” We contend that the organization of such Schumpeterian en-
-trepreneurship occurs at two spatial scales. At the macro-geographic level, it is highly clustered and concentrated
-in a relatively small number of global cities or metro areas. At the micro-geographic level, it is highly con-
-centrated in distinct districts or micro-clusters within these leading cities and metro areas. To examine the
-geographic dimensions of tech-startup entrepreneurship across these spatial scales, we use previously unused
-data on venture capital- nanced startups at the metropolitan and district levels. Our ndings support the hypothesis that tech-startup entrepreneurship is organized across two distinct but related spatial scales, which act
-on entrepreneurial activity through di erent mechanisms. These ndings suggest that local diversity and local
-specialization can simultaneously potentiate innovation, and that a multi-scalar approach to the geography of
-entrepreneurship is prudent.</t>
   </si>
   <si>
     <t>The city and high-tech startups: The spatial organization of Schumpeterian
@@ -107,9 +91,6 @@
   <si>
     <t>Proximity relations and the fate of VC‑backed startups:
 Evidence from a global 33‑year‑long dataset</t>
-  </si>
-  <si>
-    <t>Nicolas Bédu, Olivier Brossard, Matthieu Montalban3</t>
   </si>
   <si>
     <t>Journal of Evolutionary Economics</t>
@@ -408,21 +389,6 @@
   <si>
     <t>Ruiqi Li, Lingyun Lu, Weiwei Gu, Shaodong Ma, Gang Xu,  H. Eugene
 Stanley</t>
-  </si>
-  <si>
-    <t>Cities are centers for the integration of capital and incubators of invention, and attracting venture capital (VC) is of great
-importance for cities to advance in innovative technology and business models towards a sustainable and prosperous future.
-Yet we still lack a quantitative understanding of the relationship between urban characteristics and VC activities. In this paper,
-we find a clear nonlinear scaling relationship between VC activities and the urban population of Chinese cities. In such nonlinear
-systems, the widely applied linear per capita indicators would be either biased to larger cities or smaller cities depends on
-whether it is superlinear or sublinear, while the residual of cities relative to the prediction of scaling law is a more objective and
-scale-invariant metric. Such a metric can distinguish the effects of local dynamics and scaled growth induced by the change of
-population size. The spatiotemporal evolution of such metrics on VC activities reveals three distinct groups of cities, two of
-which stand out with increasing and decreasing trends, respectively. And the taxonomy results together with spatial analysis
-also signify different development modes between large urban agglomeration regions. Besides, we notice the evolution of
-scaling exponents on VC activities are of much larger fluctuations than on socioeconomic output of cities, and a conceptual
-model that focuses on the growth dynamics of different sized cities can well explain it, which we assume would be general to
-other scenarios.</t>
   </si>
   <si>
     <t>José Martí, Gerardo Trucci</t>
@@ -2641,9 +2607,6 @@
     <t>Stuart, Sorensen</t>
   </si>
   <si>
-    <t>AdministrativeScience Quarterly</t>
-  </si>
-  <si>
     <t>In this paper, we examine the ecological consequences of initial public offerings (IPOs) and acquisitions, specifically how the spatial distribution of these events influences the location-specific founding rates of new companies. We explore whether relatively small spatial units (metropolitan statistical areas) in close geographic proximity to firms that recently have been acquired or experienced an IPO exhibit high new venture creation rates and whether the magnitudes of these effects depend on regional differences in statutes governing the freedom of employees to move between employers. Count models of biotechnology firm foundings establish three findings: (1) IPOs of organizations located contiguous to or within an MSA accelerate the founding rate within that MSA, (2) acquisitions of biotech firms situated near to or within an MSA accelerate the founding rate within the MSA, but only when the acquirer enters from outside of the biotech industry, and (3) the enforceability of post-employment non-compete covenants, which is determined at the state level, strongly moderates these effects.</t>
   </si>
   <si>
@@ -2780,6 +2743,144 @@
   </si>
   <si>
     <t>This paper investigates how the interorganizational networks of young companies affect their ability to acquire the resources necessary for survival and growth. We propose that, faced with great uncertainty about the quality of young companies, third parties rely on the prominence of the affiliates of those companies to make judgments about their quality and that young companies “endorsed” by prominent exchange partners will perform better than otherwise comparable ventures that lack prominent associates. Results of an empirical examination of the rate of initial public offering (IPO) and the market capitalization at IPO of the members of a large sample of venture-capital-backed biotechnology firms show that privately held biotech firms with prominent strategic alliance partners and organizational equity investors go to IPO faster and earn greater valuations at IPO than firms that lack such connections. We also empirically demonstrate that much of the benefit of having prominent affiliates stems from the transfer of status that is an inherent byproduct of interorganizational associations.</t>
+  </si>
+  <si>
+    <t>Administrative Science Quarterly</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Journal Importance</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>Conference</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>What do we know about geographical knowledge
+spillovers and regional growth?: A survey of the
+literature</t>
+  </si>
+  <si>
+    <t>Thomas Döring &amp; Jan Schnellenbach</t>
+  </si>
+  <si>
+    <t>Modern (endogenous) growth theory tells us that knowledge is crucial for the sustained growth of high-income economies. Against this background, the paper provides a survey of theoretical and empirical findings highlighting the question of how geographically limited knowledge diffusion can help to explain clusters of regions with persistently different levels of growth. It discusses this topic in two steps. First, the theoretical concept of knowledge spillovers is outlined by discussing the different types of knowledge, the spatial dimension of knowledge spillovers, and the geographical mechanisms and structural conditions of knowledge diffusion. Second, it analyses the empirical evidence concerning the theoretical
+propositions.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/17x_nMA2J5LUSq7FZ0ANnQZf1Q2ipar0A/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>Knowledge-Based Regional Economic Development: A Synthetic Review of
+Knowledge Spillovers, Entrepreneurship,
+and Entrepreneurial Ecosystems</t>
+  </si>
+  <si>
+    <t>Haifeng Qian</t>
+  </si>
+  <si>
+    <t>The geographical nature of knowledge spillovers and entrepreneurship has been well documented in the literature. In most regional or urban studies, these two topics are separately discussed. This research reviews literature at the intersection of
+knowledge spillovers, entrepreneurship, and regional economic development. The key argument is that entrepreneurship
+can serve as a mechanism for transmitting knowledge spillovers and accordingly contribute to regional innovation, cluster
+formation, and economic development. However, the effectiveness of this mechanism depends on various factors in the regional entrepreneurial ecosystem, notably including knowledge bases, absorptive capacity, competition, networks of
+people, diversity, and culture.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/17IHyP6y3CS8l1LioopKNeje5ESMqHti7/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>International Venture Capital Research: From cross-country comparisons to crossing borders</t>
+  </si>
+  <si>
+    <t>Mike Wright, Sarika Pruthi and Andy Lockett</t>
+  </si>
+  <si>
+    <t>International Journal of Management Reviews</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hp3rje-VaHwIkS-mDlzQjLxM_PUoUmfE/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Venture capital (VC) has become an international phenomenon, and VC firms are a specific kind of service firm whose characteristics have distinctive implications for international
+behaviour. There is now a disparate body of research on international aspects of VC across a number of disciplines comprising finance, economics, strategy, entrepreneurship, inter-
+national business and economic geography. A novel aspect of this paper is that we review and synthesize this disparate literature. A number of research gaps and limitations in the theoretical and methodological approaches involved in previous studies are identified and suggestions made for further research. We show that the vast majority of the literature relates to cross-country comparisons; that is, macro-level comparisons of VC industries across different countries and micro-level comparisons of VC behaviour across countries. From our review of the literature, we argue that an under-researched area concerns the influence of institutional contexts, especially the role of social networks and cultures. Furthermore, our review of the literature indicates that there is a major research gap in relation to work dealing with the crossing of country borders by VC firms. We suggest that resource-based, capabilities, institutional and network theories may be offer insights to further our understanding of the behaviour of VC firms in this area.</t>
+  </si>
+  <si>
+    <t>The geography of venture capital
+investments in the UK</t>
+  </si>
+  <si>
+    <t>Colin M Mason,  Richard T Harrison</t>
+  </si>
+  <si>
+    <t>Transactions of the Institute of British Geographers</t>
+  </si>
+  <si>
+    <t>The role of venture capital in economic development increasingly is recognized as central to the development of an entrepreneurial economy. However, the supply of venture capital is not distributed evenly across the space economy. In the UK, evidence for the 1980s demonstrated that venture capital investments were highly concentrated in Greater London and the South East, reinforcing the existing patterns of regional concentration of economic activity. This paper reviews the regional distribution of venture capital investments in the UK in the 1990s, a period of massive growth in venture capital investment activity. It concludes that the regional concentration of venture capital investment has been considerably reduced since the 1980s. However, more detailed analysis of the data demonstrates that this shift towards a less unequal regional distribution has been driven by so-called ‘merchant’ venture capital – investments in large-scale management buy-outs and buy-ins which facilitate corporate restructuring through ownership change and often have adverse consequences for employment. ‘Classic’ venture capital – investments in young entrepreneurial companies with high growth potential – remains highly concentrated in London and the South East, and also in Scotland. This reflects both supply- and demand-side factors. The Government’s new regional venture capital funds are unlikely to be effective in closing this regional finance gap. An alternative approach to intervention, in the context of the increasing globalization of venture capital investments, is to seek to attract venture capital money and expertise from
+elsewhere.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1PMPvz2UbWuGgkkHKUgGTrVFPF9ShBREI/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>Proximity and inter-organizational collaboration: A literature Review</t>
+  </si>
+  <si>
+    <t>J. Knoben and L.A.G. Oerlemans</t>
+  </si>
+  <si>
+    <t>The proximity concept is used in many different ways in the literature. These dimensions of proximity are, however, defined and measured in many different (sometimes even contradictory) ways, show large amounts of overlap, and often are under- or overspecified. The goal of this paper is to specify the different dimensions of proximity relevant in inter-organizational collaboration more precisely and to provide definitions of these dimensions. The research presented contributes to reducing the ambiguity of the proximity concept as used in the literature.
+Based on the above, the following research question is addressed in this paper: ‘Which dimensions of proximity are relevant in inter-organizational collaboration and how are they defined?’ A systematic literature review is presented in order to disentangle the dimensions of the proximity concept. Based on this literature review, three dimensions of proximity relevant in inter-organizational collaboration are distinguished: geographical proximity, organizational proximity and technological proximity. Examples (case studies) from the literature are used to illustrate the current conceptual ambiguity as well as to clarify how
+the proposed dimensions of proximity reduce this conceptual ambiguity.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1GCDnZo02iAlIpNf0Xwf2bXUjmGW7M1UU/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>Nicolas Bédu, Olivier Brossard, Matthieu Montalban</t>
+  </si>
+  <si>
+    <t>Cities are centers for the integration of capital and incubators of invention, and attracting venture capital (VC) is of great
+importance for cities to advance in innovative technology and business models towards a sustainable and prosperous future.
+Yet we still lack a quantitative understanding of the relationship between urban characteristics and VC activities. In this paper,
+we find a clear nonlinear scaling relationship between VC activities and the urban population of Chinese cities. In such nonlinear
+systems, the widely applied linear per capita indicators would be either biased to larger cities or smaller cities depends on
+whether it is superlinear or sublinear, while the residual of cities relative to the prediction of scaling law is a more objective and
+scale-invariant metric. Such a metric can distinguish the effects of local dynamics and scaled growth induced by the change of
+population size. The spatiotemporal evolution of such metrics on VC activities reveals three distinct groups of cities, two of
+which stand out with increasing and decreasing trends, respectively. And the taxonomy results together with spatial analysis also signify different development modes between large urban agglomeration regions. Besides, we notice the evolution of
+scaling exponents on VC activities are of much larger fluctuations than on socioeconomic output of cities, and a conceptual
+model that focuses on the growth dynamics of different sized cities can well explain it, which we assume would be general to
+other scenarios.</t>
+  </si>
+  <si>
+    <t>Research on Schumpeterian entrepreneurship identifies new high-growth startup companies as key factors in
+technological innovation and economic growth. While economists have tended to focus on high-growth, high-
+tech startup rms as the unit of analysis, economic geographers and urbanists have examined the geographic
+dimensions of entrepreneurship, particularly the rise of entrepreneurial clusters and eco systems. We focus here
+on a particular type of Schumpeterian entrepreneurship associated with high-tech startup companies, or what we
+refer to as“tech-startup entrepreneurship.” We contend that the organization of such Schumpeterian en-
+trepreneurship occurs at two spatial scales. At the macro-geographic level, it is highly clustered and concentrated
+in a relatively small number of global cities or metro areas. At the micro-geographic level, it is highly con-
+centrated in distinct districts or micro-clusters within these leading cities and metro areas. To examine the
+geographic dimensions of tech-startup entrepreneurship across these spatial scales, we use previously unused
+data on venture capital- nanced startups at the metropolitan and district levels. Our ndings support the hypothesis that tech-startup entrepreneurship is organized across two distinct but related spatial scales, which act
+on entrepreneurial activity through di erent mechanisms. These ndings suggest that local diversity and local
+specialization can simultaneously potentiate innovation, and that a multi-scalar approach to the geography of
+entrepreneurship is prudent.</t>
   </si>
 </sst>
 </file>
@@ -2967,7 +3068,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3014,6 +3115,7 @@
     <xf numFmtId="9" fontId="0" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3029,15 +3131,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="65">
+  <dxfs count="70">
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -3201,6 +3313,9 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -3296,89 +3411,99 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{05A3DE70-8607-154D-94FC-886F5C5AE18F}" name="Proximity" displayName="Proximity" ref="A1:O32" totalsRowShown="0" dataDxfId="64">
-  <autoFilter ref="A1:O32" xr:uid="{05A3DE70-8607-154D-94FC-886F5C5AE18F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O31">
-    <sortCondition descending="1" ref="M1:M31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{05A3DE70-8607-154D-94FC-886F5C5AE18F}" name="Proximity" displayName="Proximity" ref="A1:P40" totalsRowShown="0" dataDxfId="69">
+  <autoFilter ref="A1:P40" xr:uid="{05A3DE70-8607-154D-94FC-886F5C5AE18F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P32">
+    <sortCondition descending="1" ref="C1:C32"/>
   </sortState>
-  <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{BE890421-FAE4-E542-9F1E-B981E196844C}" name="Paper Title" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{3EF9D581-8149-E04D-AAD0-820AB0D43B5E}" name="Authors" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{EA555D34-595C-9C43-8F97-76F1AE4A5266}" name="Year" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{D4A09DA9-9282-DF4A-ADAD-4C45732EE81B}" name="Journal Title" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{955A51EE-9B22-7B4C-BFB1-133ED1B97F29}" name="Abstract" dataDxfId="59"/>
-    <tableColumn id="12" xr3:uid="{5E3EF9B7-8FE7-1649-A6CF-F53A05750B5E}" name="DOI" dataDxfId="58"/>
-    <tableColumn id="6" xr3:uid="{70C24B6A-7FF1-5F49-B979-154258527049}" name="Research / Theory" dataDxfId="57"/>
-    <tableColumn id="10" xr3:uid="{8972665B-B720-5245-945A-E21765E20CAE}" name="Method" dataDxfId="56"/>
-    <tableColumn id="7" xr3:uid="{8AB08798-7826-5D4E-9E24-62A965A7EA52}" name="Outcome / Findings" dataDxfId="55"/>
-    <tableColumn id="13" xr3:uid="{20CDEE81-3EE9-444B-B350-BC58373FB9E6}" name="Effect" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{C197D97F-FCE4-1149-84DD-B03DA8E6B9D8}" name="Future Research" dataDxfId="53"/>
-    <tableColumn id="11" xr3:uid="{427420AC-26C0-AC44-AFC0-0B1DE7D423A6}" name="Variables" dataDxfId="52"/>
-    <tableColumn id="9" xr3:uid="{69462FAC-59D4-A243-B7A2-3A11E78ED3B1}" name="Relevance" dataDxfId="51"/>
-    <tableColumn id="14" xr3:uid="{643E54C9-B4A1-E745-B221-7C9BCB30FFB9}" name="Link" dataDxfId="50"/>
-    <tableColumn id="15" xr3:uid="{19A2B419-6ED7-A44F-9C0C-D2EF0458EF6B}" name="Reviewed?" dataDxfId="15"/>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{BE890421-FAE4-E542-9F1E-B981E196844C}" name="Paper Title" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{3EF9D581-8149-E04D-AAD0-820AB0D43B5E}" name="Authors" dataDxfId="67"/>
+    <tableColumn id="3" xr3:uid="{EA555D34-595C-9C43-8F97-76F1AE4A5266}" name="Year" dataDxfId="66"/>
+    <tableColumn id="4" xr3:uid="{D4A09DA9-9282-DF4A-ADAD-4C45732EE81B}" name="Journal Title" dataDxfId="65"/>
+    <tableColumn id="16" xr3:uid="{6E2C10AD-AB73-E24A-898B-73DDF557CB16}" name="Journal Importance" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{955A51EE-9B22-7B4C-BFB1-133ED1B97F29}" name="Abstract" dataDxfId="64"/>
+    <tableColumn id="12" xr3:uid="{5E3EF9B7-8FE7-1649-A6CF-F53A05750B5E}" name="DOI" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{70C24B6A-7FF1-5F49-B979-154258527049}" name="Research / Theory" dataDxfId="62"/>
+    <tableColumn id="10" xr3:uid="{8972665B-B720-5245-945A-E21765E20CAE}" name="Method" dataDxfId="61"/>
+    <tableColumn id="7" xr3:uid="{8AB08798-7826-5D4E-9E24-62A965A7EA52}" name="Outcome / Findings" dataDxfId="60"/>
+    <tableColumn id="13" xr3:uid="{20CDEE81-3EE9-444B-B350-BC58373FB9E6}" name="Effect" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{C197D97F-FCE4-1149-84DD-B03DA8E6B9D8}" name="Future Research" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{427420AC-26C0-AC44-AFC0-0B1DE7D423A6}" name="Variables" dataDxfId="57"/>
+    <tableColumn id="9" xr3:uid="{69462FAC-59D4-A243-B7A2-3A11E78ED3B1}" name="Relevance" dataDxfId="56"/>
+    <tableColumn id="14" xr3:uid="{643E54C9-B4A1-E745-B221-7C9BCB30FFB9}" name="Link" dataDxfId="55"/>
+    <tableColumn id="15" xr3:uid="{19A2B419-6ED7-A44F-9C0C-D2EF0458EF6B}" name="Reviewed?" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D20DD51-13C3-5845-AB11-DD7C452F876E}" name="Success" displayName="Success" ref="A1:K28" totalsRowShown="0" headerRowDxfId="49" dataDxfId="48">
-  <autoFilter ref="A1:K28" xr:uid="{4D20DD51-13C3-5845-AB11-DD7C452F876E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K28">
-    <sortCondition descending="1" ref="I1:I28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D20DD51-13C3-5845-AB11-DD7C452F876E}" name="Success" displayName="Success" ref="A1:L28" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
+  <autoFilter ref="A1:L28" xr:uid="{4D20DD51-13C3-5845-AB11-DD7C452F876E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L28">
+    <sortCondition descending="1" ref="C1:C28"/>
   </sortState>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{0063AB55-DE73-9A4D-BB26-B8B0C7549352}" name="Paper Title" dataDxfId="47"/>
-    <tableColumn id="2" xr3:uid="{7A6BCA33-7E76-884F-8D2C-C221FD761545}" name="Authors" dataDxfId="46"/>
-    <tableColumn id="3" xr3:uid="{BFF03DD3-ABE0-1441-BF7E-ECDE6EA486AC}" name="Year" dataDxfId="45"/>
-    <tableColumn id="4" xr3:uid="{7462CFB0-5041-4E40-B883-8FD56BA117B2}" name="Journal Title" dataDxfId="44"/>
-    <tableColumn id="5" xr3:uid="{A0E9FAB5-39BC-2F4F-A205-AB5CC0364F27}" name="Abstract" dataDxfId="43"/>
-    <tableColumn id="6" xr3:uid="{4C388556-A10C-6844-B741-D8339459D8C5}" name="DOI" dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{4EEB7A0F-F93B-A641-8436-B67AE36E027C}" name="Insights for Thesis" dataDxfId="41"/>
-    <tableColumn id="9" xr3:uid="{56BD3BA3-87C4-0B44-8072-EADA3EAA2EFC}" name="Outcomes" dataDxfId="40"/>
-    <tableColumn id="13" xr3:uid="{4DB6468D-1D4F-6247-AC1B-BBD4D59EE943}" name="Relevance" dataDxfId="39"/>
-    <tableColumn id="14" xr3:uid="{AE6D7396-2898-3F4D-BA46-767CBD12EE46}" name="Link" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{B540F483-EE23-984D-834A-FC30579AD342}" name="Reviewed?" dataDxfId="4"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{0063AB55-DE73-9A4D-BB26-B8B0C7549352}" name="Paper Title" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{7A6BCA33-7E76-884F-8D2C-C221FD761545}" name="Authors" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{BFF03DD3-ABE0-1441-BF7E-ECDE6EA486AC}" name="Year" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{7462CFB0-5041-4E40-B883-8FD56BA117B2}" name="Journal Title" dataDxfId="48"/>
+    <tableColumn id="10" xr3:uid="{C985F5F5-771E-7848-9FE9-A53029FFC0FB}" name="Journal Importance" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{A0E9FAB5-39BC-2F4F-A205-AB5CC0364F27}" name="Abstract" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{4C388556-A10C-6844-B741-D8339459D8C5}" name="DOI" dataDxfId="46"/>
+    <tableColumn id="8" xr3:uid="{4EEB7A0F-F93B-A641-8436-B67AE36E027C}" name="Insights for Thesis" dataDxfId="45"/>
+    <tableColumn id="9" xr3:uid="{56BD3BA3-87C4-0B44-8072-EADA3EAA2EFC}" name="Outcomes" dataDxfId="44"/>
+    <tableColumn id="13" xr3:uid="{4DB6468D-1D4F-6247-AC1B-BBD4D59EE943}" name="Relevance" dataDxfId="43"/>
+    <tableColumn id="14" xr3:uid="{AE6D7396-2898-3F4D-BA46-767CBD12EE46}" name="Link" dataDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{B540F483-EE23-984D-834A-FC30579AD342}" name="Reviewed?" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A30AD82-02A7-6745-A2CA-934FA2D6ABD4}" name="Support" displayName="Support" ref="A1:K18" totalsRowShown="0" dataDxfId="14">
-  <autoFilter ref="A1:K18" xr:uid="{6A30AD82-02A7-6745-A2CA-934FA2D6ABD4}"/>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A616AEE6-C6DE-3848-B3E0-6002397B9882}" name="Paper Title" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{FF60328E-A314-FD4E-820F-3DB20EB3439C}" name="Authors" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{CBBF5768-3F3B-6540-A093-4FD23CD75C72}" name="Year" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{01171707-AA15-DD41-B524-CDE7D67FF738}" name="Journal Title" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{AB646E0C-5A77-1444-B818-4CEB6E7B9BFA}" name="Abstract" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{A321187A-382D-FE46-806D-75FA9604EB6B}" name="DOI" dataDxfId="8" dataCellStyle="Hyperlink"/>
-    <tableColumn id="11" xr3:uid="{0512DC86-6CE5-CB45-B301-2161DBBC1236}" name="Insights for Thesis" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{B6492819-882E-6E43-A300-8E723AE7BF33}" name="Outcomes" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{FAC6D398-1FDC-6944-9A7E-34C28ECDAA8B}" name="Relevance" dataDxfId="0"/>
-    <tableColumn id="14" xr3:uid="{F7655086-4881-9D4F-BDBF-0FB8DE110B27}" name="Link" dataDxfId="5" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{3A688F49-F3F4-B549-83D0-B0942C7EE14B}" name="Reviewed?" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A30AD82-02A7-6745-A2CA-934FA2D6ABD4}" name="Support" displayName="Support" ref="A1:L18" totalsRowShown="0" dataDxfId="40">
+  <autoFilter ref="A1:L18" xr:uid="{6A30AD82-02A7-6745-A2CA-934FA2D6ABD4}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L18">
+    <sortCondition descending="1" ref="C1:C18"/>
+  </sortState>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{A616AEE6-C6DE-3848-B3E0-6002397B9882}" name="Paper Title" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{FF60328E-A314-FD4E-820F-3DB20EB3439C}" name="Authors" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{CBBF5768-3F3B-6540-A093-4FD23CD75C72}" name="Year" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{01171707-AA15-DD41-B524-CDE7D67FF738}" name="Journal Title" dataDxfId="36"/>
+    <tableColumn id="8" xr3:uid="{11C89D04-6481-D540-AA96-61DAC7AF4A34}" name="Journal Importance" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{AB646E0C-5A77-1444-B818-4CEB6E7B9BFA}" name="Abstract" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{A321187A-382D-FE46-806D-75FA9604EB6B}" name="DOI" dataDxfId="34" dataCellStyle="Hyperlink"/>
+    <tableColumn id="11" xr3:uid="{0512DC86-6CE5-CB45-B301-2161DBBC1236}" name="Insights for Thesis" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{B6492819-882E-6E43-A300-8E723AE7BF33}" name="Outcomes" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{FAC6D398-1FDC-6944-9A7E-34C28ECDAA8B}" name="Relevance" dataDxfId="31"/>
+    <tableColumn id="14" xr3:uid="{F7655086-4881-9D4F-BDBF-0FB8DE110B27}" name="Link" dataDxfId="30" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{3A688F49-F3F4-B549-83D0-B0942C7EE14B}" name="Reviewed?" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium17" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6B0EF1A4-B632-064C-B047-AFD93614047D}" name="Ecosystem" displayName="Ecosystem" ref="A1:K14" totalsRowShown="0" dataDxfId="37">
-  <autoFilter ref="A1:K14" xr:uid="{6B0EF1A4-B632-064C-B047-AFD93614047D}"/>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{DDA40927-D99D-7944-ABBB-E062EAC00CB0}" name="Paper Title" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{7063D636-C85B-3548-A015-8D7C939D4FA5}" name="Authors" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{0A4B399A-AD2E-3048-B417-A6AB46292C0E}" name="Year" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{3ED340CA-2C59-CE48-BDF0-D7CD1022D6AA}" name="Journal Title" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{CFA5C437-782F-2146-99F8-88849AC4D708}" name="Abstract" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{2C7F3A04-CCDB-D144-A543-AB8BA33557A9}" name="DOI" dataDxfId="31" dataCellStyle="Hyperlink"/>
-    <tableColumn id="8" xr3:uid="{3BA165FD-1D1B-A345-AA35-D599109FCC87}" name="Insights for Thesis" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{E3BC98A8-DF66-6B4E-8276-EBF6B58FA40E}" name="Outcomes" dataDxfId="29"/>
-    <tableColumn id="13" xr3:uid="{D0CB5091-71CC-C248-9A19-F90F8F2E8297}" name="Relevance" dataDxfId="28"/>
-    <tableColumn id="14" xr3:uid="{C927F29E-2777-C84F-A9EA-3EA05CD3B954}" name="Link" dataDxfId="27" dataCellStyle="Hyperlink"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6B0EF1A4-B632-064C-B047-AFD93614047D}" name="Ecosystem" displayName="Ecosystem" ref="A1:L14" totalsRowShown="0" dataDxfId="13">
+  <autoFilter ref="A1:L14" xr:uid="{6B0EF1A4-B632-064C-B047-AFD93614047D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L14">
+    <sortCondition descending="1" ref="C1:C14"/>
+  </sortState>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{DDA40927-D99D-7944-ABBB-E062EAC00CB0}" name="Paper Title" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{7063D636-C85B-3548-A015-8D7C939D4FA5}" name="Authors" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{0A4B399A-AD2E-3048-B417-A6AB46292C0E}" name="Year" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{3ED340CA-2C59-CE48-BDF0-D7CD1022D6AA}" name="Journal Title" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{6613DB95-863F-B043-ABF2-28DACB82C976}" name="Journal Importance" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{CFA5C437-782F-2146-99F8-88849AC4D708}" name="Abstract" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{2C7F3A04-CCDB-D144-A543-AB8BA33557A9}" name="DOI" dataDxfId="7" dataCellStyle="Hyperlink"/>
+    <tableColumn id="8" xr3:uid="{3BA165FD-1D1B-A345-AA35-D599109FCC87}" name="Insights for Thesis" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{E3BC98A8-DF66-6B4E-8276-EBF6B58FA40E}" name="Outcomes" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{D0CB5091-71CC-C248-9A19-F90F8F2E8297}" name="Relevance" dataDxfId="4"/>
+    <tableColumn id="14" xr3:uid="{C927F29E-2777-C84F-A9EA-3EA05CD3B954}" name="Link" dataDxfId="3" dataCellStyle="Hyperlink"/>
     <tableColumn id="7" xr3:uid="{FF6D7400-F425-4C42-9BBF-ADFBE98D0F07}" name="Reviewed?" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3386,23 +3511,24 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BDB057D3-C952-D345-8F2C-B84814345F7C}" name="Network" displayName="Network" ref="A1:K21" totalsRowShown="0" dataDxfId="26">
-  <autoFilter ref="A1:K21" xr:uid="{BDB057D3-C952-D345-8F2C-B84814345F7C}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition descending="1" ref="I1:I19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BDB057D3-C952-D345-8F2C-B84814345F7C}" name="Network" displayName="Network" ref="A1:L21" totalsRowShown="0" dataDxfId="28">
+  <autoFilter ref="A1:L21" xr:uid="{BDB057D3-C952-D345-8F2C-B84814345F7C}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L21">
+    <sortCondition descending="1" ref="C1:C21"/>
   </sortState>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{CF32DED6-F460-BC4E-8425-9A38061898F6}" name="Paper Title" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{CCB95980-EAA8-D249-8BBC-397525A2F450}" name="Authors" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{037E5B70-94CF-D440-816F-4E3CB4C9BD23}" name="Year" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{1E353C60-E639-2940-9E11-2CA96BECA2DB}" name="Journal Title" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{C27CEDF0-021E-AD4C-AC46-79A57416DDAD}" name="Abstract" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{5A1165FC-0522-0E42-9695-D8A474BA3183}" name="DOI" dataDxfId="20" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{0BFB5501-86F2-9343-A561-78081AAC3D16}" name="Insights for Thesis" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{46301428-00AB-1B40-B9BD-76F9077E5805}" name="Outcomes" dataDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{405179D8-608B-E04F-9EFF-3BFD48149919}" name="Relevance" dataDxfId="17"/>
-    <tableColumn id="14" xr3:uid="{9C55F2EE-8819-AB4B-BBE8-87A1890AB86E}" name="Link" dataDxfId="16" dataCellStyle="Hyperlink"/>
-    <tableColumn id="9" xr3:uid="{EC72141A-19AA-6848-B1E6-106BFB0309A1}" name="Reviewed?" dataDxfId="1"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{CF32DED6-F460-BC4E-8425-9A38061898F6}" name="Paper Title" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{CCB95980-EAA8-D249-8BBC-397525A2F450}" name="Authors" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{037E5B70-94CF-D440-816F-4E3CB4C9BD23}" name="Year" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{1E353C60-E639-2940-9E11-2CA96BECA2DB}" name="Journal Title" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{4F321EEF-3C49-F549-99B7-4791D31958FF}" name="Journal Importance" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{C27CEDF0-021E-AD4C-AC46-79A57416DDAD}" name="Abstract" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{5A1165FC-0522-0E42-9695-D8A474BA3183}" name="DOI" dataDxfId="22" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{0BFB5501-86F2-9343-A561-78081AAC3D16}" name="Insights for Thesis" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{46301428-00AB-1B40-B9BD-76F9077E5805}" name="Outcomes" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{405179D8-608B-E04F-9EFF-3BFD48149919}" name="Relevance" dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{9C55F2EE-8819-AB4B-BBE8-87A1890AB86E}" name="Link" dataDxfId="18" dataCellStyle="Hyperlink"/>
+    <tableColumn id="9" xr3:uid="{EC72141A-19AA-6848-B1E6-106BFB0309A1}" name="Reviewed?" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3725,27 +3851,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{838C02D4-FEA1-2A47-B8BA-8639EEFFB0CC}">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.5" customWidth="1"/>
     <col min="3" max="3" width="14.5" customWidth="1"/>
-    <col min="4" max="4" width="29.5" customWidth="1"/>
-    <col min="5" max="5" width="52.1640625" customWidth="1"/>
-    <col min="6" max="6" width="33.1640625" customWidth="1"/>
-    <col min="7" max="7" width="45.1640625" customWidth="1"/>
-    <col min="8" max="8" width="39.6640625" customWidth="1"/>
-    <col min="9" max="9" width="51.6640625" customWidth="1"/>
-    <col min="10" max="10" width="52.5" style="3" customWidth="1"/>
-    <col min="11" max="11" width="49" customWidth="1"/>
-    <col min="12" max="12" width="29" customWidth="1"/>
-    <col min="14" max="14" width="36.5" customWidth="1"/>
+    <col min="4" max="5" width="29.5" customWidth="1"/>
+    <col min="6" max="6" width="52.1640625" customWidth="1"/>
+    <col min="7" max="7" width="33.1640625" customWidth="1"/>
+    <col min="8" max="8" width="45.1640625" customWidth="1"/>
+    <col min="9" max="9" width="39.6640625" customWidth="1"/>
+    <col min="10" max="10" width="51.6640625" customWidth="1"/>
+    <col min="11" max="11" width="52.5" style="3" customWidth="1"/>
+    <col min="12" max="12" width="49" customWidth="1"/>
+    <col min="13" max="13" width="29" customWidth="1"/>
+    <col min="15" max="15" width="36.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
@@ -3754,1112 +3880,1437 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s">
+        <v>606</v>
+      </c>
+      <c r="F1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" t="s">
-        <v>12</v>
-      </c>
       <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>1</v>
       </c>
-      <c r="J1" t="s">
-        <v>110</v>
-      </c>
       <c r="K1" t="s">
+        <v>107</v>
+      </c>
+      <c r="L1" t="s">
         <v>2</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>7</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>8</v>
       </c>
-      <c r="N1" t="s">
-        <v>116</v>
-      </c>
       <c r="O1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+      <c r="P1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" s="1" customFormat="1" ht="323" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C2" s="5">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>19</v>
+        <v>607</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="5"/>
+        <v>28</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="11"/>
       <c r="L2" s="5"/>
-      <c r="M2" s="5">
+      <c r="M2" s="5"/>
+      <c r="N2" s="5">
         <v>3</v>
       </c>
-      <c r="N2" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="323" x14ac:dyDescent="0.2">
+      <c r="O2" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="C3" s="5">
         <v>2025</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>30</v>
+        <v>608</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="5"/>
+        <v>101</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="11"/>
       <c r="L3" s="5"/>
-      <c r="M3" s="5">
+      <c r="M3" s="5"/>
+      <c r="N3" s="5">
         <v>3</v>
       </c>
-      <c r="N3" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="221" x14ac:dyDescent="0.2">
+      <c r="O3" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="340" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="C4" s="5">
-        <v>2010</v>
-      </c>
-      <c r="D4" s="5"/>
+        <v>2025</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="E4" s="5" t="s">
-        <v>38</v>
+        <v>605</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="11">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5" t="s">
-        <v>564</v>
-      </c>
-      <c r="M4" s="5">
+      <c r="J4" s="5"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5">
         <v>3</v>
       </c>
-      <c r="N4" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="255" x14ac:dyDescent="0.2">
+      <c r="O4" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>46</v>
+        <v>634</v>
       </c>
       <c r="C5" s="5">
-        <v>2008</v>
+        <v>2024</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>52</v>
+        <v>608</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="5"/>
+        <v>17</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="11"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="5">
+      <c r="M5" s="5"/>
+      <c r="N5" s="5">
         <v>3</v>
       </c>
-      <c r="N5" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="O5" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="356" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>563</v>
+        <v>39</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="C6" s="5">
-        <v>2005</v>
+        <v>2024</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>80</v>
+        <v>605</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="5"/>
+        <v>42</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="11"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="5">
-        <v>3</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="M6" s="5"/>
+      <c r="N6" s="5">
+        <v>1</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="P6" s="5"/>
+    </row>
+    <row r="7" spans="1:16" ht="289" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="C7" s="5">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="G7" s="5"/>
+        <v>605</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="11"/>
       <c r="L7" s="5"/>
-      <c r="M7" s="5">
-        <v>3</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="306" x14ac:dyDescent="0.2">
+      <c r="M7" s="5"/>
+      <c r="N7" s="5">
+        <v>2</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="P7" s="5"/>
+    </row>
+    <row r="8" spans="1:16" ht="340" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="C8" s="5">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="G8" s="5"/>
+        <v>605</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>83</v>
+      </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="11"/>
       <c r="L8" s="5"/>
-      <c r="M8" s="5">
-        <v>3</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="323" x14ac:dyDescent="0.2">
+      <c r="M8" s="5"/>
+      <c r="N8" s="5">
+        <v>2</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="P8" s="5"/>
+    </row>
+    <row r="9" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>553</v>
+        <v>91</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>555</v>
-      </c>
-      <c r="C9" s="27">
-        <v>2009</v>
+        <v>92</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2024</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>556</v>
+        <v>93</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>554</v>
-      </c>
-      <c r="F9" s="5"/>
+        <v>608</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>94</v>
+      </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="11"/>
       <c r="L9" s="5"/>
-      <c r="M9" s="5">
-        <v>3</v>
-      </c>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="323" x14ac:dyDescent="0.2">
+      <c r="M9" s="5"/>
+      <c r="N9" s="5">
+        <v>1</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="P9" s="5"/>
+    </row>
+    <row r="10" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>511</v>
+        <v>103</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>512</v>
+        <v>104</v>
       </c>
       <c r="C10" s="5">
-        <v>2001</v>
+        <v>2023</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>513</v>
+        <v>105</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="F10" s="5"/>
+        <v>610</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>106</v>
+      </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="11"/>
       <c r="L10" s="5"/>
-      <c r="M10" s="5">
+      <c r="M10" s="5"/>
+      <c r="N10" s="5">
         <v>2</v>
       </c>
-      <c r="N10" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="404" x14ac:dyDescent="0.2">
+      <c r="O10" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="P10" s="5"/>
+    </row>
+    <row r="11" spans="1:16" ht="340" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>540</v>
+        <v>62</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>541</v>
+        <v>63</v>
       </c>
       <c r="C11" s="5">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>542</v>
+        <v>64</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>543</v>
+        <v>605</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>544</v>
-      </c>
-      <c r="G11" s="5"/>
+        <v>65</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>66</v>
+      </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="11"/>
       <c r="L11" s="5"/>
-      <c r="M11" s="5">
-        <v>2</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>545</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="340" x14ac:dyDescent="0.2">
+      <c r="M11" s="5"/>
+      <c r="N11" s="5">
+        <v>3</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="P11" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="289" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="C12" s="5">
-        <v>2025</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>91</v>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F12" s="5"/>
+        <v>607</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="11"/>
       <c r="L12" s="5"/>
-      <c r="M12" s="5">
-        <v>3</v>
-      </c>
-      <c r="N12" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="M12" s="5"/>
+      <c r="N12" s="5">
+        <v>1</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="P12" s="5"/>
+    </row>
+    <row r="13" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>137</v>
+        <v>23</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="C13" s="5">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G13" s="5"/>
+        <v>607</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="11"/>
       <c r="L13" s="5"/>
-      <c r="M13" s="5">
-        <v>1</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="M13" s="5"/>
+      <c r="N13" s="5">
+        <v>2</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="P13" s="5"/>
+    </row>
+    <row r="14" spans="1:16" ht="306" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C14" s="5">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+        <v>605</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>112</v>
+      </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="11"/>
       <c r="L14" s="5"/>
-      <c r="M14" s="5">
-        <v>2</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="O14" s="5"/>
-    </row>
-    <row r="15" spans="1:15" ht="356" x14ac:dyDescent="0.2">
+      <c r="M14" s="5"/>
+      <c r="N14" s="5">
+        <v>3</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="P14" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="221" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C15" s="5">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>44</v>
+        <v>607</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="11"/>
       <c r="L15" s="5"/>
-      <c r="M15" s="5">
-        <v>2</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="O15" s="5"/>
-    </row>
-    <row r="16" spans="1:15" ht="272" x14ac:dyDescent="0.2">
+      <c r="M15" s="5"/>
+      <c r="N15" s="5">
+        <v>1</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="P15" s="5"/>
+    </row>
+    <row r="16" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="C16" s="5">
-        <v>2006</v>
+        <v>2020</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>565</v>
+        <v>605</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="11"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="5">
-        <v>2</v>
-      </c>
-      <c r="N16" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="388" x14ac:dyDescent="0.2">
+      <c r="M16" s="5"/>
+      <c r="N16" s="5">
+        <v>1</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="P16" s="5"/>
+    </row>
+    <row r="17" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C17" s="5">
-        <v>2013</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>71</v>
-      </c>
+        <v>2020</v>
+      </c>
+      <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>73</v>
+        <v>607</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>635</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="11"/>
       <c r="L17" s="5"/>
-      <c r="M17" s="5">
-        <v>2</v>
-      </c>
-      <c r="N17" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="M17" s="5"/>
+      <c r="N17" s="5">
+        <v>1</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="P17" s="5"/>
+    </row>
+    <row r="18" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>10</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="C18" s="5">
         <v>2019</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>9</v>
+        <v>605</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="5"/>
+        <v>636</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="11"/>
       <c r="L18" s="5"/>
-      <c r="M18" s="5">
+      <c r="M18" s="5"/>
+      <c r="N18" s="5">
         <v>2</v>
       </c>
-      <c r="N18" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="O18" s="5"/>
-    </row>
-    <row r="19" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="O18" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P18" s="5"/>
+    </row>
+    <row r="19" spans="1:16" ht="388" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>25</v>
+        <v>570</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>21</v>
+        <v>569</v>
       </c>
       <c r="C19" s="5">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>22</v>
+        <v>262</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>23</v>
+        <v>605</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" s="5"/>
+        <v>571</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>572</v>
+      </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="11"/>
       <c r="L19" s="5"/>
-      <c r="M19" s="5">
+      <c r="M19" s="5"/>
+      <c r="N19" s="5">
         <v>2</v>
       </c>
-      <c r="N19" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="O19" s="5"/>
-    </row>
-    <row r="20" spans="1:15" ht="289" x14ac:dyDescent="0.2">
+      <c r="O19" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="P19" s="5"/>
+    </row>
+    <row r="20" spans="1:16" ht="356" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C20" s="5">
-        <v>2024</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>56</v>
-      </c>
+        <v>2019</v>
+      </c>
+      <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>58</v>
+        <v>607</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="11"/>
       <c r="L20" s="5"/>
-      <c r="M20" s="5">
-        <v>2</v>
-      </c>
-      <c r="N20" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="O20" s="5"/>
-    </row>
-    <row r="21" spans="1:15" ht="340" x14ac:dyDescent="0.2">
+      <c r="M20" s="5"/>
+      <c r="N20" s="5">
+        <v>3</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="P20" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="404" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>64</v>
+        <v>537</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>65</v>
+        <v>538</v>
       </c>
       <c r="C21" s="5">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>66</v>
+        <v>539</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G21" s="5"/>
+        <v>605</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>541</v>
+      </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="11"/>
       <c r="L21" s="5"/>
-      <c r="M21" s="5">
-        <v>3</v>
-      </c>
-      <c r="N21" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="O21" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="M21" s="5"/>
+      <c r="N21" s="5">
+        <v>2</v>
+      </c>
+      <c r="O21" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="P21" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="388" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>144</v>
+        <v>67</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C22" s="5">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
+        <v>605</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="11"/>
       <c r="L22" s="5"/>
-      <c r="M22" s="5">
+      <c r="M22" s="5"/>
+      <c r="N22" s="5">
         <v>2</v>
       </c>
-      <c r="N22" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="O22" s="5"/>
-    </row>
-    <row r="23" spans="1:15" ht="340" x14ac:dyDescent="0.2">
+      <c r="O22" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P22" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="221" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="C23" s="5">
-        <v>2024</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>87</v>
-      </c>
+        <v>2010</v>
+      </c>
+      <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="G23" s="5"/>
+        <v>607</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>37</v>
+      </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="11">
+        <v>1</v>
+      </c>
       <c r="L23" s="5"/>
-      <c r="M23" s="5">
-        <v>2</v>
-      </c>
-      <c r="N23" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="O23" s="5"/>
-    </row>
-    <row r="24" spans="1:15" ht="388" x14ac:dyDescent="0.2">
+      <c r="M23" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="N23" s="5">
+        <v>3</v>
+      </c>
+      <c r="O23" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="P23" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="323" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>573</v>
+        <v>550</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="C24" s="27">
-        <v>2019</v>
+        <v>552</v>
+      </c>
+      <c r="C24" s="5">
+        <v>2009</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>265</v>
+        <v>553</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>575</v>
+        <v>607</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>551</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="11"/>
       <c r="L24" s="5"/>
-      <c r="M24" s="5">
-        <v>2</v>
-      </c>
-      <c r="N24" s="8" t="s">
-        <v>576</v>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5">
+        <v>3</v>
       </c>
       <c r="O24" s="5"/>
-    </row>
-    <row r="25" spans="1:15" ht="289" x14ac:dyDescent="0.2">
+      <c r="P24" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="255" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>566</v>
+        <v>48</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="C25" s="5">
+        <v>2008</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="E25" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
+        <v>605</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="11"/>
       <c r="L25" s="5"/>
-      <c r="M25" s="5">
-        <v>1</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="O25" s="5"/>
-    </row>
-    <row r="26" spans="1:15" ht="221" x14ac:dyDescent="0.2">
+      <c r="M25" s="5"/>
+      <c r="N25" s="5">
+        <v>3</v>
+      </c>
+      <c r="O25" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="P25" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="289" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>32</v>
+        <v>599</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>33</v>
+        <v>598</v>
       </c>
       <c r="C26" s="5">
-        <v>2021</v>
+        <v>2008</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>34</v>
+        <v>235</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F26" s="5"/>
+        <v>605</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>600</v>
+      </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="11"/>
       <c r="L26" s="5"/>
-      <c r="M26" s="5">
-        <v>1</v>
-      </c>
-      <c r="N26" s="8" t="s">
+      <c r="M26" s="5"/>
+      <c r="N26" s="5">
+        <v>3</v>
+      </c>
+      <c r="O26" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="P26" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="272" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="5">
+        <v>2006</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5">
+        <v>2</v>
+      </c>
+      <c r="O27" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="O26" s="5"/>
-    </row>
-    <row r="27" spans="1:15" ht="356" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="5">
-        <v>2019</v>
-      </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5">
-        <v>3</v>
-      </c>
-      <c r="N27" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="O27" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="289" x14ac:dyDescent="0.2">
+      <c r="P27" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>143</v>
+        <v>560</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C28" s="5">
-        <v>2023</v>
-      </c>
-      <c r="D28" s="5"/>
+        <v>2005</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="E28" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
+        <v>605</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="11"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="5">
-        <v>1</v>
-      </c>
-      <c r="N28" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="O28" s="5"/>
-    </row>
-    <row r="29" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="M28" s="5"/>
+      <c r="N28" s="5">
+        <v>3</v>
+      </c>
+      <c r="O28" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="P28" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="323" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>74</v>
+        <v>574</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>75</v>
+        <v>575</v>
       </c>
       <c r="C29" s="5">
-        <v>2020</v>
-      </c>
-      <c r="D29" s="5"/>
+        <v>2003</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>604</v>
+      </c>
       <c r="E29" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F29" s="5"/>
+        <v>605</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>576</v>
+      </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="11"/>
       <c r="L29" s="5"/>
-      <c r="M29" s="5">
+      <c r="M29" s="5"/>
+      <c r="N29" s="5">
         <v>1</v>
       </c>
-      <c r="N29" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="O29" s="5"/>
-    </row>
-    <row r="30" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="O29" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="P29" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C30" s="5">
-        <v>2024</v>
+        <v>2002</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F30" s="5"/>
+        <v>605</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>81</v>
+      </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="11"/>
       <c r="L30" s="5"/>
-      <c r="M30" s="5">
-        <v>1</v>
-      </c>
-      <c r="N30" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="O30" s="5"/>
-    </row>
-    <row r="31" spans="1:15" ht="323" x14ac:dyDescent="0.2">
+      <c r="M30" s="5"/>
+      <c r="N30" s="5">
+        <v>2</v>
+      </c>
+      <c r="O30" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="P30" s="5"/>
+    </row>
+    <row r="31" spans="1:16" ht="323" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>577</v>
+        <v>508</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>578</v>
-      </c>
-      <c r="C31" s="27">
-        <v>2003</v>
+        <v>509</v>
+      </c>
+      <c r="C31" s="5">
+        <v>2001</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>579</v>
+        <v>510</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="F31" s="5"/>
+        <v>605</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>511</v>
+      </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
-      <c r="J31" s="28"/>
-      <c r="K31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="11"/>
       <c r="L31" s="5"/>
-      <c r="M31" s="5">
-        <v>1</v>
-      </c>
-      <c r="N31" s="8" t="s">
-        <v>581</v>
-      </c>
-      <c r="O31" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="289" x14ac:dyDescent="0.2">
+      <c r="M31" s="5"/>
+      <c r="N31" s="5">
+        <v>2</v>
+      </c>
+      <c r="O31" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="P31" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="289" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>603</v>
+        <v>563</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>602</v>
-      </c>
-      <c r="C32" s="27">
-        <v>2008</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>238</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="F32" s="5"/>
+        <v>607</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="11"/>
       <c r="L32" s="5"/>
-      <c r="M32" s="5">
-        <v>3</v>
-      </c>
-      <c r="N32" s="8" t="s">
+      <c r="M32" s="5"/>
+      <c r="N32" s="5">
+        <v>1</v>
+      </c>
+      <c r="O32" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="P32" s="5"/>
+    </row>
+    <row r="33" spans="1:16" ht="238" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="C33" s="28">
+        <v>2006</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="O32" s="5" t="s">
-        <v>547</v>
-      </c>
+      <c r="F33" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5">
+        <v>2</v>
+      </c>
+      <c r="O33" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="P33" s="5"/>
+    </row>
+    <row r="34" spans="1:16" ht="289" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="C34" s="28">
+        <v>2018</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5">
+        <v>2</v>
+      </c>
+      <c r="O34" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="P34" s="5"/>
+    </row>
+    <row r="35" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="C35" s="28">
+        <v>2005</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5">
+        <v>2</v>
+      </c>
+      <c r="O35" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="P35" s="5"/>
+    </row>
+    <row r="36" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="C36" s="28">
+        <v>2002</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5">
+        <v>1</v>
+      </c>
+      <c r="O36" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="P36" s="5"/>
+    </row>
+    <row r="37" spans="1:16" ht="388" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="C37" s="28">
+        <v>2006</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5">
+        <v>2</v>
+      </c>
+      <c r="O37" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="P37" s="5"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F18" r:id="rId1" xr:uid="{4D075623-F47A-C241-BA26-47F34E18DBE0}"/>
-    <hyperlink ref="F2" r:id="rId2" xr:uid="{A599610C-8E28-FF46-AF97-F654E2FF8D0C}"/>
-    <hyperlink ref="F19" r:id="rId3" xr:uid="{2BB80285-735B-8642-8B2F-DE3ECFBFB9D3}"/>
-    <hyperlink ref="F15" r:id="rId4" xr:uid="{7E3F95FA-AA8F-6547-AFD7-99B62FC32261}"/>
-    <hyperlink ref="F16" r:id="rId5" xr:uid="{52C87578-F7CD-0448-B122-43F0CF953442}"/>
-    <hyperlink ref="F20" r:id="rId6" xr:uid="{F72867A8-36AE-7E49-ADC7-8BC86A725CC5}"/>
-    <hyperlink ref="F21" r:id="rId7" xr:uid="{D69A8C58-0DEA-E044-9265-C6975A5B047F}"/>
-    <hyperlink ref="F17" r:id="rId8" xr:uid="{C8EE0297-E77F-9C49-BE05-383255A44F3C}"/>
-    <hyperlink ref="F23" r:id="rId9" xr:uid="{9247B1AB-9E42-384F-983F-69372B3F644F}"/>
-    <hyperlink ref="F13" r:id="rId10" xr:uid="{F326DCE5-B04B-2446-88A1-47458E7B8FA7}"/>
-    <hyperlink ref="F7" r:id="rId11" xr:uid="{3B3B1185-0313-EA43-A20E-A66F4E3C12C8}"/>
-    <hyperlink ref="F8" r:id="rId12" xr:uid="{87FD19EA-2FF5-0A4E-B9F0-8BF4FAA2D4C8}"/>
-    <hyperlink ref="N18" r:id="rId13" xr:uid="{62ABAC52-587B-F24B-A5F8-7B2442F7B793}"/>
-    <hyperlink ref="N2" r:id="rId14" xr:uid="{D52B21D2-1870-3445-89FB-CB0DA674EA44}"/>
-    <hyperlink ref="N19" r:id="rId15" xr:uid="{D8745F7E-73C3-0E44-9A2F-869DDF9B58BE}"/>
-    <hyperlink ref="N3" r:id="rId16" xr:uid="{BF38B245-2341-844F-B8CC-942209E9FAE6}"/>
-    <hyperlink ref="N26" r:id="rId17" xr:uid="{9AC937BC-870F-F942-A30D-275F5A55CD28}"/>
-    <hyperlink ref="N4" r:id="rId18" xr:uid="{768E63B1-3426-2A4D-9675-00F8B1DED5D6}"/>
-    <hyperlink ref="N15" r:id="rId19" xr:uid="{4CF68763-A4D3-CE4C-B3CE-EFF4C2E44BBC}"/>
-    <hyperlink ref="N16" r:id="rId20" xr:uid="{043C7281-C851-DA44-896E-785E48CC5BF0}"/>
-    <hyperlink ref="N20" r:id="rId21" xr:uid="{4B25B642-AB57-A948-9F1F-CE9FBB72552A}"/>
-    <hyperlink ref="N5" r:id="rId22" xr:uid="{AE5B19D9-6FD8-3844-B2C3-393DE6E294BD}"/>
-    <hyperlink ref="N27" r:id="rId23" xr:uid="{E503FFD0-0C6D-7B42-A7D3-B2A9369ADC3D}"/>
-    <hyperlink ref="N28" r:id="rId24" xr:uid="{A821D349-5B20-DD4A-87B3-8EEEBCF1591A}"/>
-    <hyperlink ref="N29" r:id="rId25" xr:uid="{E7C42ED7-6B2B-AA49-80AE-7DAB2961A75B}"/>
-    <hyperlink ref="N25" r:id="rId26" xr:uid="{C3D6346C-3B62-6540-93A6-5587E45AA965}"/>
-    <hyperlink ref="N22" r:id="rId27" xr:uid="{4D01A381-BDB6-A043-BB11-176654BE85BB}"/>
-    <hyperlink ref="N23" r:id="rId28" xr:uid="{2F15E816-0090-0D42-BD60-08A4C005B5E7}"/>
-    <hyperlink ref="N12" r:id="rId29" xr:uid="{EE3793CF-C275-6C4E-8397-9C0C5C1B2718}"/>
-    <hyperlink ref="N13" r:id="rId30" xr:uid="{525A1821-814E-E744-AED3-27CE95DA83E3}"/>
-    <hyperlink ref="N7" r:id="rId31" xr:uid="{8846EC74-255C-4548-AB9C-48723A3FAADB}"/>
-    <hyperlink ref="N14" r:id="rId32" xr:uid="{44447FCA-1465-A14C-A316-A7A3FE766D04}"/>
-    <hyperlink ref="N8" r:id="rId33" xr:uid="{D164B1C7-0E17-ED49-B3AA-8194BD8BD4B1}"/>
-    <hyperlink ref="N11" r:id="rId34" xr:uid="{0EBAC3C5-5187-E24E-AD1D-B017F86CAA63}"/>
-    <hyperlink ref="N6" r:id="rId35" xr:uid="{1E1BB8C5-3B47-7D40-9F70-F9CC342E7EF1}"/>
-    <hyperlink ref="F24" r:id="rId36" xr:uid="{9D6FD438-E5D5-F248-A56D-46BB846C99A3}"/>
-    <hyperlink ref="N24" r:id="rId37" xr:uid="{9DAB3A76-1857-A64E-AF97-FAA63B31D43B}"/>
-    <hyperlink ref="N31" r:id="rId38" xr:uid="{8CC8A20F-060B-504C-8AD5-0BDD88A6A5D1}"/>
-    <hyperlink ref="N10" r:id="rId39" xr:uid="{90C029BA-AD4A-B340-B468-A6D6B34352DF}"/>
-    <hyperlink ref="N21" r:id="rId40" xr:uid="{B0DD1CAC-2599-0142-A54A-FA8C4F9EC4F9}"/>
-    <hyperlink ref="N32" r:id="rId41" xr:uid="{72D9B6BC-C8EE-BA42-9E97-1F370FCFEDCA}"/>
+    <hyperlink ref="G18" r:id="rId1" xr:uid="{4D075623-F47A-C241-BA26-47F34E18DBE0}"/>
+    <hyperlink ref="G5" r:id="rId2" xr:uid="{A599610C-8E28-FF46-AF97-F654E2FF8D0C}"/>
+    <hyperlink ref="G13" r:id="rId3" xr:uid="{2BB80285-735B-8642-8B2F-DE3ECFBFB9D3}"/>
+    <hyperlink ref="G6" r:id="rId4" xr:uid="{7E3F95FA-AA8F-6547-AFD7-99B62FC32261}"/>
+    <hyperlink ref="G27" r:id="rId5" xr:uid="{52C87578-F7CD-0448-B122-43F0CF953442}"/>
+    <hyperlink ref="G7" r:id="rId6" xr:uid="{F72867A8-36AE-7E49-ADC7-8BC86A725CC5}"/>
+    <hyperlink ref="G11" r:id="rId7" xr:uid="{D69A8C58-0DEA-E044-9265-C6975A5B047F}"/>
+    <hyperlink ref="G22" r:id="rId8" xr:uid="{C8EE0297-E77F-9C49-BE05-383255A44F3C}"/>
+    <hyperlink ref="G8" r:id="rId9" xr:uid="{9247B1AB-9E42-384F-983F-69372B3F644F}"/>
+    <hyperlink ref="G16" r:id="rId10" xr:uid="{F326DCE5-B04B-2446-88A1-47458E7B8FA7}"/>
+    <hyperlink ref="G3" r:id="rId11" xr:uid="{3B3B1185-0313-EA43-A20E-A66F4E3C12C8}"/>
+    <hyperlink ref="G14" r:id="rId12" xr:uid="{87FD19EA-2FF5-0A4E-B9F0-8BF4FAA2D4C8}"/>
+    <hyperlink ref="O18" r:id="rId13" xr:uid="{62ABAC52-587B-F24B-A5F8-7B2442F7B793}"/>
+    <hyperlink ref="O5" r:id="rId14" xr:uid="{D52B21D2-1870-3445-89FB-CB0DA674EA44}"/>
+    <hyperlink ref="O13" r:id="rId15" xr:uid="{D8745F7E-73C3-0E44-9A2F-869DDF9B58BE}"/>
+    <hyperlink ref="O2" r:id="rId16" xr:uid="{BF38B245-2341-844F-B8CC-942209E9FAE6}"/>
+    <hyperlink ref="O15" r:id="rId17" xr:uid="{9AC937BC-870F-F942-A30D-275F5A55CD28}"/>
+    <hyperlink ref="O23" r:id="rId18" xr:uid="{768E63B1-3426-2A4D-9675-00F8B1DED5D6}"/>
+    <hyperlink ref="O6" r:id="rId19" xr:uid="{4CF68763-A4D3-CE4C-B3CE-EFF4C2E44BBC}"/>
+    <hyperlink ref="O27" r:id="rId20" xr:uid="{043C7281-C851-DA44-896E-785E48CC5BF0}"/>
+    <hyperlink ref="O7" r:id="rId21" xr:uid="{4B25B642-AB57-A948-9F1F-CE9FBB72552A}"/>
+    <hyperlink ref="O25" r:id="rId22" xr:uid="{AE5B19D9-6FD8-3844-B2C3-393DE6E294BD}"/>
+    <hyperlink ref="O20" r:id="rId23" xr:uid="{E503FFD0-0C6D-7B42-A7D3-B2A9369ADC3D}"/>
+    <hyperlink ref="O12" r:id="rId24" xr:uid="{A821D349-5B20-DD4A-87B3-8EEEBCF1591A}"/>
+    <hyperlink ref="O17" r:id="rId25" xr:uid="{E7C42ED7-6B2B-AA49-80AE-7DAB2961A75B}"/>
+    <hyperlink ref="O32" r:id="rId26" xr:uid="{C3D6346C-3B62-6540-93A6-5587E45AA965}"/>
+    <hyperlink ref="O30" r:id="rId27" xr:uid="{4D01A381-BDB6-A043-BB11-176654BE85BB}"/>
+    <hyperlink ref="O8" r:id="rId28" xr:uid="{2F15E816-0090-0D42-BD60-08A4C005B5E7}"/>
+    <hyperlink ref="O4" r:id="rId29" xr:uid="{EE3793CF-C275-6C4E-8397-9C0C5C1B2718}"/>
+    <hyperlink ref="O16" r:id="rId30" xr:uid="{525A1821-814E-E744-AED3-27CE95DA83E3}"/>
+    <hyperlink ref="O3" r:id="rId31" xr:uid="{8846EC74-255C-4548-AB9C-48723A3FAADB}"/>
+    <hyperlink ref="O10" r:id="rId32" xr:uid="{44447FCA-1465-A14C-A316-A7A3FE766D04}"/>
+    <hyperlink ref="O14" r:id="rId33" xr:uid="{D164B1C7-0E17-ED49-B3AA-8194BD8BD4B1}"/>
+    <hyperlink ref="O21" r:id="rId34" xr:uid="{0EBAC3C5-5187-E24E-AD1D-B017F86CAA63}"/>
+    <hyperlink ref="O28" r:id="rId35" xr:uid="{1E1BB8C5-3B47-7D40-9F70-F9CC342E7EF1}"/>
+    <hyperlink ref="G19" r:id="rId36" xr:uid="{9D6FD438-E5D5-F248-A56D-46BB846C99A3}"/>
+    <hyperlink ref="O19" r:id="rId37" xr:uid="{9DAB3A76-1857-A64E-AF97-FAA63B31D43B}"/>
+    <hyperlink ref="O29" r:id="rId38" xr:uid="{8CC8A20F-060B-504C-8AD5-0BDD88A6A5D1}"/>
+    <hyperlink ref="O31" r:id="rId39" xr:uid="{90C029BA-AD4A-B340-B468-A6D6B34352DF}"/>
+    <hyperlink ref="O11" r:id="rId40" xr:uid="{B0DD1CAC-2599-0142-A54A-FA8C4F9EC4F9}"/>
+    <hyperlink ref="O26" r:id="rId41" xr:uid="{72D9B6BC-C8EE-BA42-9E97-1F370FCFEDCA}"/>
+    <hyperlink ref="O33" r:id="rId42" xr:uid="{E551D19A-9F24-9847-AB63-D4E03D19F007}"/>
+    <hyperlink ref="O34" r:id="rId43" xr:uid="{36D428BA-B409-754F-A177-1C0215BA054D}"/>
+    <hyperlink ref="O35" r:id="rId44" xr:uid="{F472CD50-7CE9-C344-972C-6F502714E7F5}"/>
+    <hyperlink ref="O36" r:id="rId45" xr:uid="{C0B647A1-10C5-BA46-B92F-E1F17C6ADC7E}"/>
+    <hyperlink ref="O37" r:id="rId46" xr:uid="{02E2DF65-E6DD-714D-B0DE-019E6AADC004}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId42"/>
+    <tablePart r:id="rId47"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4881,7 +5332,7 @@
               <x14:cfIcon iconSet="3Symbols" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>J2:J1048576</xm:sqref>
+          <xm:sqref>K2:K1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="7" id="{BD05A43E-620D-864A-9EA6-D5EA9243105A}">
@@ -4897,7 +5348,7 @@
               </x14:cfvo>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>M2:M32</xm:sqref>
+          <xm:sqref>N2:N40</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -4907,23 +5358,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D8A0252-737B-6F45-B63E-2E85D75AF59E}">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.83203125" style="6" customWidth="1"/>
     <col min="2" max="2" width="28.1640625" customWidth="1"/>
     <col min="3" max="3" width="22.1640625" customWidth="1"/>
-    <col min="4" max="4" width="18.1640625" customWidth="1"/>
-    <col min="5" max="5" width="50.1640625" customWidth="1"/>
-    <col min="6" max="6" width="29" customWidth="1"/>
-    <col min="7" max="8" width="27" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" style="6"/>
+    <col min="4" max="5" width="18.1640625" customWidth="1"/>
+    <col min="6" max="6" width="50.1640625" customWidth="1"/>
+    <col min="7" max="7" width="29" customWidth="1"/>
+    <col min="8" max="9" width="27" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -4932,854 +5383,934 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>436</v>
+        <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="K1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="K1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C2" s="5">
         <v>2025</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5">
+        <v>3</v>
+      </c>
+      <c r="K2" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="L2" s="5"/>
+    </row>
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="388" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5">
-        <v>3</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="K2" s="5"/>
-    </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" ht="388" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="C3" s="5">
         <v>2025</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5">
+        <v>3</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="L3" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="255" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="B4" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="L4" s="5"/>
+    </row>
+    <row r="5" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2024</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5">
         <v>3</v>
       </c>
-      <c r="J3" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="K5" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="C6" s="5">
         <v>2024</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5">
-        <v>3</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C5" s="5">
-        <v>2023</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5">
-        <v>3</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="372" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C6" s="5">
-        <v>2023</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>91</v>
-      </c>
+      <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>181</v>
+        <v>607</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>584</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
-      <c r="I6" s="5">
-        <v>3</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="K6" s="5"/>
-    </row>
-    <row r="7" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I6" s="5"/>
+      <c r="J6" s="5">
+        <v>2</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="C7" s="5">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>186</v>
+        <v>611</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="5">
+      <c r="I7" s="5"/>
+      <c r="J7" s="5">
+        <v>1</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="L7" s="5"/>
+    </row>
+    <row r="8" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2023</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5">
         <v>3</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="K8" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="372" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2023</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5">
+        <v>3</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="L9" s="5"/>
+    </row>
+    <row r="10" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2023</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5">
+        <v>3</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2023</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>187</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C8" s="5">
-        <v>2021</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5">
-        <v>3</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="C9" s="5">
-        <v>2019</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5">
-        <v>3</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="C10" s="5">
-        <v>2020</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5">
-        <v>3</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="K10" s="5"/>
-    </row>
-    <row r="11" spans="1:11" ht="221" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="C11" s="5">
-        <v>2021</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>323</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
-      <c r="I11" s="5">
-        <v>3</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="289" x14ac:dyDescent="0.2">
+      <c r="I11" s="5"/>
+      <c r="J11" s="5">
+        <v>2</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="C12" s="5">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>212</v>
+        <v>607</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>192</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
-      <c r="I12" s="5">
+      <c r="I12" s="5"/>
+      <c r="J12" s="5">
+        <v>1</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="L12" s="5"/>
+    </row>
+    <row r="13" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2021</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5">
         <v>3</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C13" s="5">
-        <v>2023</v>
-      </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5">
-        <v>2</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="K13" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="221" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>203</v>
+        <v>316</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>204</v>
+        <v>317</v>
       </c>
       <c r="C14" s="5">
         <v>2021</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>205</v>
+        <v>319</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5">
+        <v>3</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="289" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="B15" s="5" t="s">
         <v>207</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5">
-        <v>2</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="K14" s="5"/>
-    </row>
-    <row r="15" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>215</v>
       </c>
       <c r="C15" s="5">
         <v>2021</v>
       </c>
-      <c r="D15" s="5"/>
+      <c r="D15" s="5" t="s">
+        <v>171</v>
+      </c>
       <c r="E15" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+        <v>607</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>209</v>
+      </c>
       <c r="H15" s="5"/>
-      <c r="I15" s="5">
+      <c r="I15" s="5"/>
+      <c r="J15" s="5">
+        <v>3</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2021</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5">
         <v>2</v>
       </c>
-      <c r="J15" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="K15" s="5"/>
-    </row>
-    <row r="16" spans="1:11" ht="340" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="C16" s="5">
-        <v>2019</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5">
-        <v>2</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="K16" s="5"/>
-    </row>
-    <row r="17" spans="1:11" ht="404" x14ac:dyDescent="0.2">
+      <c r="K16" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="L16" s="5"/>
+    </row>
+    <row r="17" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>279</v>
+        <v>211</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>280</v>
+        <v>212</v>
       </c>
       <c r="C17" s="5">
-        <v>2018</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>281</v>
-      </c>
+        <v>2021</v>
+      </c>
+      <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>282</v>
+        <v>607</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
-      <c r="I17" s="5">
+      <c r="I17" s="5"/>
+      <c r="J17" s="5">
         <v>2</v>
       </c>
-      <c r="J17" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="K17" s="5"/>
-    </row>
-    <row r="18" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="K17" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="L17" s="5"/>
+    </row>
+    <row r="18" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C18" s="5">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>300</v>
+        <v>605</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="G18" s="5"/>
+        <v>308</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>309</v>
+      </c>
       <c r="H18" s="5"/>
-      <c r="I18" s="5">
-        <v>2</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="K18" s="5"/>
-    </row>
-    <row r="19" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I18" s="5"/>
+      <c r="J18" s="5">
+        <v>3</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C19" s="5">
         <v>2020</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="G19" s="5"/>
+        <v>605</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>314</v>
+      </c>
       <c r="H19" s="5"/>
-      <c r="I19" s="5">
+      <c r="I19" s="5"/>
+      <c r="J19" s="5">
         <v>2</v>
       </c>
-      <c r="J19" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="255" x14ac:dyDescent="0.2">
+      <c r="K19" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="272" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>157</v>
+        <v>300</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>159</v>
+        <v>304</v>
       </c>
       <c r="C20" s="5">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>22</v>
+        <v>301</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5" t="s">
-        <v>528</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="G20" s="5"/>
       <c r="H20" s="5"/>
-      <c r="I20" s="5">
+      <c r="I20" s="5"/>
+      <c r="J20" s="5">
+        <v>1</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C21" s="5">
+        <v>2019</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5">
+        <v>3</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="340" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C22" s="5">
+        <v>2019</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5">
         <v>2</v>
       </c>
-      <c r="J20" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K20" s="5"/>
-    </row>
-    <row r="21" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>587</v>
-      </c>
-      <c r="C21" s="5">
-        <v>2024</v>
-      </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5" t="s">
-        <v>588</v>
-      </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5">
+      <c r="K22" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="L22" s="5"/>
+    </row>
+    <row r="23" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C23" s="5">
+        <v>2019</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5">
         <v>2</v>
       </c>
-      <c r="J21" s="8" t="s">
-        <v>589</v>
-      </c>
-      <c r="K21" s="5"/>
-    </row>
-    <row r="22" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C22" s="5">
-        <v>2022</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5">
+      <c r="K23" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="L23" s="5"/>
+    </row>
+    <row r="24" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C24" s="5">
+        <v>2019</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5">
         <v>1</v>
       </c>
-      <c r="J22" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="K22" s="5"/>
-    </row>
-    <row r="23" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="C23" s="5">
-        <v>2016</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5">
-        <v>1</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="K23" s="5"/>
-    </row>
-    <row r="24" spans="1:11" ht="404" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="C24" s="5">
-        <v>2018</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5">
-        <v>1</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="K24" s="5"/>
-    </row>
-    <row r="25" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="K24" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="L24" s="5"/>
+    </row>
+    <row r="25" spans="1:12" ht="272" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C25" s="5">
         <v>2019</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>288</v>
+        <v>605</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="G25" s="5"/>
+        <v>291</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>292</v>
+      </c>
       <c r="H25" s="5"/>
-      <c r="I25" s="5">
+      <c r="I25" s="5"/>
+      <c r="J25" s="5">
+        <v>2</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="404" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C26" s="5">
+        <v>2018</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5">
+        <v>2</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="L26" s="5"/>
+    </row>
+    <row r="27" spans="1:12" ht="404" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="C27" s="5">
+        <v>2018</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5">
         <v>1</v>
       </c>
-      <c r="J25" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="K25" s="5"/>
-    </row>
-    <row r="26" spans="1:11" ht="272" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="C26" s="5">
-        <v>2019</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5">
-        <v>2</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="272" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="C27" s="5">
-        <v>2020</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5">
+      <c r="K27" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="L27" s="5"/>
+    </row>
+    <row r="28" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C28" s="5">
+        <v>2016</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5">
         <v>1</v>
       </c>
-      <c r="J27" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="K27" s="5"/>
-    </row>
-    <row r="28" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C28" s="5">
-        <v>2024</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5">
-        <v>1</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="K28" s="5"/>
+      <c r="K28" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="L28" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{41844EDA-E4F4-674C-9A6A-65AB68637379}"/>
-    <hyperlink ref="J2" r:id="rId2" xr:uid="{8DBDFCC8-B058-C743-8BC8-07C2B1FABE92}"/>
-    <hyperlink ref="F3" r:id="rId3" xr:uid="{3DFFFDAA-430C-5B41-977E-F9AED595CBD9}"/>
-    <hyperlink ref="J3" r:id="rId4" xr:uid="{ACBE3EF4-10A1-FB49-AB9A-D2CCFD4875EA}"/>
-    <hyperlink ref="J20" r:id="rId5" xr:uid="{CDB74F28-AE30-A140-9EFE-E3F5AD62DE1A}"/>
-    <hyperlink ref="J28" r:id="rId6" xr:uid="{6E64F81D-4704-7343-9FF8-48A3D30C0423}"/>
-    <hyperlink ref="F4" r:id="rId7" xr:uid="{ED6D0D62-B1B6-6F4F-9813-82054546B603}"/>
-    <hyperlink ref="J4" r:id="rId8" xr:uid="{0EB93E0B-9D46-FC4D-B044-EB430C3C6B68}"/>
-    <hyperlink ref="F5" r:id="rId9" xr:uid="{840A6BB7-DDDD-FE4C-AC68-91A7487ACEED}"/>
-    <hyperlink ref="J5" r:id="rId10" xr:uid="{E0C3C410-4E4F-FA49-AA78-94CC56559C3B}"/>
-    <hyperlink ref="F6" r:id="rId11" xr:uid="{0CD59149-5DC9-614A-8651-CAE436870C27}"/>
-    <hyperlink ref="J6" r:id="rId12" xr:uid="{FC151FBF-3748-174E-B9F5-F31C0EA261F5}"/>
-    <hyperlink ref="F7" r:id="rId13" xr:uid="{E21B0A3F-0C7F-F945-995E-8BAA4A6546AE}"/>
-    <hyperlink ref="J13" r:id="rId14" xr:uid="{63C3D81C-14DE-B044-9202-C3545F877B7F}"/>
-    <hyperlink ref="J22" r:id="rId15" xr:uid="{A71C13AA-855B-854F-B302-2E3B38105D55}"/>
-    <hyperlink ref="F8" r:id="rId16" xr:uid="{3A2199FE-1043-A448-92A5-4BBA80D73A67}"/>
-    <hyperlink ref="J8" r:id="rId17" xr:uid="{282AB198-5BBD-FD42-8933-61F6C0020884}"/>
-    <hyperlink ref="F14" r:id="rId18" xr:uid="{46299554-52D4-554E-83E4-2F3DE791D7E1}"/>
-    <hyperlink ref="J14" r:id="rId19" xr:uid="{1F230988-6ADE-1F45-BCD0-2BDA8EAD6976}"/>
-    <hyperlink ref="F12" r:id="rId20" xr:uid="{5A0D2D79-1B8F-6D4F-B3BE-6A3D4C377BD1}"/>
-    <hyperlink ref="J12" r:id="rId21" xr:uid="{963917D3-4EAD-0247-B9DC-B2FA174E2F0F}"/>
-    <hyperlink ref="J15" r:id="rId22" xr:uid="{7F7608D2-C345-A742-BF17-0ACC05DAB3E7}"/>
-    <hyperlink ref="F16" r:id="rId23" xr:uid="{B1AFA61A-E7E8-EA46-9433-1467FD35BFB9}"/>
-    <hyperlink ref="J16" r:id="rId24" xr:uid="{1A7B98FF-0BEE-F344-8487-8836E8183F32}"/>
-    <hyperlink ref="J9" r:id="rId25" xr:uid="{B9BFEE4D-CD2C-964F-8075-639ACE98DEA8}"/>
-    <hyperlink ref="J23" r:id="rId26" xr:uid="{33662CFF-90E5-7A45-AC52-3E7DE5780F24}"/>
-    <hyperlink ref="F26" r:id="rId27" xr:uid="{E9B74A75-CD90-104E-B944-FC346AD3E6B5}"/>
-    <hyperlink ref="J26" r:id="rId28" xr:uid="{C928932D-30EB-B54C-984F-458D9D21A8C6}"/>
-    <hyperlink ref="J18" r:id="rId29" xr:uid="{B6B2C1F9-07BE-9C43-8640-E4085A454C3A}"/>
-    <hyperlink ref="F10" r:id="rId30" xr:uid="{252FB819-6F2D-6946-933A-DA5ADF1D30D8}"/>
-    <hyperlink ref="J10" r:id="rId31" xr:uid="{01E1A17F-05E2-FF4F-B85D-AC2C67A3C6B8}"/>
-    <hyperlink ref="F19" r:id="rId32" xr:uid="{716164D8-ECA0-7244-B716-6A3FAE16EC4E}"/>
-    <hyperlink ref="J19" r:id="rId33" xr:uid="{F4D9F078-2A3B-8741-B867-39F310AD9484}"/>
-    <hyperlink ref="F11" r:id="rId34" xr:uid="{FF24D29D-7F86-2146-A17A-952B73C620D3}"/>
-    <hyperlink ref="J11" r:id="rId35" xr:uid="{B452A57E-1E2B-5447-9723-6D68D82F4FAF}"/>
-    <hyperlink ref="J25" r:id="rId36" xr:uid="{F76E6AC2-6CFF-534D-9B88-F65432643D98}"/>
-    <hyperlink ref="J21" r:id="rId37" xr:uid="{09BBCFA5-A543-7F4A-91A8-ECB4B8ACBE31}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{41844EDA-E4F4-674C-9A6A-65AB68637379}"/>
+    <hyperlink ref="K2" r:id="rId2" xr:uid="{8DBDFCC8-B058-C743-8BC8-07C2B1FABE92}"/>
+    <hyperlink ref="G3" r:id="rId3" xr:uid="{3DFFFDAA-430C-5B41-977E-F9AED595CBD9}"/>
+    <hyperlink ref="K3" r:id="rId4" xr:uid="{ACBE3EF4-10A1-FB49-AB9A-D2CCFD4875EA}"/>
+    <hyperlink ref="K4" r:id="rId5" xr:uid="{CDB74F28-AE30-A140-9EFE-E3F5AD62DE1A}"/>
+    <hyperlink ref="K7" r:id="rId6" xr:uid="{6E64F81D-4704-7343-9FF8-48A3D30C0423}"/>
+    <hyperlink ref="G5" r:id="rId7" xr:uid="{ED6D0D62-B1B6-6F4F-9813-82054546B603}"/>
+    <hyperlink ref="K5" r:id="rId8" xr:uid="{0EB93E0B-9D46-FC4D-B044-EB430C3C6B68}"/>
+    <hyperlink ref="G8" r:id="rId9" xr:uid="{840A6BB7-DDDD-FE4C-AC68-91A7487ACEED}"/>
+    <hyperlink ref="K8" r:id="rId10" xr:uid="{E0C3C410-4E4F-FA49-AA78-94CC56559C3B}"/>
+    <hyperlink ref="G9" r:id="rId11" xr:uid="{0CD59149-5DC9-614A-8651-CAE436870C27}"/>
+    <hyperlink ref="K9" r:id="rId12" xr:uid="{FC151FBF-3748-174E-B9F5-F31C0EA261F5}"/>
+    <hyperlink ref="G10" r:id="rId13" xr:uid="{E21B0A3F-0C7F-F945-995E-8BAA4A6546AE}"/>
+    <hyperlink ref="K11" r:id="rId14" xr:uid="{63C3D81C-14DE-B044-9202-C3545F877B7F}"/>
+    <hyperlink ref="K12" r:id="rId15" xr:uid="{A71C13AA-855B-854F-B302-2E3B38105D55}"/>
+    <hyperlink ref="G13" r:id="rId16" xr:uid="{3A2199FE-1043-A448-92A5-4BBA80D73A67}"/>
+    <hyperlink ref="K13" r:id="rId17" xr:uid="{282AB198-5BBD-FD42-8933-61F6C0020884}"/>
+    <hyperlink ref="G16" r:id="rId18" xr:uid="{46299554-52D4-554E-83E4-2F3DE791D7E1}"/>
+    <hyperlink ref="K16" r:id="rId19" xr:uid="{1F230988-6ADE-1F45-BCD0-2BDA8EAD6976}"/>
+    <hyperlink ref="G15" r:id="rId20" xr:uid="{5A0D2D79-1B8F-6D4F-B3BE-6A3D4C377BD1}"/>
+    <hyperlink ref="K15" r:id="rId21" xr:uid="{963917D3-4EAD-0247-B9DC-B2FA174E2F0F}"/>
+    <hyperlink ref="K17" r:id="rId22" xr:uid="{7F7608D2-C345-A742-BF17-0ACC05DAB3E7}"/>
+    <hyperlink ref="G22" r:id="rId23" xr:uid="{B1AFA61A-E7E8-EA46-9433-1467FD35BFB9}"/>
+    <hyperlink ref="K22" r:id="rId24" xr:uid="{1A7B98FF-0BEE-F344-8487-8836E8183F32}"/>
+    <hyperlink ref="K21" r:id="rId25" xr:uid="{B9BFEE4D-CD2C-964F-8075-639ACE98DEA8}"/>
+    <hyperlink ref="K28" r:id="rId26" xr:uid="{33662CFF-90E5-7A45-AC52-3E7DE5780F24}"/>
+    <hyperlink ref="G25" r:id="rId27" xr:uid="{E9B74A75-CD90-104E-B944-FC346AD3E6B5}"/>
+    <hyperlink ref="K25" r:id="rId28" xr:uid="{C928932D-30EB-B54C-984F-458D9D21A8C6}"/>
+    <hyperlink ref="K23" r:id="rId29" xr:uid="{B6B2C1F9-07BE-9C43-8640-E4085A454C3A}"/>
+    <hyperlink ref="G18" r:id="rId30" xr:uid="{252FB819-6F2D-6946-933A-DA5ADF1D30D8}"/>
+    <hyperlink ref="K18" r:id="rId31" xr:uid="{01E1A17F-05E2-FF4F-B85D-AC2C67A3C6B8}"/>
+    <hyperlink ref="G19" r:id="rId32" xr:uid="{716164D8-ECA0-7244-B716-6A3FAE16EC4E}"/>
+    <hyperlink ref="K19" r:id="rId33" xr:uid="{F4D9F078-2A3B-8741-B867-39F310AD9484}"/>
+    <hyperlink ref="G14" r:id="rId34" xr:uid="{FF24D29D-7F86-2146-A17A-952B73C620D3}"/>
+    <hyperlink ref="K14" r:id="rId35" xr:uid="{B452A57E-1E2B-5447-9723-6D68D82F4FAF}"/>
+    <hyperlink ref="K24" r:id="rId36" xr:uid="{F76E6AC2-6CFF-534D-9B88-F65432643D98}"/>
+    <hyperlink ref="K6" r:id="rId37" xr:uid="{09BBCFA5-A543-7F4A-91A8-ECB4B8ACBE31}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -5803,7 +6334,7 @@
               </x14:cfvo>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>I2:I28</xm:sqref>
+          <xm:sqref>J2:J28</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -5813,23 +6344,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{536A550C-D311-0C42-8B53-D3917454C963}">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.6640625" customWidth="1"/>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="43.5" customWidth="1"/>
-    <col min="5" max="5" width="38" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" customWidth="1"/>
-    <col min="7" max="7" width="25.5" customWidth="1"/>
-    <col min="8" max="8" width="24.1640625" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="65.1640625" customWidth="1"/>
+    <col min="4" max="5" width="43.5" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" customWidth="1"/>
+    <col min="8" max="8" width="25.5" customWidth="1"/>
+    <col min="9" max="9" width="24.1640625" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="65.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -5838,574 +6369,628 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>436</v>
+        <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="C2" s="5">
+        <v>2023</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5">
+        <v>1</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="L2" s="5"/>
+    </row>
+    <row r="3" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" s="5">
+        <v>2020</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5">
+        <v>2</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="L3" s="5"/>
+    </row>
+    <row r="4" spans="1:12" ht="289" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="C4" s="5">
+        <v>2020</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="L4" s="5"/>
+    </row>
+    <row r="5" spans="1:12" ht="372" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2019</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="L5" s="5"/>
+    </row>
+    <row r="6" spans="1:12" ht="306" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2016</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5">
+        <v>3</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="1:12" ht="306" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="C2" s="5">
-        <v>2020</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5">
+      <c r="C7" s="5">
+        <v>2016</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5">
+        <v>3</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="L7" s="5"/>
+    </row>
+    <row r="8" spans="1:12" ht="356" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2013</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5">
         <v>2</v>
       </c>
-      <c r="J2" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="K2" s="5"/>
-    </row>
-    <row r="3" spans="1:11" ht="372" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="C3" s="5">
-        <v>2019</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5">
+      <c r="K8" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="L8" s="5"/>
+    </row>
+    <row r="9" spans="1:12" ht="255" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2012</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5">
+        <v>1</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="L9" s="5"/>
+    </row>
+    <row r="10" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2011</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5">
+        <v>2</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2011</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5">
+        <v>2</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="1:12" ht="323" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2009</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G12" s="8"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5">
         <v>3</v>
       </c>
-      <c r="J3" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K3" s="5"/>
-    </row>
-    <row r="4" spans="1:11" ht="306" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="C4" s="5">
-        <v>2016</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5">
+      <c r="K12" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="L12" s="5"/>
+    </row>
+    <row r="13" spans="1:12" ht="404" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2009</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5">
         <v>3</v>
       </c>
-      <c r="J4" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="K4" s="5"/>
-    </row>
-    <row r="5" spans="1:11" ht="356" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C5" s="5">
-        <v>2013</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5">
-        <v>2</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="C6" s="5">
-        <v>2011</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5">
-        <v>2</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K6" s="5"/>
-    </row>
-    <row r="7" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="K13" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="L13" s="5"/>
+    </row>
+    <row r="14" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2007</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5">
+        <v>3</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="1:12" ht="238" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2007</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="C7" s="5">
-        <v>2011</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5">
-        <v>2</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="K7" s="5"/>
-    </row>
-    <row r="8" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="E15" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5">
+        <v>3</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="L15" s="5"/>
+    </row>
+    <row r="16" spans="1:12" ht="306" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="C16" s="5">
         <v>2007</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5">
+      <c r="D16" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5">
         <v>3</v>
       </c>
-      <c r="J8" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="K8" s="5"/>
-    </row>
-    <row r="9" spans="1:11" ht="323" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="C9" s="5">
-        <v>2009</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5">
-        <v>3</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="K9" s="5"/>
-    </row>
-    <row r="10" spans="1:11" ht="255" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C10" s="5">
-        <v>2012</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5">
-        <v>1</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="K10" s="5"/>
-    </row>
-    <row r="11" spans="1:11" ht="404" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="C11" s="5">
-        <v>2009</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>493</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5">
-        <v>3</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>494</v>
-      </c>
-      <c r="K11" s="5"/>
-    </row>
-    <row r="12" spans="1:11" ht="238" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="C12" s="5">
-        <v>2007</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>498</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5">
-        <v>3</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>499</v>
-      </c>
-      <c r="K12" s="5"/>
-    </row>
-    <row r="13" spans="1:11" ht="306" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="K16" s="8" t="s">
         <v>501</v>
       </c>
-      <c r="C13" s="5">
-        <v>2007</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>503</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5">
-        <v>3</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>504</v>
-      </c>
-      <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>506</v>
-      </c>
-      <c r="C14" s="5">
-        <v>2023</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>508</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>509</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5">
-        <v>1</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="K14" s="5"/>
-    </row>
-    <row r="15" spans="1:11" ht="306" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>548</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="C15" s="5">
-        <v>2016</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>551</v>
-      </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5">
-        <v>3</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>552</v>
-      </c>
-      <c r="K15" s="5"/>
-    </row>
-    <row r="16" spans="1:11" ht="289" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>557</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="C16" s="27">
-        <v>2020</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>560</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>561</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5">
-        <v>3</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>562</v>
-      </c>
-      <c r="K16" s="5"/>
-    </row>
-    <row r="17" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="L16" s="5"/>
+    </row>
+    <row r="17" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C17" s="5">
         <v>2003</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="5"/>
+        <v>605</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="G17" s="8"/>
       <c r="H17" s="5"/>
-      <c r="I17" s="5">
+      <c r="I17" s="5"/>
+      <c r="J17" s="5">
         <v>2</v>
       </c>
-      <c r="J17" s="8" t="s">
-        <v>585</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="K17" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="C18" s="5">
         <v>1999</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="5"/>
+        <v>605</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="G18" s="8"/>
       <c r="H18" s="5"/>
-      <c r="I18" s="5">
+      <c r="I18" s="5"/>
+      <c r="J18" s="5">
         <v>3</v>
       </c>
-      <c r="J18" s="8" t="s">
-        <v>606</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F19" s="10"/>
-      <c r="J19" s="10"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F20" s="10"/>
-      <c r="J20" s="10"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F21" s="10"/>
-      <c r="J21" s="10"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F22" s="10"/>
-      <c r="J22" s="10"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F23" s="10"/>
-      <c r="J23" s="10"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F24" s="10"/>
-      <c r="J24" s="10"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F25" s="10"/>
-      <c r="J25" s="10"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F26" s="10"/>
-      <c r="J26" s="10"/>
+      <c r="K18" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G19" s="10"/>
+      <c r="K19" s="10"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G20" s="10"/>
+      <c r="K20" s="10"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G21" s="10"/>
+      <c r="K21" s="10"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G22" s="10"/>
+      <c r="K22" s="10"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G23" s="10"/>
+      <c r="K23" s="10"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G24" s="10"/>
+      <c r="K24" s="10"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G25" s="10"/>
+      <c r="K25" s="10"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G26" s="10"/>
+      <c r="K26" s="10"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{5E051D2E-8A51-9C49-98A2-93D6AA6F50D5}"/>
-    <hyperlink ref="J2" r:id="rId2" xr:uid="{9CF25073-F57B-7642-99E2-B110DA9D83A0}"/>
-    <hyperlink ref="J3" r:id="rId3" xr:uid="{FE5DD0B2-EFA3-374F-B812-56B5D85B7730}"/>
-    <hyperlink ref="F4" r:id="rId4" xr:uid="{E7FC474A-99BF-FD41-999E-36632789845F}"/>
-    <hyperlink ref="J4" r:id="rId5" xr:uid="{E47795F3-3710-E945-B85D-1EC2EDE54CA2}"/>
-    <hyperlink ref="J5" r:id="rId6" xr:uid="{9FD08A96-9DCF-A34C-8A82-ED2E36D5619D}"/>
-    <hyperlink ref="F6" r:id="rId7" xr:uid="{8F1A4DDD-1533-7045-B4B7-072CD9399501}"/>
-    <hyperlink ref="J8" r:id="rId8" xr:uid="{DA92A0B6-1132-8646-A395-3D4A59F92847}"/>
-    <hyperlink ref="J9" r:id="rId9" xr:uid="{AA41A86D-AB86-4C45-A9A7-B04B2679C551}"/>
-    <hyperlink ref="J10" r:id="rId10" xr:uid="{3E3C577C-C496-4644-B882-61F1E53BCE42}"/>
-    <hyperlink ref="F11" r:id="rId11" xr:uid="{A92F3E09-F7E4-1F4B-9CA7-29B100FA902A}"/>
-    <hyperlink ref="J11" r:id="rId12" xr:uid="{EAE1E3ED-A19C-0649-8828-A11D59E4D14F}"/>
-    <hyperlink ref="F12" r:id="rId13" xr:uid="{A0F73390-3B9B-CA4E-AE33-25CA94209C38}"/>
-    <hyperlink ref="J12" r:id="rId14" xr:uid="{D3305050-626E-9548-8722-31BBE427C6F9}"/>
-    <hyperlink ref="F13" r:id="rId15" xr:uid="{A7988CAB-5F79-C14A-B19D-1A9DC67ADAAA}"/>
-    <hyperlink ref="J13" r:id="rId16" xr:uid="{7D2EEB1B-5D12-B34A-B4A3-D5FAFB4AF66B}"/>
-    <hyperlink ref="F14" r:id="rId17" xr:uid="{A115D294-6534-5448-92F9-E491FB4AA863}"/>
-    <hyperlink ref="J14" r:id="rId18" xr:uid="{07BD87B6-32BB-D944-829B-131389FE31F1}"/>
-    <hyperlink ref="J15" r:id="rId19" xr:uid="{7A2701BC-C6BA-E94D-8605-C25439B4D5C6}"/>
-    <hyperlink ref="J16" r:id="rId20" xr:uid="{3D75FD6D-F44A-D944-A916-9CD3911CACA9}"/>
-    <hyperlink ref="F16" r:id="rId21" xr:uid="{5DB764C5-C8A2-984F-ADFD-80678C403475}"/>
-    <hyperlink ref="J17" r:id="rId22" xr:uid="{FFC89CFE-9FC1-8A42-B912-A5802A72D8D9}"/>
-    <hyperlink ref="J18" r:id="rId23" xr:uid="{26F94C8D-B49D-2E4B-835F-7091716661F3}"/>
+    <hyperlink ref="G3" r:id="rId1" xr:uid="{5E051D2E-8A51-9C49-98A2-93D6AA6F50D5}"/>
+    <hyperlink ref="K3" r:id="rId2" xr:uid="{9CF25073-F57B-7642-99E2-B110DA9D83A0}"/>
+    <hyperlink ref="K5" r:id="rId3" xr:uid="{FE5DD0B2-EFA3-374F-B812-56B5D85B7730}"/>
+    <hyperlink ref="G6" r:id="rId4" xr:uid="{E7FC474A-99BF-FD41-999E-36632789845F}"/>
+    <hyperlink ref="K6" r:id="rId5" xr:uid="{E47795F3-3710-E945-B85D-1EC2EDE54CA2}"/>
+    <hyperlink ref="K8" r:id="rId6" xr:uid="{9FD08A96-9DCF-A34C-8A82-ED2E36D5619D}"/>
+    <hyperlink ref="G10" r:id="rId7" xr:uid="{8F1A4DDD-1533-7045-B4B7-072CD9399501}"/>
+    <hyperlink ref="K14" r:id="rId8" xr:uid="{DA92A0B6-1132-8646-A395-3D4A59F92847}"/>
+    <hyperlink ref="K12" r:id="rId9" xr:uid="{AA41A86D-AB86-4C45-A9A7-B04B2679C551}"/>
+    <hyperlink ref="K9" r:id="rId10" xr:uid="{3E3C577C-C496-4644-B882-61F1E53BCE42}"/>
+    <hyperlink ref="G13" r:id="rId11" xr:uid="{A92F3E09-F7E4-1F4B-9CA7-29B100FA902A}"/>
+    <hyperlink ref="K13" r:id="rId12" xr:uid="{EAE1E3ED-A19C-0649-8828-A11D59E4D14F}"/>
+    <hyperlink ref="G15" r:id="rId13" xr:uid="{A0F73390-3B9B-CA4E-AE33-25CA94209C38}"/>
+    <hyperlink ref="K15" r:id="rId14" xr:uid="{D3305050-626E-9548-8722-31BBE427C6F9}"/>
+    <hyperlink ref="G16" r:id="rId15" xr:uid="{A7988CAB-5F79-C14A-B19D-1A9DC67ADAAA}"/>
+    <hyperlink ref="K16" r:id="rId16" xr:uid="{7D2EEB1B-5D12-B34A-B4A3-D5FAFB4AF66B}"/>
+    <hyperlink ref="G2" r:id="rId17" xr:uid="{A115D294-6534-5448-92F9-E491FB4AA863}"/>
+    <hyperlink ref="K2" r:id="rId18" xr:uid="{07BD87B6-32BB-D944-829B-131389FE31F1}"/>
+    <hyperlink ref="K7" r:id="rId19" xr:uid="{7A2701BC-C6BA-E94D-8605-C25439B4D5C6}"/>
+    <hyperlink ref="K4" r:id="rId20" xr:uid="{3D75FD6D-F44A-D944-A916-9CD3911CACA9}"/>
+    <hyperlink ref="G4" r:id="rId21" xr:uid="{5DB764C5-C8A2-984F-ADFD-80678C403475}"/>
+    <hyperlink ref="K17" r:id="rId22" xr:uid="{FFC89CFE-9FC1-8A42-B912-A5802A72D8D9}"/>
+    <hyperlink ref="K18" r:id="rId23" xr:uid="{26F94C8D-B49D-2E4B-835F-7091716661F3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -6428,7 +7013,7 @@
               </x14:cfvo>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>I2:I15</xm:sqref>
+          <xm:sqref>J2:J15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="1" id="{0B4F1477-D0B2-8743-8721-49B0CAEE014D}">
@@ -6444,7 +7029,7 @@
               </x14:cfvo>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>I2:I18</xm:sqref>
+          <xm:sqref>J2:J18</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -6454,26 +7039,26 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73C9E597-FF64-4A4E-8508-2E5949A63CAC}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.33203125" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="70.33203125" customWidth="1"/>
-    <col min="6" max="6" width="33" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
-    <col min="9" max="9" width="24.1640625" customWidth="1"/>
-    <col min="10" max="10" width="31.33203125" customWidth="1"/>
-    <col min="11" max="11" width="14.1640625" customWidth="1"/>
-    <col min="12" max="12" width="39.1640625" customWidth="1"/>
+    <col min="4" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="70.33203125" customWidth="1"/>
+    <col min="7" max="7" width="33" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
+    <col min="10" max="10" width="24.1640625" customWidth="1"/>
+    <col min="11" max="11" width="31.33203125" customWidth="1"/>
+    <col min="12" max="12" width="14.1640625" customWidth="1"/>
+    <col min="13" max="13" width="39.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -6482,425 +7067,467 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>436</v>
+        <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="K1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="289" x14ac:dyDescent="0.2">
+      <c r="K1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="306" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="C2" s="5">
+        <v>2019</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5">
+        <v>3</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="L2" s="5"/>
+    </row>
+    <row r="3" spans="1:12" ht="289" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="C3" s="5">
+        <v>2018</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5">
+        <v>3</v>
+      </c>
+      <c r="K3" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="L3" s="5"/>
+    </row>
+    <row r="4" spans="1:12" ht="153" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="C2" s="5">
-        <v>2018</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="F2" s="9" t="s">
+      <c r="B4" s="5" t="s">
         <v>421</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5">
-        <v>3</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="K2" s="5"/>
-    </row>
-    <row r="3" spans="1:11" ht="153" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="C3" s="5">
-        <v>2017</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5">
-        <v>3</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>427</v>
-      </c>
-      <c r="K3" s="5"/>
-    </row>
-    <row r="4" spans="1:11" ht="187" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>430</v>
       </c>
       <c r="C4" s="5">
         <v>2017</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>293</v>
+        <v>245</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>431</v>
-      </c>
-      <c r="G4" s="5"/>
+        <v>605</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>423</v>
+      </c>
       <c r="H4" s="5"/>
-      <c r="I4" s="5">
+      <c r="I4" s="5"/>
+      <c r="J4" s="5">
         <v>3</v>
       </c>
-      <c r="J4" s="8" t="s">
-        <v>432</v>
-      </c>
-      <c r="K4" s="5"/>
-    </row>
-    <row r="5" spans="1:11" ht="221" x14ac:dyDescent="0.2">
+      <c r="K4" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="L4" s="5"/>
+    </row>
+    <row r="5" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="C5" s="5">
         <v>2017</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>66</v>
+        <v>290</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>435</v>
-      </c>
-      <c r="G5" s="5"/>
+        <v>605</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>428</v>
+      </c>
       <c r="H5" s="5"/>
-      <c r="I5" s="5">
+      <c r="I5" s="5"/>
+      <c r="J5" s="5">
         <v>3</v>
       </c>
-      <c r="J5" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" spans="1:11" ht="272" x14ac:dyDescent="0.2">
+      <c r="K5" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="L5" s="5"/>
+    </row>
+    <row r="6" spans="1:12" ht="221" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="C6" s="5">
         <v>2017</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5">
+        <v>3</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="1:12" ht="272" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2017</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5">
+        <v>3</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="L7" s="5"/>
+    </row>
+    <row r="8" spans="1:12" ht="272" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="B8" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5">
+      <c r="C8" s="5">
+        <v>2016</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5">
+        <v>2</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="L8" s="5"/>
+    </row>
+    <row r="9" spans="1:12" ht="306" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2015</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5">
+        <v>2</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="L9" s="5"/>
+    </row>
+    <row r="10" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2014</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5">
         <v>3</v>
       </c>
-      <c r="J6" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="K6" s="5"/>
-    </row>
-    <row r="7" spans="1:11" ht="272" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="C7" s="5">
-        <v>2016</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5">
+      <c r="K10" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2013</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5">
+        <v>3</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="1:12" ht="238" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2004</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="G12" s="8"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5">
+        <v>1</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="L12" s="5"/>
+    </row>
+    <row r="13" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2000</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5">
+        <v>3</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="L13" s="5"/>
+    </row>
+    <row r="14" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1995</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="G14" s="8"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5">
         <v>2</v>
       </c>
-      <c r="J7" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="K7" s="5"/>
-    </row>
-    <row r="8" spans="1:11" ht="306" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C8" s="5">
-        <v>2015</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5">
-        <v>2</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="K8" s="5"/>
-    </row>
-    <row r="9" spans="1:11" ht="221" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="C9" s="5">
-        <v>2014</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5">
-        <v>3</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="K9" s="5"/>
-    </row>
-    <row r="10" spans="1:11" ht="187" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="C10" s="5">
-        <v>2013</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>467</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5">
-        <v>3</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="K10" s="5"/>
-    </row>
-    <row r="11" spans="1:11" ht="238" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="C11" s="5">
-        <v>2004</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5">
-        <v>1</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="K11" s="5"/>
-    </row>
-    <row r="12" spans="1:11" ht="136" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="K14" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="C12" s="5">
-        <v>1995</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5">
-        <v>2</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="K12" s="5"/>
-    </row>
-    <row r="13" spans="1:11" ht="306" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>517</v>
-      </c>
-      <c r="C13" s="5">
-        <v>2019</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>520</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5">
-        <v>3</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" ht="221" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>523</v>
-      </c>
-      <c r="C14" s="5">
-        <v>2000</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5">
-        <v>3</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>527</v>
-      </c>
-      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{88D0A256-582C-1740-B747-81D4B0F163A5}"/>
-    <hyperlink ref="J2" r:id="rId2" xr:uid="{E6D8BD33-A939-1442-8647-C8362C2AE27D}"/>
-    <hyperlink ref="F3" r:id="rId3" xr:uid="{597B4205-BC41-4743-ADE5-DDDF460FB4B7}"/>
-    <hyperlink ref="J3" r:id="rId4" xr:uid="{842691E2-7EAF-EF47-9C1B-F28D37C06B19}"/>
-    <hyperlink ref="F4" r:id="rId5" xr:uid="{4F4C93DD-8A14-504C-BA9A-BC9534951090}"/>
-    <hyperlink ref="J4" r:id="rId6" xr:uid="{6ADE2E15-CB0E-DF46-A93C-351BFA4B368B}"/>
-    <hyperlink ref="J5" r:id="rId7" xr:uid="{B42EE202-E0C0-8F49-A0FB-885D35489A34}"/>
-    <hyperlink ref="J6" r:id="rId8" xr:uid="{E312C5CB-6F1A-6846-AA05-431E8BDFA2E0}"/>
-    <hyperlink ref="J7" r:id="rId9" xr:uid="{0815EEF7-1B85-2E4F-9A10-2CC2EBBED651}"/>
-    <hyperlink ref="F8" r:id="rId10" xr:uid="{C86D56A9-EE17-8F47-89E4-36E2498ADCD9}"/>
-    <hyperlink ref="J8" r:id="rId11" xr:uid="{A1CEB55E-DD0E-8748-A0E3-A961B4426C26}"/>
-    <hyperlink ref="F9" r:id="rId12" xr:uid="{BD0677AD-7D3F-6548-9CAC-1D047233BDC7}"/>
-    <hyperlink ref="J9" r:id="rId13" xr:uid="{9EC1B994-E92F-2644-9484-03A94A752D4E}"/>
-    <hyperlink ref="F10" r:id="rId14" xr:uid="{CB1E753D-EF1E-354F-A5BC-022D1640302F}"/>
-    <hyperlink ref="J10" r:id="rId15" xr:uid="{85B0E369-2637-9540-8B5C-935C11BEDA7D}"/>
-    <hyperlink ref="J11" r:id="rId16" xr:uid="{C78E89F4-1C74-5144-B3E4-107276AF5977}"/>
-    <hyperlink ref="J12" r:id="rId17" xr:uid="{1F03A957-AE7A-2040-9E62-98CFD4C99C88}"/>
-    <hyperlink ref="J13" r:id="rId18" xr:uid="{F1FA5B79-3907-1D4C-A99F-FCBA27E332C6}"/>
-    <hyperlink ref="F14" r:id="rId19" xr:uid="{190FB587-31DD-5246-B8B2-F7EBDAD4FAF4}"/>
-    <hyperlink ref="J14" r:id="rId20" xr:uid="{951AE929-D624-B748-ABFD-9F32EF261D75}"/>
+    <hyperlink ref="G3" r:id="rId1" xr:uid="{88D0A256-582C-1740-B747-81D4B0F163A5}"/>
+    <hyperlink ref="K3" r:id="rId2" xr:uid="{E6D8BD33-A939-1442-8647-C8362C2AE27D}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{597B4205-BC41-4743-ADE5-DDDF460FB4B7}"/>
+    <hyperlink ref="K4" r:id="rId4" xr:uid="{842691E2-7EAF-EF47-9C1B-F28D37C06B19}"/>
+    <hyperlink ref="G5" r:id="rId5" xr:uid="{4F4C93DD-8A14-504C-BA9A-BC9534951090}"/>
+    <hyperlink ref="K5" r:id="rId6" xr:uid="{6ADE2E15-CB0E-DF46-A93C-351BFA4B368B}"/>
+    <hyperlink ref="K6" r:id="rId7" xr:uid="{B42EE202-E0C0-8F49-A0FB-885D35489A34}"/>
+    <hyperlink ref="K7" r:id="rId8" xr:uid="{E312C5CB-6F1A-6846-AA05-431E8BDFA2E0}"/>
+    <hyperlink ref="K8" r:id="rId9" xr:uid="{0815EEF7-1B85-2E4F-9A10-2CC2EBBED651}"/>
+    <hyperlink ref="G9" r:id="rId10" xr:uid="{C86D56A9-EE17-8F47-89E4-36E2498ADCD9}"/>
+    <hyperlink ref="K9" r:id="rId11" xr:uid="{A1CEB55E-DD0E-8748-A0E3-A961B4426C26}"/>
+    <hyperlink ref="G10" r:id="rId12" xr:uid="{BD0677AD-7D3F-6548-9CAC-1D047233BDC7}"/>
+    <hyperlink ref="K10" r:id="rId13" xr:uid="{9EC1B994-E92F-2644-9484-03A94A752D4E}"/>
+    <hyperlink ref="G11" r:id="rId14" xr:uid="{CB1E753D-EF1E-354F-A5BC-022D1640302F}"/>
+    <hyperlink ref="K11" r:id="rId15" xr:uid="{85B0E369-2637-9540-8B5C-935C11BEDA7D}"/>
+    <hyperlink ref="K12" r:id="rId16" xr:uid="{C78E89F4-1C74-5144-B3E4-107276AF5977}"/>
+    <hyperlink ref="K14" r:id="rId17" xr:uid="{1F03A957-AE7A-2040-9E62-98CFD4C99C88}"/>
+    <hyperlink ref="K2" r:id="rId18" xr:uid="{F1FA5B79-3907-1D4C-A99F-FCBA27E332C6}"/>
+    <hyperlink ref="G13" r:id="rId19" xr:uid="{190FB587-31DD-5246-B8B2-F7EBDAD4FAF4}"/>
+    <hyperlink ref="K13" r:id="rId20" xr:uid="{951AE929-D624-B748-ABFD-9F32EF261D75}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -6923,7 +7550,7 @@
               </x14:cfvo>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>I2:I14</xm:sqref>
+          <xm:sqref>J2:J14</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -6933,23 +7560,23 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EB2E9E2-7914-4049-9832-CDEB1A045AD2}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.6640625" customWidth="1"/>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" customWidth="1"/>
-    <col min="5" max="5" width="44.5" customWidth="1"/>
-    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.83203125" customWidth="1"/>
-    <col min="8" max="8" width="26.6640625" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="26.5" customWidth="1"/>
+    <col min="4" max="5" width="35.33203125" customWidth="1"/>
+    <col min="6" max="6" width="44.5" customWidth="1"/>
+    <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.83203125" customWidth="1"/>
+    <col min="9" max="9" width="26.6640625" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="26.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -6958,623 +7585,686 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>436</v>
+        <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="K1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="340" x14ac:dyDescent="0.2">
+      <c r="K1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="340" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C2" s="5">
         <v>2019</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5">
+        <v>3</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="L2" s="5"/>
+    </row>
+    <row r="3" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="C3" s="5">
+        <v>2019</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="G3" s="8"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5">
+        <v>2</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="L3" s="5"/>
+    </row>
+    <row r="4" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="F2" s="9" t="s">
+      <c r="B4" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5">
+      <c r="C4" s="5">
+        <v>2016</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="L4" s="5"/>
+    </row>
+    <row r="5" spans="1:12" ht="372" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2015</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5">
         <v>3</v>
       </c>
-      <c r="J2" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="K2" s="5"/>
-    </row>
-    <row r="3" spans="1:11" ht="238" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="K5" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="L5" s="8"/>
+    </row>
+    <row r="6" spans="1:12" ht="238" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2013</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5">
+        <v>3</v>
+      </c>
+      <c r="K6" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="C3" s="5">
-        <v>2013</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="1:12" ht="356" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="B7" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5">
+      <c r="C7" s="5">
+        <v>2011</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5">
+        <v>2</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="L7" s="5"/>
+    </row>
+    <row r="8" spans="1:12" ht="272" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2010</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5">
         <v>3</v>
       </c>
-      <c r="J3" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="K3" s="5"/>
-    </row>
-    <row r="4" spans="1:11" ht="272" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="C4" s="5">
-        <v>2010</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="K8" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="L8" s="5"/>
+    </row>
+    <row r="9" spans="1:12" ht="356" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="B9" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5">
+      <c r="C9" s="5">
+        <v>2008</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5">
+        <v>2</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="L9" s="5"/>
+    </row>
+    <row r="10" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2007</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5">
         <v>3</v>
       </c>
-      <c r="J4" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="K4" s="5"/>
-    </row>
-    <row r="5" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="C5" s="5">
-        <v>2007</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="K10" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="1:12" ht="272" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="B11" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5">
+      <c r="C11" s="5">
+        <v>2003</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5">
         <v>3</v>
       </c>
-      <c r="J5" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" spans="1:11" ht="272" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="K11" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="1:12" ht="340" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="C6" s="5">
+      <c r="B12" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C12" s="5">
         <v>2003</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5">
+      <c r="D12" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5">
+        <v>2</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="L12" s="5"/>
+    </row>
+    <row r="13" spans="1:12" ht="289" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2002</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5">
         <v>3</v>
       </c>
-      <c r="J6" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="K6" s="5"/>
-    </row>
-    <row r="7" spans="1:11" ht="289" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="K13" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="C7" s="5">
+      <c r="L13" s="5"/>
+    </row>
+    <row r="14" spans="1:12" ht="323" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C14" s="5">
         <v>2002</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="F7" s="8" t="s">
+      <c r="D14" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5">
+      <c r="E14" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="G14" s="8"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5">
         <v>3</v>
       </c>
-      <c r="J7" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="K7" s="5"/>
-    </row>
-    <row r="8" spans="1:11" ht="323" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="K14" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="1:12" ht="289" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2000</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="C8" s="5">
-        <v>2002</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5">
+      <c r="E15" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5">
+        <v>2</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="L15" s="5"/>
+    </row>
+    <row r="16" spans="1:12" ht="404" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1998</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="G16" s="8"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5">
         <v>3</v>
       </c>
-      <c r="J8" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="K8" s="5"/>
-    </row>
-    <row r="9" spans="1:11" ht="404" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="K16" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="C9" s="5">
-        <v>1998</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="L16" s="5"/>
+    </row>
+    <row r="17" spans="1:12" ht="323" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5">
+      <c r="C17" s="5">
+        <v>1997</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5">
         <v>3</v>
       </c>
-      <c r="J9" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="K9" s="5"/>
-    </row>
-    <row r="10" spans="1:11" ht="323" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="K17" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="C10" s="5">
-        <v>1997</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="L17" s="5"/>
+    </row>
+    <row r="18" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1994</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>395</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5">
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5">
         <v>3</v>
       </c>
-      <c r="J10" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="K10" s="5"/>
-    </row>
-    <row r="11" spans="1:11" ht="187" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="C11" s="5">
-        <v>1994</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="K18" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5">
-        <v>3</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>402</v>
-      </c>
-      <c r="K11" s="5"/>
-    </row>
-    <row r="12" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="C12" s="5">
-        <v>1991</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5">
-        <v>3</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>413</v>
-      </c>
-      <c r="K12" s="5"/>
-    </row>
-    <row r="13" spans="1:11" ht="356" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="C13" s="5">
-        <v>1991</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5">
-        <v>3</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="C14" s="5">
-        <v>2016</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5">
-        <v>2</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="K14" s="5"/>
-    </row>
-    <row r="15" spans="1:11" ht="356" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="C15" s="5">
-        <v>2011</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5">
-        <v>2</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="K15" s="5"/>
-    </row>
-    <row r="16" spans="1:11" ht="356" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="C16" s="5">
-        <v>2008</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5">
-        <v>2</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="K16" s="5"/>
-    </row>
-    <row r="17" spans="1:11" ht="340" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="C17" s="5">
-        <v>2003</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5">
-        <v>2</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="K17" s="5"/>
-    </row>
-    <row r="18" spans="1:11" ht="289" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C18" s="5">
-        <v>2000</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5">
-        <v>2</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="K18" s="5"/>
-    </row>
-    <row r="19" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C19" s="5">
         <v>1991</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="G19" s="5"/>
+        <v>605</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>409</v>
+      </c>
       <c r="H19" s="5"/>
-      <c r="I19" s="5">
+      <c r="I19" s="5"/>
+      <c r="J19" s="5">
+        <v>3</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="L19" s="5"/>
+    </row>
+    <row r="20" spans="1:12" ht="356" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="C20" s="5">
+        <v>1991</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="G20" s="8"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5">
+        <v>3</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C21" s="5">
+        <v>1991</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5">
         <v>2</v>
       </c>
-      <c r="J19" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="K19" s="5"/>
-    </row>
-    <row r="20" spans="1:11" ht="372" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>590</v>
-      </c>
-      <c r="C20" s="5">
-        <v>2015</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>591</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>592</v>
-      </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5">
-        <v>3</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>594</v>
-      </c>
-      <c r="K20" s="8"/>
-    </row>
-    <row r="21" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="C21" s="5">
-        <v>2019</v>
-      </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5">
-        <v>2</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>597</v>
-      </c>
-      <c r="K21" s="5"/>
+      <c r="K21" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="L21" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{2854F3D9-80AC-8849-811F-BD8D53B0BC76}"/>
-    <hyperlink ref="J2" r:id="rId2" xr:uid="{553D59FE-CE85-824B-8CD2-A7EC45F552FD}"/>
-    <hyperlink ref="J14" r:id="rId3" xr:uid="{E139180E-F93D-8141-8EB8-2DFA459F9ACE}"/>
-    <hyperlink ref="F3" r:id="rId4" xr:uid="{CF467A60-11A2-2745-B49C-079A47640700}"/>
-    <hyperlink ref="J3" r:id="rId5" xr:uid="{8B97049D-21A7-1140-BF45-75244669C1F1}"/>
-    <hyperlink ref="J15" r:id="rId6" xr:uid="{CC0507EB-B3AB-B14F-AA4A-3615C1EC5D12}"/>
-    <hyperlink ref="F4" r:id="rId7" xr:uid="{014E7580-712A-4144-8B28-B7595E6BD425}"/>
-    <hyperlink ref="J4" r:id="rId8" xr:uid="{1228A3DA-6729-6849-A28A-3CD25AB9FA0F}"/>
-    <hyperlink ref="J16" r:id="rId9" xr:uid="{58E9A66E-E641-D54E-8747-631DE7B861F4}"/>
-    <hyperlink ref="J5" r:id="rId10" xr:uid="{0B23576E-4D66-ED45-831D-B2DFAE0A5451}"/>
-    <hyperlink ref="J6" r:id="rId11" xr:uid="{7271BFC5-B673-384C-823A-A1E8DC399452}"/>
-    <hyperlink ref="J17" r:id="rId12" xr:uid="{76668C5D-3EEA-BE49-BC15-0FE494097270}"/>
-    <hyperlink ref="F17" r:id="rId13" xr:uid="{AC57CE0E-F10A-3246-943C-94919820B202}"/>
-    <hyperlink ref="F7" r:id="rId14" xr:uid="{BE3A31D8-716E-474F-82E1-82E38BE26081}"/>
-    <hyperlink ref="J7" r:id="rId15" xr:uid="{3B8C16B0-EC7D-6B47-85E5-988B4808BC49}"/>
-    <hyperlink ref="J8" r:id="rId16" xr:uid="{379C8021-D2CA-9841-B8CB-D533123CD398}"/>
-    <hyperlink ref="F18" r:id="rId17" tooltip="Persistent link using digital object identifier" xr:uid="{3C0E58DD-1DB5-2947-B4D4-9156DAF2604F}"/>
-    <hyperlink ref="J18" r:id="rId18" xr:uid="{12B86B53-6462-CE4A-9D8A-005E68EABE0E}"/>
-    <hyperlink ref="J9" r:id="rId19" xr:uid="{75458F21-C440-4746-9C5C-E80A758C773C}"/>
-    <hyperlink ref="F10" r:id="rId20" xr:uid="{68DE58B1-856D-4B4B-A434-866020C7E13D}"/>
-    <hyperlink ref="J10" r:id="rId21" xr:uid="{5EA1095B-054C-7B46-8E88-090F7B9D7588}"/>
-    <hyperlink ref="J11" r:id="rId22" xr:uid="{AE4182DB-BAC6-6E4B-AC33-D8036DCE6AC4}"/>
-    <hyperlink ref="F11" r:id="rId23" xr:uid="{C8A308ED-2E3F-5145-B21D-63A39C59489C}"/>
-    <hyperlink ref="F19" r:id="rId24" xr:uid="{D5684DCC-B4D0-2248-B12C-45B14C805EED}"/>
-    <hyperlink ref="J19" r:id="rId25" xr:uid="{50E8034F-FFFB-9347-8FB4-516D91BC6591}"/>
-    <hyperlink ref="J12" r:id="rId26" xr:uid="{E6F13B55-E7D8-5543-8AEF-A003EE9F8211}"/>
-    <hyperlink ref="J13" r:id="rId27" xr:uid="{56802269-BE89-5044-AE4E-AA47286276D3}"/>
-    <hyperlink ref="J20" r:id="rId28" xr:uid="{DB9C9A64-2335-C047-B5FF-3DDAE676E30D}"/>
-    <hyperlink ref="J21" r:id="rId29" xr:uid="{BC0704BB-2184-364F-84E6-AD211FF9A975}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{2854F3D9-80AC-8849-811F-BD8D53B0BC76}"/>
+    <hyperlink ref="K2" r:id="rId2" xr:uid="{553D59FE-CE85-824B-8CD2-A7EC45F552FD}"/>
+    <hyperlink ref="K4" r:id="rId3" xr:uid="{E139180E-F93D-8141-8EB8-2DFA459F9ACE}"/>
+    <hyperlink ref="G6" r:id="rId4" xr:uid="{CF467A60-11A2-2745-B49C-079A47640700}"/>
+    <hyperlink ref="K6" r:id="rId5" xr:uid="{8B97049D-21A7-1140-BF45-75244669C1F1}"/>
+    <hyperlink ref="K7" r:id="rId6" xr:uid="{CC0507EB-B3AB-B14F-AA4A-3615C1EC5D12}"/>
+    <hyperlink ref="G8" r:id="rId7" xr:uid="{014E7580-712A-4144-8B28-B7595E6BD425}"/>
+    <hyperlink ref="K8" r:id="rId8" xr:uid="{1228A3DA-6729-6849-A28A-3CD25AB9FA0F}"/>
+    <hyperlink ref="K9" r:id="rId9" xr:uid="{58E9A66E-E641-D54E-8747-631DE7B861F4}"/>
+    <hyperlink ref="K10" r:id="rId10" xr:uid="{0B23576E-4D66-ED45-831D-B2DFAE0A5451}"/>
+    <hyperlink ref="K11" r:id="rId11" xr:uid="{7271BFC5-B673-384C-823A-A1E8DC399452}"/>
+    <hyperlink ref="K12" r:id="rId12" xr:uid="{76668C5D-3EEA-BE49-BC15-0FE494097270}"/>
+    <hyperlink ref="G12" r:id="rId13" xr:uid="{AC57CE0E-F10A-3246-943C-94919820B202}"/>
+    <hyperlink ref="G13" r:id="rId14" xr:uid="{BE3A31D8-716E-474F-82E1-82E38BE26081}"/>
+    <hyperlink ref="K13" r:id="rId15" xr:uid="{3B8C16B0-EC7D-6B47-85E5-988B4808BC49}"/>
+    <hyperlink ref="K14" r:id="rId16" xr:uid="{379C8021-D2CA-9841-B8CB-D533123CD398}"/>
+    <hyperlink ref="G15" r:id="rId17" tooltip="Persistent link using digital object identifier" xr:uid="{3C0E58DD-1DB5-2947-B4D4-9156DAF2604F}"/>
+    <hyperlink ref="K15" r:id="rId18" xr:uid="{12B86B53-6462-CE4A-9D8A-005E68EABE0E}"/>
+    <hyperlink ref="K16" r:id="rId19" xr:uid="{75458F21-C440-4746-9C5C-E80A758C773C}"/>
+    <hyperlink ref="G17" r:id="rId20" xr:uid="{68DE58B1-856D-4B4B-A434-866020C7E13D}"/>
+    <hyperlink ref="K17" r:id="rId21" xr:uid="{5EA1095B-054C-7B46-8E88-090F7B9D7588}"/>
+    <hyperlink ref="K18" r:id="rId22" xr:uid="{AE4182DB-BAC6-6E4B-AC33-D8036DCE6AC4}"/>
+    <hyperlink ref="G18" r:id="rId23" xr:uid="{C8A308ED-2E3F-5145-B21D-63A39C59489C}"/>
+    <hyperlink ref="G21" r:id="rId24" xr:uid="{D5684DCC-B4D0-2248-B12C-45B14C805EED}"/>
+    <hyperlink ref="K21" r:id="rId25" xr:uid="{50E8034F-FFFB-9347-8FB4-516D91BC6591}"/>
+    <hyperlink ref="K19" r:id="rId26" xr:uid="{E6F13B55-E7D8-5543-8AEF-A003EE9F8211}"/>
+    <hyperlink ref="K20" r:id="rId27" xr:uid="{56802269-BE89-5044-AE4E-AA47286276D3}"/>
+    <hyperlink ref="K5" r:id="rId28" xr:uid="{DB9C9A64-2335-C047-B5FF-3DDAE676E30D}"/>
+    <hyperlink ref="K3" r:id="rId29" xr:uid="{BC0704BB-2184-364F-84E6-AD211FF9A975}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -7597,7 +8287,7 @@
               </x14:cfvo>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>I2:I21</xm:sqref>
+          <xm:sqref>J2:J21</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -7619,7 +8309,7 @@
   <sheetData>
     <row r="2" spans="2:11" ht="27" x14ac:dyDescent="0.35">
       <c r="B2" s="14" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
@@ -7638,31 +8328,31 @@
       <c r="F3" s="13"/>
     </row>
     <row r="4" spans="2:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="B4" s="24" t="s">
-        <v>529</v>
-      </c>
-      <c r="C4" s="25"/>
-      <c r="E4" s="24" t="s">
-        <v>536</v>
-      </c>
-      <c r="F4" s="26"/>
-      <c r="G4" s="25"/>
-      <c r="I4" s="24" t="s">
-        <v>568</v>
-      </c>
-      <c r="J4" s="26"/>
-      <c r="K4" s="29"/>
+      <c r="B4" s="25" t="s">
+        <v>526</v>
+      </c>
+      <c r="C4" s="26"/>
+      <c r="E4" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="F4" s="27"/>
+      <c r="G4" s="26"/>
+      <c r="I4" s="25" t="s">
+        <v>565</v>
+      </c>
+      <c r="J4" s="27"/>
+      <c r="K4" s="24"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="15" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C5" s="16">
         <f>ROWS(Proximity[])</f>
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F5" s="12">
         <f>COUNTIF(Proximity[Relevance],3) + COUNTIF(Success[Relevance],3) + COUNTIF(Support[Relevance],3) + COUNTIF(Ecosystem[Relevance],3) + COUNTIF(Network[Relevance],3)</f>
@@ -7670,74 +8360,74 @@
       </c>
       <c r="G5" s="21">
         <f>F5/$C$10</f>
-        <v>0.5092592592592593</v>
+        <v>0.47413793103448276</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>569</v>
-      </c>
-      <c r="J5" s="30">
+        <v>566</v>
+      </c>
+      <c r="J5" s="12">
         <f>COUNTIF(Proximity[Reviewed?],"DONE") + COUNTIF(Success[Reviewed?],"DONE") + COUNTIF(Support[Reviewed?],"DONE") + COUNTIF(Ecosystem[Reviewed?],"DONE") + COUNTIF(Network[Reviewed?],"DONE")</f>
         <v>29</v>
       </c>
       <c r="K5" s="21">
         <f>J5/$C$10</f>
-        <v>0.26851851851851855</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="15" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C6" s="16">
         <f>ROWS(Success[])</f>
         <v>27</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="F6" s="12">
         <f>COUNTIF(Proximity[Relevance],2) + COUNTIF(Success[Relevance],2) + COUNTIF(Support[Relevance],2) + COUNTIF(Ecosystem[Relevance],2) + COUNTIF(Network[Relevance],2)</f>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G6" s="21">
         <f t="shared" ref="G6:G7" si="0">F6/$C$10</f>
-        <v>0.34259259259259262</v>
+        <v>0.34482758620689657</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="J6" s="22">
         <f>C10-J5</f>
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K6" s="23">
         <f>J6/$C$10</f>
-        <v>0.73148148148148151</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="15" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C7" s="16">
         <f>ROWS(Support[])</f>
         <v>17</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F7" s="22">
         <f>COUNTIF(Proximity[Relevance],1) + COUNTIF(Success[Relevance],1) + COUNTIF(Support[Relevance],1) + COUNTIF(Ecosystem[Relevance],1) + COUNTIF(Network[Relevance],1)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G7" s="23">
         <f t="shared" si="0"/>
-        <v>0.14814814814814814</v>
+        <v>0.15517241379310345</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="15" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C8" s="16">
         <f>ROWS(Ecosystem[])</f>
@@ -7746,7 +8436,7 @@
     </row>
     <row r="9" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="17" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C9" s="18">
         <f>ROWS(Network[])</f>
@@ -7755,11 +8445,11 @@
     </row>
     <row r="10" spans="2:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B10" s="19" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C10" s="20">
         <f>SUM(C5:C9)</f>
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/docs/working_documents/Research_Overview.xlsx
+++ b/docs/working_documents/Research_Overview.xlsx
@@ -8,17 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/janlinzner/Projects/Master-Thesis-Spatial-Proximity-Venture-Capital/docs/working_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DECA84-FB94-A046-A54A-219CA9075CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0720FCB-B29B-8A44-98D7-615E6F8E8ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{AB2802A1-B2D6-D448-8853-2C20DC0DE37E}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="6" xr2:uid="{AB2802A1-B2D6-D448-8853-2C20DC0DE37E}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximity" sheetId="1" r:id="rId1"/>
     <sheet name="Startup-Success" sheetId="2" r:id="rId2"/>
-    <sheet name="VC-Support" sheetId="7" r:id="rId3"/>
-    <sheet name="Ecosystem" sheetId="4" r:id="rId4"/>
-    <sheet name="Startup Network" sheetId="3" r:id="rId5"/>
-    <sheet name="Paper-Analysis" sheetId="8" r:id="rId6"/>
+    <sheet name="Venture Capital" sheetId="9" r:id="rId3"/>
+    <sheet name="Startup-Financing" sheetId="13" r:id="rId4"/>
+    <sheet name="VC Theory" sheetId="11" r:id="rId5"/>
+    <sheet name="VC-Support" sheetId="7" r:id="rId6"/>
+    <sheet name="Ecosystem" sheetId="4" r:id="rId7"/>
+    <sheet name="Startup Network" sheetId="3" r:id="rId8"/>
+    <sheet name="Other" sheetId="12" r:id="rId9"/>
+    <sheet name="Paper-Analysis" sheetId="8" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="933">
   <si>
     <t>Abstract</t>
   </si>
@@ -2036,9 +2040,6 @@
     <t>Philip T. Roundy, Mike Bradshaw, Beverly K. Brockman</t>
   </si>
   <si>
-    <t>https://doi.org/10.1016/j.jbusres.2018.01.032</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1XBKwsb6T7trFlZr3A5efgVvc3uM2wkPd/view?usp=sharing</t>
   </si>
   <si>
@@ -2051,9 +2052,6 @@
     <t>Entrepreneurial ecosystems have emerged as a popular concept to explain the persistence of high–growth entrepreneurship within regions. However, as a theoretical concept ecosystems remain underdeveloped, making it difficult to understand their structure and influence on the entrepreneurship process. The article argues that ecosystems are composed of 10 cultural, social, and material attributes that provide benefits and resources to entrepreneurs and that the relationships between these attributes reproduce the ecosystem. This model is illustrated with case studies of Waterloo, Ontario, and Calgary, Alberta, Canada. The cases demonstrate the variety of different configurations that ecosystems can take.</t>
   </si>
   <si>
-    <t>https://doi.org/10.1111/etap.12167</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/17nnFz6VnjZ9c7Bxcd27dmdmClNFrQ89n/view?usp=sharing</t>
   </si>
   <si>
@@ -2066,9 +2064,6 @@
     <t>Philip T. Roundy, Beverly K. Brockman, Mike Bradshaw</t>
   </si>
   <si>
-    <t>http://dx.doi.org/10.1016/j.jbvi.2017.08.002</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1N2CZGjgplsqyAXublPOIF-aidHtWiooW/view?usp=sharing</t>
   </si>
   <si>
@@ -2076,9 +2071,6 @@
   </si>
   <si>
     <t>Ross Brown, Colin Mason</t>
-  </si>
-  <si>
-    <t>10.1007/s11187-017-9865-7</t>
   </si>
   <si>
     <t>Insights for Thesis</t>
@@ -2107,9 +2099,6 @@
   </si>
   <si>
     <t>In its most abstract sense, an ecosystem is a biotic community, encompassing its physical environment, and all the interactions possible in the complex of living and nonliving components. Economics has always been about systems that explain differential output and outcomes. However, economics has generally ignored the role of entrepreneurship in economic systems, just as entrepreneurship studies have largely overlooked the role of systems in explaining the prevalence and performance of entrepreneurship. The entrepreneurial ecosystem approach has the promise to correct these shortcomings. Its two dominant lineages are the regional development literature and the strategy literature. Both lineages share common roots in ecological systems thinking, providing fresh insights into the interdependence of actors in a particular community to create new value. But studies of both regional development and strategic management have largely ignored the role of entrepreneurs in new value creation. In this paper, we will outline contributions to the entrepreneurial ecosystem approach and conclude with a promising new line of research to our understanding of the emergence, growth, and context of start-ups that have achieved great impact by developing new platforms.</t>
-  </si>
-  <si>
-    <t>10.1007/s11187-017-9864-8</t>
   </si>
   <si>
     <t>https://drive.google.com/file/d/1Zy_KpV2xlRbM-1k1pN4XL5GS6bK5h-kD/view?usp=sharing</t>
@@ -2129,9 +2118,6 @@
     <t>We critically examine how an entrepreneurial ecosystem is structured using an exploratory and bottom-up approach. Past studies in this area have discussed the presence of elements in the system or captured the ecosystem as holistically as possible by extending to social, cultural, and institutional dimension. However, we find that such aggregated conceptualizations gave limited understanding to how different elements are connected and constitute the system. Here, we apply a social network approach by analyzing the connections of the ecosystem at multiple layers: (1) among entrepreneurs, (2) among support organizations, and (3) between and among entrepreneurs and key support organizations. Through a series of interviews with entrepreneurs and support organizations in St. Louis, we find that the ways in which support organizations in this region interacted with each other and with entrepreneurs, including explicit cross-organizational collaboration and strategic structuring of resources, significantly impacted the way that entrepreneurs interacted with one another and with organizations, thus deepening our understanding of these connections and identifying intervening points within the ecosystem.</t>
   </si>
   <si>
-    <t>10.1515/erj-2016-0011</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1wVYe3vYEbGxsldCaZz-8IAR6O4JAkt74/view?usp=sharing</t>
   </si>
   <si>
@@ -2145,9 +2131,6 @@
     <t>Regional policies for entrepreneurship are currently going through a transition from increasing the quantity of entrepreneurship to increasing the quality of entrepreneurship. The next step will be the transition from entrepreneurship policy towards policy for an entrepreneurial economy. The entrepreneurial ecosystem approach has been heralded as a new framework accommodating these transitions. This approach starts with the entrepreneurial actor, but emphasizes the context of productive entrepreneurship. Entrepreneurship is not only the output of the system, entrepreneurs are important players themselves in creating the ecosystem and keeping it healthy. This research briefing reviews the entrepreneurial ecosystem literature and its shortcomings, and provides a novel synthesis. The entrepreneurial ecosystem approach speaks directly to practitioners, but its causal depth and evidence base is rather limited. This article provides a novel synthesis including a causal scheme of how the framework and systemic conditions of the ecosystem lead to particular entrepreneurial activities as output of the ecosystem and new value creation as outcome of the ecosystem. In addition it provides a framework for analysing the interactions between the elements within the ecosystem. This offers a much more rigorous and relevant starting point for subsequent studies into entrepreneurial ecosystems and the regional policy implications of these.</t>
   </si>
   <si>
-    <t>https://doi.org/10.1080/09654313.2015.1061484</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1nwbOQTXG5WK9E6Udi3AsgKi9tQLCWQxg/view?usp=sharing</t>
   </si>
   <si>
@@ -2160,9 +2143,6 @@
     <t>The purpose of this article and the special issue is to improve our understanding of the theoretical, managerial, and policy implications of entrepreneurial innovation. We accomplish this objective by examining the role of context in stimulating such activity, as well as its impact on the outcomes of entrepreneurial innovation. Our analysis begins by outlining an overarching framework for entrepreneurial innovation and context. With reference to this framework we then compare the attributes of national innovation systems, entrepreneurship and entrepreneurial innovation, and categorize contextual influences on entrepreneurial innovation. We then situate the papers presented in this special issue within this framework. We conclude by outlining an agenda for additional research on this topic, focusing on the relationships between contexts and entrepreneurial innovation and then discuss policy implications, focusing on how public and private actors can meet these challenges.</t>
   </si>
   <si>
-    <t>https://doi.org/10.1016/j.respol.2014.01.015</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1M1_S6ltw3eLecq31gQ7Qb_j1fw_oqLvO/view?usp=sharing</t>
   </si>
   <si>
@@ -2176,9 +2156,6 @@
   </si>
   <si>
     <t>This article focuses on entrepreneurship in economic geography and aims at a systematic investigation of regional variation in knowledge-based entrepreneurial activity. We develop and test a three-phase structural model for regional systems of entrepreneurship after introducing a systems approach to entrepreneurship. The model is built upon the absorptive capacity theory of knowledge spillover entrepreneurship that identifies new knowledge as one source of entrepreneurial opportunities and human capital as the major source of entrepreneurial absorptive capacity. Based on data of US metropolitan areas, we find that entrepreneurial absorptive capacity is a critical driving force for knowledge-based entrepreneurial activity. We also find that high technology and cultural diversity contribute to the vibrancy of regional systems of entrepreneurship.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1093/jeg/lbs009</t>
   </si>
   <si>
     <t>https://drive.google.com/file/d/14t2oYkGMjEY4XCgQP5-siUB3SVKkwnEt/view?usp=sharing</t>
@@ -2379,9 +2356,6 @@
     <t>IEEE TRANSACTIONS ON ENGINEERING MANAGEMENT</t>
   </si>
   <si>
-    <t>10.1109/TEM.2018.2859162</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1bN7NcnzegYS8DKxAzsawT0KNJYhw28p5/view?usp=sharing</t>
   </si>
   <si>
@@ -2395,9 +2369,6 @@
   </si>
   <si>
     <t>Economic geography during an era of global competition involves a paradox. It is widely recognized that changes in technology and competition have diminished many of the traditional roles of location. Yet clusters, or geographic concentrations of interconnected companies, are a striking feature of virtually every national, regional, state, and even metropolitan economy, especially in more advanced nations. The prevalence of clusters reveals important insights about the microeconomics of competition and the role of location in competitive advantage. Even as old reasons for clustering have diminished in importance with globalization, new influences of clusters on competition have taken on growing importance in an increasingly complex, knowledge-based, and dynamic economy. Clusters represent a new way of thinking about national, state, and local economies, and they necessitate new roles for companies, government, and other institutions in enhancing competitiveness.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1177/089124240001400105</t>
   </si>
   <si>
     <t>https://drive.google.com/file/d/1vF_D1fSezavrpquaqerCF7XiFK5UQgrO/view?usp=sharing</t>
@@ -2882,12 +2853,1054 @@
 specialization can simultaneously potentiate innovation, and that a multi-scalar approach to the geography of
 entrepreneurship is prudent.</t>
   </si>
+  <si>
+    <t>The Venture Capital Revolution</t>
+  </si>
+  <si>
+    <t>Paul Gompers and Josh Lerner</t>
+  </si>
+  <si>
+    <t>Journal of Economic Perspectives</t>
+  </si>
+  <si>
+    <t>Venture capital has emerged as an important intermediary in financial markets, providing capital to young high-technology firms that might have otherwise gone unfunded. Venture capitalists have developed a variety of mechanisms to overcome the problems that emerge at each stage of the investment process. At the same time, the venture capital process is also subject to various pathologies from time to time, which can create problems for investors or entrepreneurs. This article reviews the recent empirical literature on these organizations and points out area where further research is needed.</t>
+  </si>
+  <si>
+    <t>The structure and governance of venture-capital organizations</t>
+  </si>
+  <si>
+    <t>William A. Sahlman</t>
+  </si>
+  <si>
+    <t>Venture-capital organizations raise money from individuals and institutions for investment in early-stage businesses that offer high potential but high risk. This paper describes and analyzes the structure of venture-capital organizations, focusing on the relationship between investors and venture capitalists and between venture-capital firms and the ventures in which they invest. The agency problems in these organizations and to the contracts and operating procedures that have evolved in response are emphasized. Venture-capital organizations are contrasted with large, publicly traded corporations and with leveraged buyout organizations.</t>
+  </si>
+  <si>
+    <t>When do incumbents learn from entrepreneurial ventures?
+Corporate venture capital and investing firm innovation rates</t>
+  </si>
+  <si>
+    <t>Gary Dushnitsky, Michael J. Lenox</t>
+  </si>
+  <si>
+    <t>In this paper, we focus on the potential innovative benefits to corporate venture capital (CVC), i.e. equity investments in entrepreneurial ventures by incumbent firms. We propose that corporate venture capital programs may be instrumental in harvesting innovations from entrepreneurial ventures and thus an important part of a firm's overall innovation strategy. We hypothesize that these programs are especially effective in weak intellectual property (IP) regimes and when the firm has sufficient absorptive capacity. We analyze a large panel of public firms over a 20-year period and find that increases in corporate venture capital investments are associated with subsequent increases in firm patenting.</t>
+  </si>
+  <si>
+    <t>Venture Capital Governance and Value Added in Four Countries</t>
+  </si>
+  <si>
+    <t>Sophie Manigart, Harry J. Sapienza, Wim Vermeir</t>
+  </si>
+  <si>
+    <t>Research has identified the means by which venture capitalists (VCs) in the United States add value to their portfolio firms beyond money. The venture capital industry has expanded into other nations, and this study explores the relations of venture capitalists with their portfolio firms in the three largest European venture capital markets –- the United Kingdom, France and the Netherlands. Roles for VCs are categorized as strategic (e.g., providing business advice), interpersonal (e.g., mentoring the CEO), and networking (providing links to other resources). Utilizing agency and organization theory perspectives, this study analyzes governance and decision making issues from the viewpoints of the VCs. Perceived risks and uncertainty are hypothesized to increase the level of interaction between CEO and VC, and to increase the value added by such interaction. Interviews and surveys of venture capitalists and the CEOs of their portfolio firms were conducted in the US in 1987-1988. In 1982, a similar questionnaire was administered to VCs in the three European countries. Both similarities and differences were found among the four countries. In the US and the UK, for example, VCs interact more frequently with their portfolio firms, to monitor and assist them, than do those in France and the Netherlands. However, in all four countries VCs rate the greatest value added as strategic, and the least as networking. The situations in which VCs are likely to provide assistance are also</t>
+  </si>
+  <si>
+    <t>Private Equity Performance: Returns,
+Persistence, and Capital Flows</t>
+  </si>
+  <si>
+    <t>Steven Kaplan, Antoinette Schoar</t>
+  </si>
+  <si>
+    <t>This paper investigates the performance of private equity partnerships using a data set of individual fund returns collected by Venture Economics. Over the sample period, average fund returns net of fees approximately equal the S&amp;P 500 although there is a large degree of heterogeneity among fund returns. Returns persist strongly across funds raised by individual private equity partnerships. The returns also improve with partnership experience. Better performing funds are more likely to raise follow-on funds and raise larger funds than funds that perform poorly. This relationship is concave so that top performing funds do not grow proportionally as much as the average fund in the market. At the industry level, we show that market entry in the private equity industry is cyclical. Funds (and partnerships) started in boom times are less likely to raise follow-on funds, suggesting that these funds subsequently perform worse. Aggregate industry returns are lower following a boom, but most of this effect is driven by the poor performance of new entrants, while the returns of established funds are much less affected by these industry cycles. Several of these results differ markedly from those for mutual funds.</t>
+  </si>
+  <si>
+    <t>Thomas Chemmanur, Karthik Krishnan and Debarshi Nandy</t>
+  </si>
+  <si>
+    <t>Do Accelerators Work? If So, How?</t>
+  </si>
+  <si>
+    <t>Hallen et al.</t>
+  </si>
+  <si>
+    <t>Accelerators are entrepreneurial programs that attempt to help ventures learn, often utilizing extensive consultation with mentors, program directors, customers, guest speakers, alumni and peers. While accelerators have rapidly emerged as prominent players in the entrepreneurial ecosystem, entrepreneurs, policy makers, and academics continue to raise questions about their efficacy. Moreover, relevant organizational literature suggests that even if accelerators are associated with better venture outcomes, results could be due to mechanisms other than learning, such as sorting or signaling. Drawing on mixed empirical methods that include proprietary data on the ventures accepted and “almost accepted” to a set of top accelerators, we find evidence that some, but not all, of the early accelerators we study substantially aid and accelerate venture development. We also find some evidence of sorting dynamics. These findings are corroborated using an auxiliary quantitative dataset constructed from publicly observable data. Complementary qualitative fieldwork suggests a key driver of these accelerator effects is a novel learning mechanism we label broad, intensive, and paced consultation. The implication of these insights is that the practices of early accelerators represent a beneficial and likely replicable form of intervention that may also have relevance for independent entrepreneurs, educational programs, and corporate innovation.</t>
+  </si>
+  <si>
+    <t>Venture Capital and the Professionalization of Start-Up Firms: Empirical Evidence</t>
+  </si>
+  <si>
+    <t>Hellmann et. al</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>This paper examines empirical evidence on the impact that venture capitalists can have on the development path of new firms. We use a hand-collected data set on Silicon Valley start-up companies that allows us to "look inside the black box" and analyze the influence of venture capital on the professionalization of firms' internal organization. The evidence suggests that there is a "soft" facet to venture capitalists, in terms of supporting companies to build up their human resources within the organization. Venture capital is also important at the top, in that venture capital backed companies are more likely and faster to bring in outsiders as CEOs. These CEO replacements are often accompanied with the founder departing from the company, suggesting that venture capitalists also exhibit a "hard" facet in terms of exercising control. The paper examines how these various roles are interrelated, and shows how the role of venture capital varies with the state of the company.</t>
+  </si>
+  <si>
+    <t>The Capital Structure Decisions of New Firms</t>
+  </si>
+  <si>
+    <t>Robb &amp; Robinson</t>
+  </si>
+  <si>
+    <t>Review of Financial Studies</t>
+  </si>
+  <si>
+    <t>We study capital structure choices that entrepreneurs make in their firms' initial year of operation, using restricted-access data from the Kauffman Firm Survey. Firms in our data rely heavily on external debt sources, such as bank financing, and less extensively on friends-and-family-based funding sources. Many startups receive debt financed through the personal balance sheets of the entrepreneur, effectively resulting in the entrepreneur holding levered equity claims in their startups. This fact is robust to numerous controls, including credit quality. The reliance on external debt underscores the importance of credit markets for the success of nascent business activity.</t>
+  </si>
+  <si>
+    <t>The economics of small business Finance: The roles of private equity and debt markets in the Financial growth cycle</t>
+  </si>
+  <si>
+    <t>Allen N. Berger, Gregory F. Udell</t>
+  </si>
+  <si>
+    <t>This article examines the economics of financing small business in private equity and debt markets. Firms are viewed through a financial growth cycle paradigm in which different capital structures are optimal at different points in the cycle. We show the sources of small business finance, and how capital structure varies with firm size and age. The interconnectedness of small firm finance is discussed along with the impact of the macroeconomic environment. We also analyze a number of research and policy issues, review the literature, and suggest topics for future research.</t>
+  </si>
+  <si>
+    <t>Assessing the Contribution of Venture Capital to Innovation</t>
+  </si>
+  <si>
+    <t>Samuel Kortum, Josh LernerJosh Lerner</t>
+  </si>
+  <si>
+    <t>RAND Journal of Economics</t>
+  </si>
+  <si>
+    <t>We examine the influence of venture capital on patented inventions in the United States across twenty industries over three decades. We address concerns about causality in several ways, including exploiting a 1979 policy shift that spurred venture capital fundraising. We find that increases in venture capital activity in an industry are associated with significantly higher patenting rates. While the ratio of venture capital to R&amp;D averaged less than 3% from 1983-1992, our estimates suggest that venture capital may have accounted for 8% of industrial innovations in that period.</t>
+  </si>
+  <si>
+    <t>Who are the active investors?
+Evidence from venture capital</t>
+  </si>
+  <si>
+    <t>Laura Bottazzi, Marco Da Rin, Thomas Hellmann</t>
+  </si>
+  <si>
+    <t>This paper examines the determinants and consequences of investor activism in venture capital. Using a hand-collected sample of European venture capital deals, it shows the importance of human capital. Venture capital firms with partners that have prior business experience are more active recruiting managers and directors, helping with fundraising, and interacting more frequently with their portfolio companies. Independent venture capital firms are also more active than ‘captive’ (bank-, corporate-, or government-owned) firms. After controlling for endogeneity, investor activism is shown to be positively related to the success of portfolio companies.</t>
+  </si>
+  <si>
+    <t>The Economics of Private Equity Funds</t>
+  </si>
+  <si>
+    <t>Andrew Metrick, Ayako Yasuda</t>
+  </si>
+  <si>
+    <t>This article analyzes the economics of the private equity industry using a novel model and dataset. We obtain data from a large investor in private equity funds, with detailed records on 238 funds raised between 1993 and 2006. We build a model to estimate the expected revenue to managers as a function of their investor contracts, and we test how this estimated revenue varies across the characteristics of our sample funds. Among our sample funds, about two-thirds of expected revenue comes from fixed-revenue components that are not sensitive to performance. We find sharp differences between venture capital (VC) and buyout (BO) funds. BO managers build on their prior experience by increasing the size of their funds faster than VC managers do. This leads to significantly higher revenue per partner and per professional in later BO funds. The results suggest that the BO business is more scalable than the VC business and that past success has a differential impact on the terms of their future funds.</t>
+  </si>
+  <si>
+    <t>This article examines the representation of venture capitalists on the boards of private firms in their portfolios. If venture capitalists are intensive monitors of managers, their involvement as directors should be more intense when the need for oversight is greater. I show that venture capitalists' representation on the board increases around the time of chief executive officer turnover, while the number of other outsiders remains constant. I also show that distance to the firm is an important determinant of the board membership of venture capitalists, as might be anticipated if the oversight of local firms is less costly than more distant businesses.</t>
+  </si>
+  <si>
+    <t>Josh Lerner</t>
+  </si>
+  <si>
+    <t>Venture Capitalists and the Oversight of Private Firms</t>
+  </si>
+  <si>
+    <t>Government, Venture Capital and the Growth of European High-Tech Entrepreneurial Firms</t>
+  </si>
+  <si>
+    <t>Grilli et al.</t>
+  </si>
+  <si>
+    <t>Using a new European Union-sponsored firm-level longitudinal dataset, we assess the impact of government-managed (GVC) and independent venture capital (IVC) funds on the sales and employee growth of European high-tech entrepreneurial firms. Our results show that the main statistically robust and economically relevant positive effect is exerted by IVC investors on firm sales growth. Conversely, the impact of GVC alone appears to be negligible. We also find a positive and statistically significant impact of syndicated investments by both types of investors on firm sales growth, but only when led by IVC investors. Our results remain stable after controlling for endogeneity, survivorship bias, reverse causality, anticipation effects, legal and institutional differences across countries and over time and are stable with respect to potential non-linear effects of age and size of entrepreneurial firms. Overall, our analysis casts doubt on the ability of governments to support high-tech entrepreneurial firms through a direct and active involvement in VC markets.</t>
+  </si>
+  <si>
+    <t>University spin-out companies and venture capital</t>
+  </si>
+  <si>
+    <t>Wright et al.</t>
+  </si>
+  <si>
+    <t>The creation of university spin-out companies that create wealth is a major policy objective of governments and universities. Finance is a catalyst of this wealth creation yet access to venture capital is a major impediment faced by these companies. In this article we adopt a finance pecking order perspective to examine the problems faced by those university spin-out companies seeking to access venture capital. We triangulate evidence from spin-out companies, university technology transfer offices and venture capital firms in the UK and Continental Europe to identify the problems and to suggest policy developments for these parties as well as government. We compare perceptions of high-tech venture capital firms that invest in spin-outs with those that do not, and also consider VCs’ views on spin-outs versus other high-tech firms. Our evidence identifies a mismatch between the demand and supply side of the market. In line with the pecking order theory, venture capitalists prefer to invest after the seed stage. However, in contrast to the pecking order theory, TTOs see venture capital as more important than internal funds early on. We develop policy implications for universities, technology transfer offices, academic entrepreneurs, venture capital firms and government and suggest areas for further research.</t>
+  </si>
+  <si>
+    <t>On the Life Cycle Dynamics of Venture-Capital- and Non-Venture-Capital-Financed Firms</t>
+  </si>
+  <si>
+    <t>We use data over 25 years to understand the life cycle dynamics of VC- and non-VC-financed firms. We find successful and failed VC-financed firms achieve larger scale but are not more profitable at exit than matched non-VC-financed firms. Cumulative failure rates of VC-financed firms are lower, with the difference driven largely by lower failure rates in the initial years after receiving VC. Our results are not driven by VCs disguising failures as acquisitions or by certain types of VCs. The performance difference between VC- and non-VC-financed firms narrows in the post-internet bubble years, but does not disappear.</t>
+  </si>
+  <si>
+    <t>Venture-Capital Syndication: Improved
+Venture Selection vs. the Value-Added Hypothesis</t>
+  </si>
+  <si>
+    <t>Brander et al.</t>
+  </si>
+  <si>
+    <t>Syndication arises when venture capitalists jointly invest in projects. We model and test two possible reasons for syndication: project selection, as an additional venture capitalist provides an informative second opinion; and complementary management skills of additional venture capitalists. The central question is whether venture capitalists are engaged primarily in selection or in managerial value added. These alternatives imply contrasting predictions about comparative returns to syndicated and standalone investments. Our empirical analysis, using Canadian data, finds that syndicated investments have higher returns, favoring the value‐added interpretation. We also discuss risk sharing and project scale as possible reasons for syndication.</t>
+  </si>
+  <si>
+    <t>A Survey of Venture Capital Research</t>
+  </si>
+  <si>
+    <t>Rin et al.</t>
+  </si>
+  <si>
+    <t>This survey reviews the growing body of academic work on venture capital. It lays out the major data
+sources used. It examines the work on venture capital investments in companies, looking at issues
+of selection, contracting, post-investment services and exits. The survey considers recent work on
+organizational structures of venture capital firms, and the relationship between general and limited
+partners. It discusses the work on the returns to venture capital investments. It also examines public
+policies, and the role of venture capital in the economy at large.</t>
+  </si>
+  <si>
+    <t>Smart Institutions, Foolish Choices? The Limited Partner Performance Puzzle</t>
+  </si>
+  <si>
+    <t>Lerner et al.</t>
+  </si>
+  <si>
+    <t>The returns that institutional investors realize from private equity investments differ dramatically across institutions. Using detailed and hitherto unexplored records of fund investors and performance, we document large heterogeneity in the performance of different classes of limited partners. In particular, endowments' annual returns are nearly 14% greater than average. Funds selected by investment advisors and banks lag sharply. These results are robust to controlling for the type and year of the investment, as well as to the use of different specifications. Analyses of reinvestment decisions and young funds suggest that the results are not primarily due to endowments' greater access to established funds. Finally, we examine the differences in the choice of intermediaries across various institutional investors and their relationship to success. We find that LPs that have higher average IRRs also tend to invest in older funds and have a smaller fraction of GPs in their geographic area, and that the performance of university endowments is correlated with measures of the quality and loyalty of the student body.</t>
+  </si>
+  <si>
+    <t>Governmental and independent venture capital investments in Europe: A firm-level performance analysis</t>
+  </si>
+  <si>
+    <t>Cumming et al.</t>
+  </si>
+  <si>
+    <t>Journal of Corporate Finance</t>
+  </si>
+  <si>
+    <t>This paper examines the impact of government versus private independent venture capital (VC) backing on the exit performance of entrepreneurial firms. Our analyses are based on the VICO dataset, which avoids the coding problems of VC type in the Thompson Financial SDC dataset. The data indicate that private independent VC-backed companies have better exit performance than government-backed companies. Mixed-syndicates of private-independent and governmental VC investors give rise to a higher (but not statistically different) likelihood of positive exits than that of IVC-backing. Our findings are not influenced by the composition of the syndicate in terms of size and institutional heterogeneity. Our results remain stable after controlling for endogeneity concerns, selection bias, omitted variable bias, legal and institutional differences across countries and over time through several econometric techniques. Moreover, our results are not driven by: i) the holding period of the different types of VC investors; ii) the potential signaling effect of GVC towards IVC investors; iii) the firm's financial structure and net cash-flow ratio; iv) the investment stage; and v) the distance between the VC investor and the target company.</t>
+  </si>
+  <si>
+    <t>Does governmental venture capital spur invention and innovation?
+Evidence from young European biotech companies</t>
+  </si>
+  <si>
+    <t>Fabio Bertoni, Tereza Tykvová</t>
+  </si>
+  <si>
+    <t>This paper explores whether and how governmental venture capital investors (GVCs) spur invention and
+innovation in young biotech companies in Europe. To gauge invention we focus on the simple patent stock
+at the company level, while innovation is proxied by the citation-weighted patent stock. Our findings
+indicate that GVCs, as stand-alone investors, have no impact on invention and innovation. However, GVCs
+boost the impact of independent venture capital investors (IVCs) on both invention and innovation. We
+conclude that GVCs are an ineffective substitute, but an effective complement, of IVCs. We also distinguish
+between technology-oriented GVCs (TVCs) and development-oriented GVCs (DVCs). We find that DVCs
+are better at increasing firm’s inventions, and that TVCs, combined with IVCs, support innovations.</t>
+  </si>
+  <si>
+    <t>Cost of Experimentation and the Evolution of Venture Capital</t>
+  </si>
+  <si>
+    <t>Michael Ewens, Ramana Nanda, Matthew Rhodes-Kropf</t>
+  </si>
+  <si>
+    <t>We study how technological shocks to the cost of starting new businesses have led the venture capital model to adapt in fundamental ways over the prior decade. We both document and provide a framework to understand the changes in the investment strategy of VCs in recent years—an increased prevalence of a "spray and pray" investment approach—where investors provide a little funding and limited governance to an increased number of startups that they are more likely to abandon, but where initial experiments significantly inform beliefs about the future potential of the venture. This adaptation and related entry by new financial intermediaries has led to a disproportionate rise in innovations where information on future prospects is revealed quickly and cheaply and has reduced the relative share of innovation in complex technologies where initial experiments cost more and reveal less.</t>
+  </si>
+  <si>
+    <t>The financial and innovation literature generally claims that venture capital (VC) investments spur the growth of new technology-based firms (NTBFs). However, it has proved difficult so far to separate the “treatment” effect of the VC investment from the “selection” effect attributable to the ability of the VC investor to screen high growth NTBFs. The aim of this work is to test whether VC investments have a positive treatment effect on the growth of employment and sales of NTBFs. For this purpose we consider a 10-year longitudinal data set for 538 Italian NTBFs, most of which are privately held. The sample includes both VC-backed and non-VC-backed firms. We estimate Gibrat-law-type dynamic panel-data models augmented with time-varying variables that capture the VC status of firms. To control for the endogeneity of VC investments we use several GMM estimators. The econometric results strongly support the view that VC investments positively influence firm growth. The treatment effect of VC investments is of large economic magnitude, especially on growth of employment. Most of it is obtained immediately after the first round of VC finance. Conversely, the selection effect of VC appears to be negligible in the Italian context.</t>
+  </si>
+  <si>
+    <t>Venture Capitalists as Principals:
+Contracting, Screening, and Monitoring</t>
+  </si>
+  <si>
+    <t>Kaplan, Strömberg</t>
+  </si>
+  <si>
+    <t>The American Economic Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Picking winners or building them? Alliance, intellectual, and human capital as selection criteria in venture financing and performance of biotechnology startups
+</t>
+  </si>
+  <si>
+    <t>Joel A. C. Baum and Brian Silverman</t>
+  </si>
+  <si>
+    <t>In the entrepreneurial setting, financial intermediaries such as venture capital firms (VCs) are perhaps the dominant source of selection shaping the environment within which new ventures evolve. VCs affect selection both by acting as a “scout” able to identify future potential and as a “coach” that can help realize it. Despite the large literature on the role of VCs in encouraging startups, it is generally taken for granted that VCs are expert scouts and coaches, and so the ways in which VCs actually enhance startup performance are not well understood. In this study, we examine whether VCs' emphasize picking winners or building them by comparing the effects of startups' alliance, intellectual, and human capital characteristics on VCs decisions to finance them with the effects of the same characteristics on future startup performance. Our findings point to a joint logic that combines the roles: VCs finance startups that have strong technology, but are at risk of failure in the short run, and so in need of management expertise. Our findings thus support the belief in VC expertise, but only to a point. VCs also appear to make a common attribution error overemphasizing startups' human capital when making their investment decisions.</t>
+  </si>
+  <si>
+    <t>Venture capital and the structure of capital markets: banks versus stock markets</t>
+  </si>
+  <si>
+    <t>Bernard S. Black, Ronald J. Gilson</t>
+  </si>
+  <si>
+    <t>The United States has many banks that are small relative to large corporations and play a limited role in corporate governance, and a well developed stock market with an associated market for corporate control. In contrast, Japanese and German banks are fewer in number but larger in relative size and are said to play a central governance role. Neither country has an active market for corporate control. We extend the debate on the relative efficiency of bank- and stock market-centered capital markets by developing a further systematic difference between the two systems: the greater vitality of venture capital in stock market-centered systems. Understanding the link between the stock market and the venture capital market requires understanding the contractual arrangements between entrepreneurs and venture capital providers; especially the importance of the opportunity to enter into an implicit contract over control, which gives a successful entrepreneur the option to reacquire control from the venture capitalist by using an initial public offering as the means by which the venture capitalist exits from a portfolio investment. We also extend the literature on venture capital contracting by offering an explanation for two central characteristics of the U.S. venture capital market: relatively rapid exit by venture capital providers from investments in portfolio companies; and the common practice of exit through an initial public offering.</t>
+  </si>
+  <si>
+    <t>Topic</t>
+  </si>
+  <si>
+    <t>VC Definition</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1x7TPGUYJZvusQiaEHf_MDwyAcoRywF5e/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1x0NasR-C_VSLF0kkhVwG-pC5KLVDqC4T/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1OjIRoo-cfLL96ISyWiXSs5CAsV6l7G0A/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/133tpogdzEUkIgdg4dLBeTMGew9jj_aSG/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1pcKvf4HImgv0yp3B_-86WXHBzY6XRADT/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/11Ewjm_jCWvI80VcYqi2rlPOrPTRacMwO/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1M4lRPg6cGzatBwHlxGE4WeJavcikDTzl/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zBZFBqhRKmC645leGwSTZd-d-mULkzO9/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hGQ08AnSgtjz-722qNIRnAxvBFtVgEdS/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12cCvttChNIlwbvU8CvWDEBk1hEs8ey9h/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/17mJn82p85umQ6y3nn64Ghujjm5vuUojY/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1KrnBg3G3phFEhMcfe_Xnzj1KDgNoFkdf/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1r2V5OXMV0ymTkig7H2Lx_KMT9x2gUzwP/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1uzVN6JfixKkV0ijz4VKtcG0rJQYBtyV9/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1LKarmexvREvtjzXnLrZ2DF0osQ6pSHdv/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Q6FxlgiC0PFdmxjgzK66J21zPziK-EL-/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1n0MSxPPLaJb5cof8MvpyWeXkqHEWLsrH/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1kmuEFzulN45nJsv-SelxpA266JzVAQmU/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1-yahtqQICadbjBXLzg_wxdvuNJ79_AfG/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bA2zF3tVg2AuSwexskVBZK0c18FR3wcO/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ZzgIDs5T46Hot_9zwZJx6qXJtq-GGjeq/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1XSPwPwtW2ozBMMj4N-HeC0MUCIjMNyL9/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1dyZnazFGfJJqEBdFvJ2f5mHp5nMqdjCj/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1eai53VQTeognW4EkzYGtbSsJxmWHgX6l/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Jo8l5aZDB1CUuJ4Xn1kzugJ_kuPcBYRw/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jQEz1YvfKn9b7pdkGV_n2LnA36dLN7f8/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>Entrepreneurial Ability, Venture Investments, and Risk Sharing</t>
+  </si>
+  <si>
+    <t>Information Asymmetry / Agency Theory</t>
+  </si>
+  <si>
+    <t>Raphael Amit, Lawrence Glosten and Eitan Muller</t>
+  </si>
+  <si>
+    <t>A number of issues that relate to the desirability and implications of new venture financing are examined within a principal-agent framework that captures the essence of the relationship between entrepreneurs and venture capitalists. The model suggests: (1) As long as the skill levels of entrepreneurs are common knowledge, all will choose to involve venture capital investors, since the risk sharing provided by outside participation dominates the agency relationship that is created. (2) The less able entrepreneurs will choose to involve venture capitalists, whereas the more profitable ventures will be developed without external participation because of the adverse selection problem associated with asymmetric information. (3) If a costly signal is available that conveys the entrepreneur's ability, some entrepreneurs will invest in such a signal and then sell to investors; these entrepreneurs, however, need not be the more able ones. The implications for new venture financing of these and other findings are discussed and illustrated by example.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ntWPbfc11lrQ4N8Bt6S3lkYfVB8hiIJp/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>A Model of Venture Capitalist Investment Activity</t>
+  </si>
+  <si>
+    <t>Tyzoon T. Tyebjee and Albert V. Bruno</t>
+  </si>
+  <si>
+    <t>The paper describes the activities of venture capitalists as an orderly process involving five sequential steps. These are (1) Deal Origination: The processes by which deals enter into consideration as investment prospects, (2) Deal Screening: A delineation of key policy variables which delimit investment prospects to a manageable few for in-depth evaluation, (3) Deal Evaluation: The assessment of perceived risk and expected return on the basis of a weighting of several characteristics of the prospective venture and the decision whether or not to invest as determined by the relative levels of perceived risk and expected return, (4) Deal Structuring: The negotiation of the price of the deal, namely the equity relinquished to the investor, and the covenants which limit the risk of the investor, (5) Post-Investment Activities: The assistance to the venture in the areas of recruiting key executives, strategic planning, locating expansion financing, and orchestrating a merger, acquisition or public offering. 41 venture capitalists provided data on a total of 90 deals which had received serious consideration in their firms. The questionnaire measured the mechanism of initial contact between venture capitalist and entrepreneur, the venture's industry, the stage of financing and product development, ratings of the venture on 23 characteristics, an assessment of the potential return and perceived risk, and the decision vis-à-vis whether to invest. The modal venture represented in the database was a start-up in the electronics industry with a production capability in place and seeking $1 million (median) in outside financing. There is a high degree of cross-referrals between venture capitalists, particularly for the purposes of locating co-investors. Factor analysis reduced the 23 characteristics of the deal to five underlying dimensions namely (1) Market Attractiveness (size, growth, and access to customers), (2) Product Differentiation (uniqueness, patents, technical edge, profit margin), (3) Managerial Capabilities (skills in marketing, management, finance and the references of the entrepreneur), (4) Environmental Threat Resistance (technology life cycle, barriers to competitive entry, insensitivity to business cycles and down-side risk protection), (5) Cash-Out Potential (future opportunities to realize capital gains by merger, acquisition or public offering). The results of regression analyses showed expected return to be determined by Market Attractiveness and Product Differentiation (R2 = 0.22). Perceived risk is determined by Managerial Capabilities and Environmental Threat Resistance (R2 = 0.33). Finally, a discriminant analysis correctly predicted, in 89.4% of the cases, whether or not a venture capitalist was willing to commit funds to the deal on the basis of the expected return and perceived risk. The reactions of seven venture capitalists who reviewed the model's specification were used to test its validit</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1CzlHnkAmQ94GIf4-xeWnAsl1SIeAUOUy/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>On the Positive Role of Financial Intermediation in Allocation of Venture Capital in a Market with Imperfect Information</t>
+  </si>
+  <si>
+    <t>Yuk-Shee Chan</t>
+  </si>
+  <si>
+    <t>This paper develops a theory of financial intermediation that highlights the contribution of intermediaries as informed agents in a market with imperfect information. We consider a venture capital market where the entrepreneurs select the qualities of projects and their perquisite consumptions, about which the investors are imperfectly informed. It is shown that when all investors have positive search costs, the entrepreneurs are induced to offer the unacceptable inferior projects ("lemons" only), and the investors will not enter the venture capital market, but put their funds in other low return investments--an undesirable allocation of resources. Beginning with an initial undesirable situation, the financial intermediaries may evolve as informed agents that induce a Pareto-preferred allocation, leading the investors to a higher welfare state. We focus our analysis on the existence of intermediation equilibra when the market for intermediation services is competitive. The distribution of returns on projects, the fees charged by intermediaries, and the fraction of institutional holdings are all endogenous in equilibrium. It is shown that (i) there cannot be a competitive intermediation equilibrium with very high institutional holdings, and (ii) in other cases multiple equilibra may exist, but the one with the highest institutional holdings dominates the others in a Pareto sense.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1I-IGLAVVEpf1UPNGpbtWXrXdLZwBhoZy/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Credit Rationing in Markets with Imperfect Information</t>
+  </si>
+  <si>
+    <t>Joseph E. Stiglitz, Andrew Weiss</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/19M8GRggDqahIv69JeCgGfkrz15C3ESE_/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>The Market for "Lemons": Quality Uncertainty and the Market Mechanism</t>
+  </si>
+  <si>
+    <t>George A. Akerlof</t>
+  </si>
+  <si>
+    <t>The Quarterly Journal of Economics</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1A-RtoLtxQ8ONMNbBeneHI7zKwHBCegyd/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>Corporate Financing and Investment Decisions when firms have information that investors dont have</t>
+  </si>
+  <si>
+    <t>Myers, Mayluf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Financial Economics </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1stSa9uYN9yvNC98BStmlsOdzbphLyjyF/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>Theory of the firm: Managerial behavior, agency costs and ownership structure</t>
+  </si>
+  <si>
+    <t>Jensen/Meckling</t>
+  </si>
+  <si>
+    <t>This paper integrates elements from the theory of agency, the theory of property rights and the theory of finance to develop a theory of the ownership structure of the firm. We define the concept of agency costs, show its relationship to the ‘separation and control’ issue, investigate the nature of the agency costs generated by the existence of debt and outside equity, demonstrate who bears these costs and why, and investigate the Pareto optimality of their existence. We also provide a new definition of the firm, and show how our analysis of the factors influencing the creation and issuance of debt and equity claims is a special case of the supply side of the completeness of markets problem.
+The directors of such [joint-stock] companies, however, being the managers rather of other people's money than of their own, it cannot well be expected, that they should watch over it with the same anxious vigilance with which the partners in a private copartnery frequently watch over their own. Like the stewards of a rich man, they are apt to consider attention to small matters as not for their master's honour, and very easily give themselves a dispensation from having it. Negligence and profusion, therefore, must always prevail, more or less, in the management of the affairs of such a company.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1G5zsARZKs0j6n9Jq9iQl85Y8tQkctLIL/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>Agency Problems and the Theory of the Firm</t>
+  </si>
+  <si>
+    <t>Fama</t>
+  </si>
+  <si>
+    <t>The Journal of Political Economy</t>
+  </si>
+  <si>
+    <t>This paper attempts to explain how the separation of security ownership and control, typical of large corporations, can be an efficient form of economic organization. We first set aside the presumption that a corporation has owners in any meaningful sense. The entrepreneur is also laid to rest, at least for the purposes of the large modern corporation. The two functions usually attributed to the entrepreneur--management and risk bearing--are treated as naturally separate factors within the set of contracts called a firm. The firm is disciplined by competition from other firms, which forces the evolution of devides for efficiently monitoring the performance of the entire team and of its individual members. Individual participants in the firm, and in particular its managers, face both the discipline and opportunities provided by the markets for their services, both within and outside the firm.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/11xKafqIsfuP1Sch7WTT_RNZ9ufTUWAOV/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1K3CubNtxVwSFKRx3XqUbQqGaigVd71f1/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>The role of imperfect information in a principal-agent relationship subject to moral hazard is considered. A necessary and sufficient condition for imperfect information to improve on contracts based on the payoff alone is derived, and a characterization of the optimal use of such information is given.</t>
+  </si>
+  <si>
+    <t>Holmstrom</t>
+  </si>
+  <si>
+    <t>Moral Hazard and Observability</t>
+  </si>
+  <si>
+    <t>Financial Contracting Theory Meets
+the Real World: An Empirical
+Analysis of Venture Capital
+Contracts</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hoke52b67v79Q_1nyFc0ykhOM1Ej8Snw/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>We compare the characteristics of real-world financial contracts to their counterparts in financial
+contracting theory. We do so by studying the actual contracts between venture capitalists (VCs) and
+entrepreneurs. The distinguishing characteristic of VC financings is that they allow VCs to separately
+allocate cash flow rights, board rights, voting rights, liquidation rights, and other control rights. We
+describe and measure these rights. We then interpret our results in relation to existing financial contracting
+theories. We also describe the interrelation and the evolution across financing rounds of the different rights.</t>
+  </si>
+  <si>
+    <t>The Bell Journal of Economcis</t>
+  </si>
+  <si>
+    <t>Review of Economic Studies</t>
+  </si>
+  <si>
+    <t>Firm Resources and Sustained Competitive Advantage</t>
+  </si>
+  <si>
+    <t>Barney</t>
+  </si>
+  <si>
+    <t>Resource Based View</t>
+  </si>
+  <si>
+    <t>Journal of Management</t>
+  </si>
+  <si>
+    <t>Understanding sources of sustained competitive advantage has become a major area of research in strategic management. Building on the assumptions that strategic resources are heterogeneously distributed acrossfirms and that these differences are stable over time, this article examines the link betweenfirm resources and sustained competitive advantage. Four empirical indicators of the potential of firm resources to generate sustained competitive advantage-value, rareness, imitability, and substitutability-are discussed. The model is applied by analyzing the potential of severalfirm resourcesfor generating sustained competitive advantages. The article concludes by examining implications of this firm resource model of sustained competitive advantage for other business disciplines.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1r-dKyhj4ErXhGBNC8BQx1oUKNFEobnqV/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>A Resource-Based View of the Firm</t>
+  </si>
+  <si>
+    <t>Birger Wernerfelt</t>
+  </si>
+  <si>
+    <t>The paper explores the usefulness of analysing firms from the resource side rather than from the product side. In analogy to entry barriers and growth-share matrices, the concepts of resource position barrier and resource-product matrices are suggested. These tools are then used to highlight the new strategic options which naturally emerge from the resource perspective.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1vmgXDtvNGHt-ShyDCCqSkVXHLRxb-LZW/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>The Cornerstones of Competitive Advantage: A Resource-Based View</t>
+  </si>
+  <si>
+    <t>Margaret A. Peteraf</t>
+  </si>
+  <si>
+    <t>This paper elucidates the underlying economics of the resource-based view of competitive advantage and integrates existing perspectives into a parsimonious model of resources and firm performance. The essence of this model is that four conditions underlie sustained competitive advantage, all of which must be met. These include superior resources (heterogeneity within an industry), ex post limits to competition, imperfect resource mobility, and ex ante limits to competition. In the concluding section, applications of the model for both single business strategy and corporate strategy are discussed.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1PQowaHJquefgCoqCqsV2gtqMcMwzIA6i/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>How Entrepreneurial Firms Can Benefit from Alliances with Large Partners</t>
+  </si>
+  <si>
+    <t>Sharon A. Alvarez and Jay B. Barney</t>
+  </si>
+  <si>
+    <t>The Academy of Management Executive</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1WoACRLC9AcliBaYMwHX1yAJL1iPgWANI/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>This paper uses a case study methodology to develop a model of the venture capital investment decision-making process. It identifies generic criteria that venture capitalists use. A six-stage process model is proposed: origination, venture capital firm-specific screen, generic screen, first-phase evaluation, second-phase evaluation, and closing. Different activities occur in each stage. It is argued that the venture capitalist provides both supply-side and demand-side benefits to the market.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1OprQQVpgCVFySJ_yzVzSlOeaVJlhHEu5/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>The potential of actuarial decision models: Can they improve the venture capital investment decision?</t>
+  </si>
+  <si>
+    <t>Andrew L. Zacharakis,
+G. Dale Meyer</t>
+  </si>
+  <si>
+    <t>Venture capitalists (VCs) are considered experts in identifying high-potential new ventures—gazelles. VC-backed ventures survive at a much higher rate than those ventures backed by other sources Kunkel and Hofer 1991, Sandberg 1986, Timmons 1994. Thus, the VC decision process has received tremendous attention within the entrepreneurship literature. Nonetheless, VC-backed firms still fail at a surprisingly high rate (20%). Moreover, another 20% of the VC's portfolio fails to provide any return to the VC. Therefore, there is room for improvement in the VC investment process.
+The three staged investment process often begins with venture screening. First, VCs screen the hundreds of proposals they receive to assess which deserve further consideration. Those ventures that survive the initial stage are then subjected to extensive due diligence. Finally, the VC and entrepreneur negotiate terms of the investment. Considering the amount of time that due diligence and negotiation of terms may take, it is imperative that VCs minimize their efforts during screening so that only those ventures with the most potential proceed to the next stage. Yet, at the same time, the screening process should also be careful not to eliminate gazelles prematurely. VCs are in a quandary. How can they efficiently screen venture proposals without unduly rejecting high potential investments? The answer may be to use actuarial decision aides to assist in the screening process.
+Actuarial decision aides are models that decompose a decision into component parts (or cues) and recombine those cues to predict the potential outcome. For example, an actuarial model about the VC decision might decompose a venture proposal into decisions about the entrepreneurial team, the product, the market, etc. The sub-component decisions are than recombined to reach an overall assessment of the venture's potential. Such models have been developed in a number of decision domains (e.g., bank lending, psychological evaluations, etc.) and been found to be very robust. Specifically, these models often outperform the very experts that they are meant to mimic.
+The current study had 53 practicing VCs participate in a policy capturing experiment. The participants examined 50 ventures and judged each venture's success potential; would the venture ultimately succeed or fail. Likewise, identical information about each venture was input into two different types of actuarial models. One actuarial model—a bootstrap model—used information factors that VCs had identified as being most important to making a good investment decision. The second actuarial model was derived by Roure and Keeley (1990). The Roure and Keeley model best distinguished between success and failure in a study of 36 high-technology ventures. The bootstrap model outperformed all but one participating VC (he achieved the same accuracy rate as the bootstrap model). The Roure and Keely model, although less successful than the bootstrap model, outperformed over half of the participating VCs.
+The implications of this study are that properly developed actuarial models may be successful screening decision aides. The success of the actuarial models may be attributed to their consistency across different proposals and time. The models always weight the information cues the same. VCs, as are all human decision makers, may often be biased by differing salient information cues that cause them to misinterpret or ignore other important cues. For example, a VC may overlook product weaknesses if (s)he is familiar with the entrepreneur putting forth a particular proposal. Although the current study developed a generalized actuarial model, each VC firm could create screening models that fit it's particular decision criteria. The models could then be used by junior associates or lower level employees to perform an initial screen of received venture proposals thereby freeing senior associates' time.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FZrFpT5X_m9gqZV0S3kNzUKlLjCRNM8_/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>A questionnaire was administered to one hundred venture capitalists to determine the most important criteria that they use to decide on funding new ventures. Perhaps the most important finding from the study is direct confirmation of the frequently iterated position taken by the venture capital community that above all it is the quality of the entrepreneur that ultimately determines the funding decision. Five of the top ten most important criteria had to do with the entrepreneur's experience or personality. There is no question that irrespective of the horse (product), horse race (market), or odds (financial criteria), it is the jockey (entrepreneur) who fundamentally determines whether the venture capitalist will place a bet at all.
+The question is if this is the case, then why is so much emphasis placed on the business plan? In a business plan there is generally little to indicate the characteristics of the entrepreneur—it is generally devoted to a detailed discussion of the product/service, the market, and the competition. To us, the implications are obvious—such content is necessary, but not sufficient. The business plan should also show as clearly as possible that the “jockey is fit to ride” —namely, indicate by whatever feasible and credible means possible that the entrepreneur has staying power, has a track record, can react to risk well, and has familiarity with the target market. Failing this, he or she needs to be able to pull together a team that has such characteristics and show that he or she is capable of leading that team.
+Factor analysis of the results indicate that venture capitalists appear to assess ventures systematically in terms of six categories of risk to be managed. These are: risk of losing the entire investment: risk of being unable to bail out if necessary; risk of failure to implement the venture idea; competitive risk; risk of management failure; and risk of leadership failure.
+Finally, three clusters of venture capitalists were identified: those who carefully assess the competitive and implementation risks: those who seek easy bail out; and those who deliberately keep as many options open as possible.</t>
+  </si>
+  <si>
+    <t>Ian C. Macmillan, Robin Siegel, P.N.Subba Narasimha</t>
+  </si>
+  <si>
+    <t>Criteria used by venture capitalists to evaluate new venture proposals</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1okUKHhVjn_hxRofN-ld8duNv0gnVeeKi/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>Venture Capitalists' Assessment of New Venture Survival</t>
+  </si>
+  <si>
+    <t>Dean A. Shepherd</t>
+  </si>
+  <si>
+    <t>This study investigates whether VCs' assessment policies of new venture survival are consistent with those arising from the strategy literature (using two established strategy perspectives). Strategy scholars suggest the nature of the markets, competition, and decisions made by the management team affect a new venture's survival chances. The findings demonstrate that VCs' assessment policies are predominantly consistent with those proposed by strategy scholars—providing insight into why VCs consider certain criteria in their assessment of new venture survival as well as why some criteria are more important in their assessment than others. Through this increased understanding of venture capitalists' decision making, entrepreneurs seeking capital may be better able to address their requests for funding to those criteria venture capitalists find most critical to the survival of a new venture. Venture capitalists may use these findings to better understand their own decision making process, which, in turn, provides the opportunity to increase evaluation efficiency.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DvD9Q62lHu5Wjq_WuTOmzSzl3GpyDiOj/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>Covenants in Venture Capital Contracts</t>
+  </si>
+  <si>
+    <t>Bengtsson</t>
+  </si>
+  <si>
+    <t>This paper studies how covenants are included in contracts between venture capitalists (VCs) and entrepreneurs. I show that VCs hold covenanted veto rights even though they are shareholders who have access to other powerful governance solutions. Unlike bank loans and bonds, venture capital (VC) contracts exhibit considerable variation in their contractual designs. I exploit this variation to confirm the argument that covenants are in place to overcome a conflict of interest that arises from debt-like contractual features of a venture capitalist's preferred stock. In particular, I find that contracts with higher fixed payoffs include 1.6 more covenants than do contracts with lower fixed payoffs. Similarly, VC contracts with no VC board majority requirement include 0.6 more covenants than do contracts that require a VC board majority. Covenants are also more common with older companies and when fewer VCs invest in a round. My findings contribute to both the debt covenant literature and the entrepreneurial finance literature.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1YOri8g5Z0NrNpi01dAzyhBgO_SJvO2R5/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>When do venture capitalists add value?</t>
+  </si>
+  <si>
+    <t>Sapienza</t>
+  </si>
+  <si>
+    <t>Venture capitalists functioning as lead investors and the entrepreneur-CEOs of their portfolio companies responded to questionnaire surveys that asked them to rate the venture capitalists' involvement in the ventures. The perceived effectiveness of the investor's involvement weighted by its perceived importance was used as a proxy for the investor's value to the venture. The survey was administered in the early part of 1988. Eighty percent of venture capitalists and 85% of entrepreneurs surveyed responded; in all, 51 matched pairs of lead investor-CEO surveys were completed and returned. Over 50 hours of interviews were also conducted to help clarify information derived through the surveys.
+CEOs and venture capitalists rated the nature and intensity of their interaction as well as the performance of the venture over a one-year period. CEOs also provided data on strategy, level of innovation, environmental uncertainty, and their level of experience. Regression analyses indicated that a significant portion of variation in the value of venture capitalist involvement was explained by these factors. Specifically, the greater the innovation pursued by the venture, the more frequent the contact between the lead investor and the CEO, the more open the communication, and the less conflict of perspective in the venture capitalist-CEO pair, the greater was the value of the involvement. Neither the stage of the venture nor the CEO's experience had a significant impact on value added. The value of venture capitalists' involvement was also strongly positively correlated with venture performance.
+The implications for the venture capitalists include the following: (1) the value of involvement varies with circumstances; (2) the most effective venture capitalists are those who maintain frequent, open communications while minimizing conflict; (3) opportunities exist for adding value in all venture stages; and (4) both experienced and inexperienced CEOs can benefit.
+For entrepreneurs, three key findings are: (1) because venture capitalists can add value beyond the money supplied, choosing the right one at the outset is very important; (2) once in, it is important to keep communication channels open; and (3) high innovation ventures benefit most from venture capitalist involvement.
+The results are important because they provide insight into controllable circumstances that impact the value of venture capitalist involvement in their portfolio companies. Given the general economic conditions now facing entrepreneurs and the degree of cut-throat competition in the venture capital industry, such information may prove extremely useful to both as they plan strategies for the 1990s.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rg4SNguVf8SVrxlJCMj6JBYZA5jQfn0i/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>This paper examines the dynamics of exit options for US venture capital funds. Using a sample of more than 20,000 investment rounds, we analyze the time to ‘IPO’, ‘trade sale’ and ‘liquidation’ for 6000 VC-backed firms. We model these exit times using competing risks models, which allow for a joint analysis of exit type and exit timing. The hazard rate for IPOs are clearly non-monotonic with respect to time. As time flows, VC-backed firms first exhibit an increased likelihood of exiting to an IPO. However, after having reached a plateau, non-exited investments have fewer possibilities of IPO exits as time increases. This sharply contrasts with trade sale exits, where the hazard rate is less time-varying. We further provide evidence on the impact of economic factors such as syndicate size and composition, geographical location and VC value adding, on exit outcomes.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1f3TMc1ThaUNga-3-2dH_pxj2bVX48EQm/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/10vh4KdOpBXEFQot8DFIKEGCl0Yg_r2Qq/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>Evaluation uncertainty of venture capitalists' investment criteria</t>
+  </si>
+  <si>
+    <t>Tobias Kollmann,
+Andreas Kuckertz</t>
+  </si>
+  <si>
+    <t>This paper analyzes the decision process of venture capitalists. The study focuses on aligning the evaluation uncertainty in the decision criteria of venture capitalists with the progress of the process. The reasoning builds from the concept of search, experience and credence qualities, which was developed in the economics of information and allows the identification of the varying uncertainty of a single decision criterion compared to other criteria, along with uncertainty variations throughout the process. Exploratory empirical evidence suggests that in the early steps of the process in particular, management criteria are uncertain, while at the end of the process other criteria couple with uncertainty.</t>
+  </si>
+  <si>
+    <t>“In pursuit of the real deal”
+A longitudinal study of VC decision making</t>
+  </si>
+  <si>
+    <t>Jeffrey S. Petty, Marc Gruber</t>
+  </si>
+  <si>
+    <t>This paper investigates actual Venture Capital (VC) decision making as it occurs over time in its
+natural decision environment. Our qualitative analysis is based on a comprehensive,
+longitudinal data set comprising 11 years of archival data from a European-based VC firm.
+During this time, the VC managed two funds, reviewed a total of 3631 deals, and made 35
+investments. By adopting this research methodology, we can overcome several limitations of
+post-hoc methods and experiments commonly used in this research stream, and also have the
+opportunity to tackle some fundamental, yet hitherto elusive research topics. For example, our
+findings reveal how the importance of decision-making criteria varies between different stages
+of the evaluation process. They also show how VC portfolio composition and VC management
+time serve as important, yet to-date largely neglected decision-making criteria. Implications for
+research and practice are outlined.</t>
+  </si>
+  <si>
+    <t>Venture Capital</t>
+  </si>
+  <si>
+    <t>Venture Capital Theory</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1vfMdpwV37WY0R822toN5BxcWeLW3pq5S/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Attributes of Angel and Crowdfunded Investments as Determinants of VC Screening Decisions</t>
+  </si>
+  <si>
+    <t>Will Drover, Matthew S. Wood, and Andrew Zacharakis</t>
+  </si>
+  <si>
+    <t>This research explores whether relationships between young firms and certain early–stage seed funders portray certification effects that influence venture capitalist (VC) screening decisions. Specifically, we analyze how varying attributes of angel and crowdfunded investments certify venture quality in the minds of VCs as they make due diligence screening decisions. Results from two experiments utilizing 104 VCs making 1,036 screening decisions demonstrate that the heterogeneous nature of the attributes of angels and the crowd can produce highly influential certification effects.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1p17quOxb-CAbSx9awfyUORDrd0xfufBo/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Optimal Investment, Monitoring, and the Staging of Venture Capital</t>
+  </si>
+  <si>
+    <t>Paul A. Gompers</t>
+  </si>
+  <si>
+    <t>Factors that determine the reputation of private equity managers in developing markets</t>
+  </si>
+  <si>
+    <t>This paper examines the structure of staged venture capital investments when agency and monitoring costs exist. Expected agency costs increase as assets become less tangible, growth options increase, and asset specificity rises. Data from a random sample of 794 venture capital-backed firms support the predictions. Venture capitalists concentrate investments in early stage and high technology companies where informational asymmetries are highest. Decreases in industry ratios of tangible assets to total assets, higher market-to-book ratios, and greater R&amp;D intensities lead to more frequent monitoring. Venture capitalists periodically gather information and maintain the option to discontinue funding projects with little probability of going public.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1cfH9AglEcsGhSKy5Nliq8RuWY5fXX4T_/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14KhDfw_OQtMMVBbUMlMqkCZDBVOeLKnz/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>This paper analyzes the relationship between investors and private equity managers in order to
+identify the factors that affect the latter's reputation. Since there are no individual references about
+their past returns in developing private equity markets, the reputation of such players is thought to be linked to their capacity for obtaining new funds. Results provide evidence of the volume of in-
+vestments recorded in the past, the ratio of portfolio companies to investment manager, the per-
+centage of divestments carried out through initial public offerings and trade sales, the membership of the national private equity association and the size of funds under management as characteristics of the highest importance in raising funds.</t>
+  </si>
+  <si>
+    <t>Marina Balboaa, José Martí</t>
+  </si>
+  <si>
+    <t>This paper introduces an analysis of the impact of Legality on the exiting of venture capital investments. We consider a sample of 468 venture-backed companies from 12 Asia-Pacific countries, and these countries' venture capitalists' investments in US-based entrepreneurial firms. The data indicate IPOs are more likely in countries with a higher Legality index. This core result is robust to controls for country-specific stock market capitalization, MSCI market conditions, venture capitalist fund manager skill and fund characteristics, and entrepreneurial firm and transaction characteristics. Although Black and Gilson (1998) speculate on a central connection between active stock markets and active venture capital markets, our data in fact indicate the quality of a country's legal system is much more directly connected to facilitating VC-backed IPO exits than the size of a country's stock market. The data indicate Legality is a central mechanism which mitigates agency problems between outside shareholders and entrepreneurs, thereby fostering the mutual development of IPO markets and venture capital markets.</t>
+  </si>
+  <si>
+    <t>Legality and Venture Capital Exits</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VD3eSVIGgE53SpDXkaqAVnu-qpmLGlOx/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>What do venture capitalists do?</t>
+  </si>
+  <si>
+    <t>Michael Gorman, William A. Sahlman</t>
+  </si>
+  <si>
+    <t>This paper presents the results derived from 49 responses to a questionnaire mailed to 100 venture capitalists in late 1984. The purpose of the survey was to shed light on the relationship between venture capitalists and their portfolio companies. The survey revealed that the venture capitalists who responded spend about half their time monitoring nine portfolio investments; of these, five are companies on whose boards they sit. For the latter group, a venture capitalist typically devotes 80 hours of on-site time and 30 hours of phone time per year in direct contact with each company. The most frequently performed service for portfolio companies is to help raise additional funds, with strategic analysis and management recruiting also mentioned as important roles. Finally, the venture capitalists in the survey had replaced an average of three CEOs during their careers; weak senior management was considered to be the dominant cause of venture failure.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1wg0zVr-tvmK498gAt5jZqbkdle791-vD/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Venture capitalists' involvement in their investments: Extent and performance</t>
+  </si>
+  <si>
+    <t>Ian C. Macmillan, David M. Kulow and Roubina Khoylian</t>
+  </si>
+  <si>
+    <t>Venture capitalists responded to a questionnaire that asked them to identify their degree of involvement in a number of activities for a funded venture as well as other characteristics of the venture, including its performance. The three-page questionnaire was distributed to a sample of 350 venture capitalists during December 1986 and February 1987. In all, 62 questionnaires (18%) were completed and returned.
+The results indicated that venture capitalists were involved most—compared to the entrepreneur—in the financial aspects of the venture. The activity that had the highest degree of involvement was serving as a sounding board to the entrepreneur. The lowest degree of involvement occurred in those activities concerning the ongoing operations. Factor analysis on involvement patterns in the venture activities identified four distinct areas of involvement: development and operations, management selection, personnel management, and financial participation.
+The venture capitalists indicated that if they could change their degree of involvement, overall they would have done so only slightly. It was evident, however, that they would have increased their involvement in those activities requiring a minimal time commitment, such as formulating business strategy or marketing plans, or serving as a sounding board to the entrepreneur. It was evident that they would have decreased their involvement in activities that required substantial time commitment, such as developing production or service techniques, selecting vendors and equipment, or soliciting customers or distributors.
+Perhaps the most important result was the identification of three distinct levels of involvement adopted by venture capitalists: 1) Laissez Faire involvement, in which the venture capitalists exhibited limited involvement; 2) Moderate involvement, in which venture capitalists exhibited moderate involvement; and 3) Close Tracker involvement, in which venture capitalists exhibited more involvement than the entrepreneur in a majority of the identified activities. Because tests regarding the venture firms, the products or services in relation to the market, and management team characteristics did not significantly explain why the three distinct types of venture capitalist involvement emerged, it appears that venture capitalists exhibited different involvement levels solely because they elected to do so. Tests also indicated that the difference in the performance level of the ventures among the three groups was statistically insignificant.
+Regression analyses indicated that for each of the three types of involvement, involvement in various activities had different correlations with performance. Among Laissez Faire involvement ventures, developing the professional support group had a positive correlation with venture performance. Among Moderate involvement ventures, monitoring operations had a positive correlation with venture performance while involvement at the strategic level and in searching for management candidates exhibited negative correlations. Finally, among Close Tracker involvement ventures, negotiating employment terms with management had a positive correlation with performance, while searching for management candidates exhibited a negative correlation. It is interesting that searching for management candidates in both the Moderate and Close Tracker ventures had a negative correlation with venture performance.
+These results are important because they show that depending on the involvement types selected by venture capitalists, different involvement strategies in the various activities should be more suitable. If venture capitalists recognize this they can adopt more appropriate strategies, which may lead to more successful ventures.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1siNqOpBto80CdBhzCLtOw3szV2iBRBud/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>Characteristics, Contracts, and Actions:
+Evidence from Venture Capitalist Analyses</t>
+  </si>
+  <si>
+    <t>STEVEN N. KAPLAN, PER STROMBERG</t>
+  </si>
+  <si>
+    <t>We study the investment analyses of 67 portfolio investments by 11 venture capital
+(VC) firms. VCs describe the strengths and risks of the investments as well as expected
+postinvestment actions. We classify the risks into three categories and relate them to
+the allocation of cash f low rights, contingencies, control rights, and liquidation rights
+between VCs and entrepreneurs. The risk results suggest that agency and hold-up
+problems are important to contract design and monitoring, but that risk sharing is
+not. Greater VC control is associated with increased management intervention, while
+greater VC equity incentives are associated with increased value-added support.</t>
+  </si>
+  <si>
+    <t>Proximity and Innovation: A Critical Assessment</t>
+  </si>
+  <si>
+    <t>Ron Boschma</t>
+  </si>
+  <si>
+    <t>Proximity and innovation: a critical assessment, Regional Studies 39, 61–74. A key issue in economic
+geography is to determine the impact of geographical proximity on interactive learning and innovation. We argue that the
+importance of geographical proximity cannot be assessed in isolation, but should always be examined in relation to other
+dimensions of proximity that may provide alternative solutions to the problem of coordination. We claim that geographical
+proximity per se is neither a necessary nor a suﬃcient condition for learning to take place. Nevertheless, it facilitates interactive
+learning, most likely by strengthening the other dimensions of proximity. However, proximity may also have negative impacts
+on innovation due to the problem of lock-in. Accordingly, not only too little, but also too much proximity may be detrimental
+to interactive learning and innovation. This may be the case for all five dimensions of proximity discussed in the paper, i.e.
+cognitive, organizational, social, institutional and geographical proximity. Finally, the paper presents a number of mechanisms
+that oﬀer, by their own, or in combination, solutions to the problems of coordination and lock-in. That is, they enhance
+eﬀective coordination and control (solving the problem of too little proximity), while they prevent actors to become locked-in
+through ensuring openness and flexibility (solving the problem of too much proximity).</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1S7q5-KpbZZ4XZOG1NWjqsl00bZOZOTFj/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Optimal cognitive distance and absorptive capacity</t>
+  </si>
+  <si>
+    <t>Noteboom et al.</t>
+  </si>
+  <si>
+    <t>In this paper we test the relation between cognitive distance and innovation performance of firms engaged in technology-based alliances. The key finding is that the hypothesis of an inverted U-shaped effect of cognitive distance on innovation performance of firms is confirmed. Moreover, as expected, we found that the positive effect for firms is much higher when engaging in more radical, exploratory alliances than in more exploitative alliances. The effect of cumulative R&amp;D turns out to be mixed. It appears to increase absorptive capacity, as expected, but there is clear evidence that it also reduces the effect of cognitive distance on novelty value, making it increasingly difficult to find additional novelty.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1u8suOEliGnDm-nvtmzq34JvGb4NLNJP-/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Proximity and Localization</t>
+  </si>
+  <si>
+    <t>ANDRE TORRE,  ALAIN RALLET</t>
+  </si>
+  <si>
+    <t>The objective of this paper is to pave the way for an analysis of the relations between proximity and localization of activities and people, two notions that are often mistaken for one another. Our method consists in exploiting the semantic wealth of the notion of proximity. We distinguish two types of proximity (geographical and organized) and propose a grid of analysis of the main models of geographic organization of activities by articulating both types of proximity. We then introduce the phenomenon of tension between geographical and organized proximity in order to discuss problems that are often underestimated in spatial economy. First, organized proximity offers powerful mechanisms of long-distance coordination that constitute the foundation of the increasing geographical development of socio-economic interactions. The confusion between information interactions and knowledge exchange, and the constraint of being located in proximity neglects the fact that the collective rules and representations do manage, and at a distance, an increasing part of these interactions. It is then shown that there is a disjunction between the need for geographical proximity and co-localization of actors by introducing professional mobility and temporary geographical proximity. We also emphasize the ability of big organizations to manage the presence in different areas of their units, whereas smaller ones are more constrained by fixed co-localizations, which are only needed for certain phases of their interactions. Finally, we raise the often neglected question of the negative effects of geographical proximity, which creates tensions between the actors who use limited support-goods and tends to damage the local relational network. However, these negative effects can be limited by integrating them within organizations or institutions, that is through a re-composed organized proximity enabling one to solve conflicts and launch processes of cooperation or negotiation within ad- hoc mechanisms.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VPVayrf7c7lv-megCC1hH7s0kG7_Lqk4/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Management and Organization Review</t>
+  </si>
+  <si>
+    <t>Batjargal</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> I compare networks of entrepreneurs and venture capitalists in China and Russia by examining professional social networks of software entrepreneurs and private equity investors from the perspectives of institutional theory and culture paradigm. In the empirical study, I draw on survey data from Beijing and Moscow based on interviews of 159 software entrepreneurs and 124 venture capital decisions. I found that professional networks of the Chinese software entrepreneurs are smaller, denser and more homogeneous in educational specializations, compared with the networks of Russian entrepreneurs. Furthermore, I found that both ties and interpersonal trust in the referral tie are stronger in China than in Russia.</t>
+  </si>
+  <si>
+    <t>Comparative Social Capital: Networks of Entrepreneurs and Venture Capitalists in China and Russia</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1MT_0jhBKylqm_gsA1WT7C4Gpj3BYeFsZ/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Startups in times of crisis– A rapid response to the
+COVID-19 pandemic</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rTOGKRRmdF6tanqTHXVEgfbQupmWOovf/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>Kuckertz et al.</t>
+  </si>
+  <si>
+    <t>Covid, Startups</t>
+  </si>
+  <si>
+    <t>The discovery of the coronavirus (SARS-CoV-2) and the spread of COVID-19
+have led many governments to take drastic measures. The lockdown of large parts of society
+and economic life has come as an exogenous shock to many economic actors, not least innovative
+startups. This rapid response research combines a qualitative research design informed by
+entrepreneurial ecosystem actors with an analysis of policy measures called for, announced, and
+reportedly implemented in the international press. Interviews from an entrepreneurial ecosystem
+offer a rst-hand account of the adversity startups face during a crisis and how by utilizing
+bricolage responses they cope, and the analysis of policy measures can serve as an inspiration to
+design support initiatives to protect startups from the consequences of the current lockdown and to
+alleviate the effects of future crises.
+Managerial summary: The lockdown measures as a response to the spread of the new coronavirus
+threaten the existence of many innovative startups. Our rapid response research rst illustrates the
+challenges entrepreneurs face as a consequence of the crisis. Second, we illustrate how entre-
+preneurs are dealing with the effects of the crisis and what they are doing to protect their ventures.
+Finally, we present measures that could be utilized by policymakers to assist entrepreneurs facing
+challenges. The research conducted suggests that while startups are successfully leveraging their
+available resources as a rst response to the crisis, their growth and innovation potential are at
+risk. Therefore, policy measures should not only provide rst aid to startups by alleviating the
+pressure caused by constrained cash ow, but also involve long-term measures embedded in and
+supported by the wider entrepreneurial ecosystem to ensure rapid recovery and growth.</t>
+  </si>
+  <si>
+    <t>Proximity and Innovation: From Statics to Dynamics</t>
+  </si>
+  <si>
+    <t>Balland et al.</t>
+  </si>
+  <si>
+    <t>Despite theoretical and empirical advances, the proximity framework has remained essentially static. A dynamic extension of the proximity framework is proposed that accounts for co-evolutionary dynamics between knowledge networking and proximity. For each proximity dimension, how proximities might increase over time as a result of past knowledge ties is described. These dynamics are captured through the processes of learning (cognitive proximity), integration (organizational proximity), decoupling (social proximity), institutionalization (institutional proximity), and agglomeration (geographical proximity). The paper ends with a discussion of several avenues for future research on the dynamics of knowledge networking and proximity.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15xPB1mJZSUKO3rSYPBFh4Iq0P5AgYwmS/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>The New Ways to Raise Capital: An Exploratory Study of Crowdfunding</t>
+  </si>
+  <si>
+    <t>Rossi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Journal of Financial Research </t>
+  </si>
+  <si>
+    <t>Paper aims is to describe, analyze and to increase the knowledge of the emerging crowdfunding phenomenon. This can be defined as the practice of funding a project or venture by raising a lot of small quantities of money from a huge number of people. Even though the number of academic studies has been increasing, the coverage of the population is relatively weak and not well understood by entrepreneurs and individual investors.Design/Methodology/Findings - The research can be classified as an exploratory research. It focuses on how the crowdfunding works. The research addresses the following research questions: What is crodwfunding? Which are the main characteristics of this phenomenon? Wihic are the principal strengths and the main weaknesses of crowdfunding? The findings expose purposes, characteristics, roles and tasks, and investment size of crowd-funding activity.Practical implications - The findings have implications for service managers interested in managing crowd-funding initiatives and to improve the activity of the consumers.Originality/value - The paper analyses a new emergent phenomenon. It aims to define the user/costuemr’s role from co-creation to investment.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1M_L6okxFfmOIhYEMko3YAq8MswG1W_dD/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1GAZiPTAPuDZlulWLGbGLU-4tZwE5iD6r/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ZS4HT3LmOwRMCdwfH3kvpMKcB1qL8JD6/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>A process model of entrepreneurial venture creation</t>
+  </si>
+  <si>
+    <t>Mahesh P. Bhave</t>
+  </si>
+  <si>
+    <t>Venture Creation Process</t>
+  </si>
+  <si>
+    <t>The process model of entrepreneurial venture creation developed in this paper is based on interviews with entrepreneurs who started twenty-seven business in a range of industries in upstate New York. The venture creation process described here is an iterative, nonlinear, feedback-driven, conceptual, and physical process.
+The model includes internally and externally stimulated opportunity recognition, commitment to physical creation, set-up of production technology, organization creation, product creation, linking with markets, and customer feedback. For analytical convenience, the process has been divided into the opportunity stage, the technology set-up and organization-creation stage, and the exchange stage. Business concept, production technology, and product are respectively the core variables representing the three stages.
+Entrepreneurs introduce differing amounts of novelty at each core variable during venture creation, and the varying amounts of novelty qualitatively distinguish one kind of entrepreneurship from another.
+For the researcher, the model suggests a better method for specifying samples of entrepreneurial firms. It shows how studies on the context of venture creation can be more specific, and proposes that novelty at the core variables be operationalized as a step toward defining the entrepreneurial content of ventures.
+For the prospective entrepreneur, the model will serve as a useful road map. It will alert the entrepreneur to the strategic issues at each stage in the venture creation process, particularly when introducing significant novelty at any of the core variables.</t>
+  </si>
+  <si>
+    <t>The Design of Startup Accelerators</t>
+  </si>
+  <si>
+    <t>Cohen et al.</t>
+  </si>
+  <si>
+    <t>Accelerator programs are an increasingly important part of entrepreneurial ecosystems. While accelerators have core defining features—fixed-term, cohort-based educational and mentorship programs for startups— there is also significant variation amongst them. In this paper, we relate key variation in the antecedents, organizational design and operation of these programs to theories of firm-level entrepreneurial performance. We then document descriptive correlations between these design elements and the performance of the startups that attend these programs. In doing so, we probe the connections between design and performance in ways that integrate previously disparate research on accelerators and expand our understanding of startup intermediaries. Our findings delineate the building blocks as well as an agenda for future researchers to build upon not only our understanding of accelerators, but also our understanding of what new ventures need to survive and flourish.</t>
+  </si>
+  <si>
+    <t>Accelerators</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1l90Y6qJX2K5nsRrZl0Hsh-mkpO4cXB40/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>ANALYSIS OF FINANCING SOURCES FOR START-UP COMPANIES</t>
+  </si>
+  <si>
+    <t>Overview Financing Instruments</t>
+  </si>
+  <si>
+    <t>Čalopa et al.</t>
+  </si>
+  <si>
+    <t>Journal of Contemporary Management Issues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This paper presents the development of start-up companies, their types and potential sources of financing with special emphasis on financing ventures in Croatia. The expected scientific contribution supports the defining stages of development for start-ups, as well as their financing sources at each stage. The goal of the research was to investigate whether Croatia has made a shift from traditional to newer methods of financing. Scientific and research contributions of the paper are reflected in the fact that there is a relatively small number of papers, especially in the domestic literature, that address these issues. Therefore, this research can contribute to a better understanding of the financing strategy of entrepreneurial ventures. Presented and interpreted results could be a useful basis and encouragement for a further research in this and similar topics related to the start-up scene at the local as well as the global level.
+</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Kke6fd3-if9yMqDuxTcPgxeWNphYQ-Fu/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1wKKbfsMmQjimWplwBu8Cl2XtncmhmA3-/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>Venture-Capital Financing and the
+Growth of Startup Firms</t>
+  </si>
+  <si>
+    <t>Davila</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1b9bEe_1bNJHCweOr0UlOmwyqv_y9TuGj/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>This study examines the association between the presence of venture capital (VC) and the employee growth of startups. Grounded in signaling theory, it investigates the impact, if any, of VC financing events upon the growth of these companies and whether the amount of funding affects the intensity of the signal. It further explores whether VC leads to growth or, alternatively, whether growth signals the need for VC. Finally, it documents the relationship between growth in startup financial valuation and changes in the number of employees over successive rounds of financing.</t>
+  </si>
+  <si>
+    <t>Blockchain-Based ICOs: Pure Hype or the Dawn of a New Era of Startup Financing?</t>
+  </si>
+  <si>
+    <t>Ante et al.</t>
+  </si>
+  <si>
+    <t>Blockchain Financing, ICO</t>
+  </si>
+  <si>
+    <t>J. Risk Financial Manag.</t>
+  </si>
+  <si>
+    <t>This study explores the determinants of initial coin offering (ICO) success, where success is
+defined as the amount of capital a project could raise. ICOs are a tool for startups in the blockchain
+ecosystem to raise early capital with relative ease. The market for ICOs has grown at a rapid pace since
+its start in 2013. We analyze a unique dataset of 278 projects that finished their ICOs by August 2017
+to assess determinants of funding success that we derive from the crowdfunding and venture capital
+literature. Our results show that ICOs exhibit similarities to classical crowdfunding and venture
+capital markets. Specifically, we identify resemblances in determinants of funding success regarding
+human capital characteristics, business model quality, project elaboration, and social media activity.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jCu6LxBZP8EIC45iYf8J5YD3IdZAEUdX/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1fDivHZOTX4mDhTmJr9NKTSfrpY3Fdhe6/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Jeong et al.</t>
+  </si>
+  <si>
+    <t>The Role of Venture Capital Investment in Startups’ Sustainable Growth and  Performance: Focusing on Absorptive Capacity and Venture Capitalists’ Reputation</t>
+  </si>
+  <si>
+    <t>Sustainability</t>
+  </si>
+  <si>
+    <t>This study provides evidence on how venture capital (VC) investment affects startup firms’
+sustainable growth and performance. Despite the rich and abundant research on the relationship
+between VC investment and startup performance, there is no clear evidence about the contribution
+of VC investment on the performance and market value of invested firms. In order to accurately
+measure the impact of VC investment, this study explored how VC investment at each stage of
+growth affects a startup’s sustainable growth and performance. Based on signaling theory and
+information asymmetry, this study proposed a positive link between initial-stage VC investment and
+a startup’s growth and performance. Using a sample of 363 firms listed from 2000 to 2007, this study demonstrated that startups are sustained and perform better as they receive their VC investment at the initial stage. The level of potential absorptive capacity positively moderated this association, unlike realized absorptive capacity, which did not show significant moderating effects.</t>
+  </si>
+  <si>
+    <t>Entrepreneurial ecosystem elements</t>
+  </si>
+  <si>
+    <t>Stam, van de ven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There is a growing interest in ecosystems as an approach for understanding the context of entrepreneurship at the macro level of an organizational community. It consists of all the interdependent actors and factors that enable and constrain entrepreneurship within a particular territory. Although growing in popularity, the entrepreneurial ecosystem concept remains loosely defined and measured. This paper shows the value of taking a systems view of the context of entrepreneurship: understanding entrepreneurial economies from a systems perspective. We use a systems framework for studying entrepreneurial ecosystems, develop a measurement instrument of its elements, and use this to compose an entrepreneurial ecosystem index to examine the quality of entrepreneurial ecosystems in the Netherlands. We find that the prevalence of high-growth firms in a region is strongly related to the quality of its entrepreneurial ecosystem. Strong interrelationships among the ecosystem elements reveal their interdependence and need for a systems perspective.
+</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_xnz9yMbKKATh04CzNM7sN6llls8zxmM/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Startup Financing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bruvI89emqcWDNX2lA21E0kmoeQObPae/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Toward an Entrepreneurial Ecosystem Research Program</t>
+  </si>
+  <si>
+    <t>Wurth, Stam, Spigel</t>
+  </si>
+  <si>
+    <t>Entrepreneurial ecosystems have become a prominent concept, yet in its current state, the concept itself represents a paradox. While it draws on a rich intellectual history and provides an opportunity to synthesize different strands of research, it is also under-theorized and the mechanisms that govern ecosystem evolution are not well understood. This paper takes stock of recent advancements in ecosystem scholarship and synthesizes the empirical reality of the causal mechanisms. We use these dynamics to position ecosystems in a broader context, within and beyond the domain of entrepreneurship research, and propose a transdisciplinary research program for ecosystem research and practice.</t>
+  </si>
+  <si>
+    <t>Toward a process theory of entrepreneurial ecosystems</t>
+  </si>
+  <si>
+    <t>Entrepreneurial ecosystems have recently emerged as a popular concept within entrepreneurship policy and practitioner communities. Specifically, they are seen as a regional economic development strategy that is based around creating supportive environments that foster innovative start-ups. However, existing research on entrepreneurial ecosystems has been largely typological and atheoretical and has not yet explored how they influence the entrepreneurship process. This article critically examines the relationships between ecosystems and other existing literatures such as clusters and regional innovation systems. Drawing on this background, the article suggests that a process-based view of ecosystems provides a better framework to understand their role in supporting new venture creation. This framework is used to explain the evolution and transformation of entrepreneurial ecosystems and to create a typology of different ecosystem structures.</t>
+  </si>
+  <si>
+    <t>Spigel, Harrison</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1RFLVSRYy1_fa2rdLIVhcWBN_0N79l2NO/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>strategic entrepreneurship journal</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2930,6 +3943,16 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Display"/>
     </font>
   </fonts>
   <fills count="4">
@@ -3068,7 +4091,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3116,6 +4139,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3125,10 +4154,25 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3137,8 +4181,90 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="70">
+  <dxfs count="110">
     <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3262,6 +4388,279 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Display"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3359,6 +4758,9 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -3411,126 +4813,198 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{05A3DE70-8607-154D-94FC-886F5C5AE18F}" name="Proximity" displayName="Proximity" ref="A1:P40" totalsRowShown="0" dataDxfId="69">
-  <autoFilter ref="A1:P40" xr:uid="{05A3DE70-8607-154D-94FC-886F5C5AE18F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{05A3DE70-8607-154D-94FC-886F5C5AE18F}" name="Proximity" displayName="Proximity" ref="A1:P47" totalsRowShown="0" dataDxfId="109">
+  <autoFilter ref="A1:P47" xr:uid="{05A3DE70-8607-154D-94FC-886F5C5AE18F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P32">
     <sortCondition descending="1" ref="C1:C32"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{BE890421-FAE4-E542-9F1E-B981E196844C}" name="Paper Title" dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{3EF9D581-8149-E04D-AAD0-820AB0D43B5E}" name="Authors" dataDxfId="67"/>
-    <tableColumn id="3" xr3:uid="{EA555D34-595C-9C43-8F97-76F1AE4A5266}" name="Year" dataDxfId="66"/>
-    <tableColumn id="4" xr3:uid="{D4A09DA9-9282-DF4A-ADAD-4C45732EE81B}" name="Journal Title" dataDxfId="65"/>
-    <tableColumn id="16" xr3:uid="{6E2C10AD-AB73-E24A-898B-73DDF557CB16}" name="Journal Importance" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{955A51EE-9B22-7B4C-BFB1-133ED1B97F29}" name="Abstract" dataDxfId="64"/>
-    <tableColumn id="12" xr3:uid="{5E3EF9B7-8FE7-1649-A6CF-F53A05750B5E}" name="DOI" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{70C24B6A-7FF1-5F49-B979-154258527049}" name="Research / Theory" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{8972665B-B720-5245-945A-E21765E20CAE}" name="Method" dataDxfId="61"/>
-    <tableColumn id="7" xr3:uid="{8AB08798-7826-5D4E-9E24-62A965A7EA52}" name="Outcome / Findings" dataDxfId="60"/>
-    <tableColumn id="13" xr3:uid="{20CDEE81-3EE9-444B-B350-BC58373FB9E6}" name="Effect" dataDxfId="59"/>
-    <tableColumn id="8" xr3:uid="{C197D97F-FCE4-1149-84DD-B03DA8E6B9D8}" name="Future Research" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{427420AC-26C0-AC44-AFC0-0B1DE7D423A6}" name="Variables" dataDxfId="57"/>
-    <tableColumn id="9" xr3:uid="{69462FAC-59D4-A243-B7A2-3A11E78ED3B1}" name="Relevance" dataDxfId="56"/>
-    <tableColumn id="14" xr3:uid="{643E54C9-B4A1-E745-B221-7C9BCB30FFB9}" name="Link" dataDxfId="55"/>
-    <tableColumn id="15" xr3:uid="{19A2B419-6ED7-A44F-9C0C-D2EF0458EF6B}" name="Reviewed?" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{BE890421-FAE4-E542-9F1E-B981E196844C}" name="Paper Title" dataDxfId="108"/>
+    <tableColumn id="2" xr3:uid="{3EF9D581-8149-E04D-AAD0-820AB0D43B5E}" name="Authors" dataDxfId="107"/>
+    <tableColumn id="3" xr3:uid="{EA555D34-595C-9C43-8F97-76F1AE4A5266}" name="Year" dataDxfId="106"/>
+    <tableColumn id="4" xr3:uid="{D4A09DA9-9282-DF4A-ADAD-4C45732EE81B}" name="Journal Title" dataDxfId="105"/>
+    <tableColumn id="16" xr3:uid="{6E2C10AD-AB73-E24A-898B-73DDF557CB16}" name="Journal Importance" dataDxfId="104"/>
+    <tableColumn id="5" xr3:uid="{955A51EE-9B22-7B4C-BFB1-133ED1B97F29}" name="Abstract" dataDxfId="103"/>
+    <tableColumn id="12" xr3:uid="{5E3EF9B7-8FE7-1649-A6CF-F53A05750B5E}" name="DOI" dataDxfId="102"/>
+    <tableColumn id="6" xr3:uid="{70C24B6A-7FF1-5F49-B979-154258527049}" name="Research / Theory" dataDxfId="101"/>
+    <tableColumn id="10" xr3:uid="{8972665B-B720-5245-945A-E21765E20CAE}" name="Method" dataDxfId="100"/>
+    <tableColumn id="7" xr3:uid="{8AB08798-7826-5D4E-9E24-62A965A7EA52}" name="Outcome / Findings" dataDxfId="99"/>
+    <tableColumn id="13" xr3:uid="{20CDEE81-3EE9-444B-B350-BC58373FB9E6}" name="Effect" dataDxfId="98"/>
+    <tableColumn id="8" xr3:uid="{C197D97F-FCE4-1149-84DD-B03DA8E6B9D8}" name="Future Research" dataDxfId="97"/>
+    <tableColumn id="11" xr3:uid="{427420AC-26C0-AC44-AFC0-0B1DE7D423A6}" name="Variables" dataDxfId="96"/>
+    <tableColumn id="9" xr3:uid="{69462FAC-59D4-A243-B7A2-3A11E78ED3B1}" name="Relevance" dataDxfId="95"/>
+    <tableColumn id="14" xr3:uid="{643E54C9-B4A1-E745-B221-7C9BCB30FFB9}" name="Link" dataDxfId="94"/>
+    <tableColumn id="15" xr3:uid="{19A2B419-6ED7-A44F-9C0C-D2EF0458EF6B}" name="Reviewed?" dataDxfId="93"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D20DD51-13C3-5845-AB11-DD7C452F876E}" name="Success" displayName="Success" ref="A1:L28" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D20DD51-13C3-5845-AB11-DD7C452F876E}" name="Success" displayName="Success" ref="A1:L28" totalsRowShown="0" headerRowDxfId="92" dataDxfId="91">
   <autoFilter ref="A1:L28" xr:uid="{4D20DD51-13C3-5845-AB11-DD7C452F876E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L28">
     <sortCondition descending="1" ref="C1:C28"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{0063AB55-DE73-9A4D-BB26-B8B0C7549352}" name="Paper Title" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{7A6BCA33-7E76-884F-8D2C-C221FD761545}" name="Authors" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{BFF03DD3-ABE0-1441-BF7E-ECDE6EA486AC}" name="Year" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{7462CFB0-5041-4E40-B883-8FD56BA117B2}" name="Journal Title" dataDxfId="48"/>
-    <tableColumn id="10" xr3:uid="{C985F5F5-771E-7848-9FE9-A53029FFC0FB}" name="Journal Importance" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{A0E9FAB5-39BC-2F4F-A205-AB5CC0364F27}" name="Abstract" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{4C388556-A10C-6844-B741-D8339459D8C5}" name="DOI" dataDxfId="46"/>
-    <tableColumn id="8" xr3:uid="{4EEB7A0F-F93B-A641-8436-B67AE36E027C}" name="Insights for Thesis" dataDxfId="45"/>
-    <tableColumn id="9" xr3:uid="{56BD3BA3-87C4-0B44-8072-EADA3EAA2EFC}" name="Outcomes" dataDxfId="44"/>
-    <tableColumn id="13" xr3:uid="{4DB6468D-1D4F-6247-AC1B-BBD4D59EE943}" name="Relevance" dataDxfId="43"/>
-    <tableColumn id="14" xr3:uid="{AE6D7396-2898-3F4D-BA46-767CBD12EE46}" name="Link" dataDxfId="42"/>
-    <tableColumn id="7" xr3:uid="{B540F483-EE23-984D-834A-FC30579AD342}" name="Reviewed?" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{0063AB55-DE73-9A4D-BB26-B8B0C7549352}" name="Paper Title" dataDxfId="90"/>
+    <tableColumn id="2" xr3:uid="{7A6BCA33-7E76-884F-8D2C-C221FD761545}" name="Authors" dataDxfId="89"/>
+    <tableColumn id="3" xr3:uid="{BFF03DD3-ABE0-1441-BF7E-ECDE6EA486AC}" name="Year" dataDxfId="88"/>
+    <tableColumn id="4" xr3:uid="{7462CFB0-5041-4E40-B883-8FD56BA117B2}" name="Journal Title" dataDxfId="87"/>
+    <tableColumn id="10" xr3:uid="{C985F5F5-771E-7848-9FE9-A53029FFC0FB}" name="Journal Importance" dataDxfId="86"/>
+    <tableColumn id="5" xr3:uid="{A0E9FAB5-39BC-2F4F-A205-AB5CC0364F27}" name="Abstract" dataDxfId="85"/>
+    <tableColumn id="6" xr3:uid="{4C388556-A10C-6844-B741-D8339459D8C5}" name="DOI" dataDxfId="84"/>
+    <tableColumn id="8" xr3:uid="{4EEB7A0F-F93B-A641-8436-B67AE36E027C}" name="Insights for Thesis" dataDxfId="83"/>
+    <tableColumn id="9" xr3:uid="{56BD3BA3-87C4-0B44-8072-EADA3EAA2EFC}" name="Outcomes" dataDxfId="82"/>
+    <tableColumn id="13" xr3:uid="{4DB6468D-1D4F-6247-AC1B-BBD4D59EE943}" name="Relevance" dataDxfId="81"/>
+    <tableColumn id="14" xr3:uid="{AE6D7396-2898-3F4D-BA46-767CBD12EE46}" name="Link" dataDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{B540F483-EE23-984D-834A-FC30579AD342}" name="Reviewed?" dataDxfId="79"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A30AD82-02A7-6745-A2CA-934FA2D6ABD4}" name="Support" displayName="Support" ref="A1:L18" totalsRowShown="0" dataDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F5A9A02E-BD4A-BB42-9BBA-32FC0C2447E8}" name="VentureCapital" displayName="VentureCapital" ref="A1:I51" totalsRowShown="0" dataDxfId="78">
+  <autoFilter ref="A1:I51" xr:uid="{F5A9A02E-BD4A-BB42-9BBA-32FC0C2447E8}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{D18B0CA3-5962-7543-A774-144A16809721}" name="Paper Title" dataDxfId="77"/>
+    <tableColumn id="13" xr3:uid="{8FBDFE7C-578A-1242-A9A5-41270D7EC615}" name="Topic" dataDxfId="76"/>
+    <tableColumn id="2" xr3:uid="{A696C405-4D9F-C942-B4F3-D377F3ADB0BA}" name="Authors" dataDxfId="75"/>
+    <tableColumn id="3" xr3:uid="{02AC25AE-6EC3-0D42-9A56-9045A3DE8A7A}" name="Year" dataDxfId="74"/>
+    <tableColumn id="4" xr3:uid="{45930856-5789-9D4B-8D0C-C8D9650AB468}" name="Journal Title" dataDxfId="73"/>
+    <tableColumn id="5" xr3:uid="{CF388386-F820-334E-BAA4-68781F530E64}" name="Journal Importance" dataDxfId="72"/>
+    <tableColumn id="6" xr3:uid="{458708A2-BB18-684F-BE7A-50B5FF60B83F}" name="Abstract" dataDxfId="71"/>
+    <tableColumn id="11" xr3:uid="{63E15EA5-038A-1346-9985-6BAD37ABE163}" name="Link" dataDxfId="70"/>
+    <tableColumn id="12" xr3:uid="{6F91624F-B7DD-2644-B4B3-2A5B05F97964}" name="Reviewed?" dataDxfId="69"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{DA3DAF49-133B-4342-B1F1-A669623B84B7}" name="StartupFinancing" displayName="StartupFinancing" ref="A1:I6" totalsRowShown="0" dataDxfId="1">
+  <autoFilter ref="A1:I6" xr:uid="{DA3DAF49-133B-4342-B1F1-A669623B84B7}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{D8161E5E-71F1-1946-B4E1-B30528D422AA}" name="Paper Title" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{45133EC8-77DB-BC45-8846-B40214F1638C}" name="Topic" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{7EC44AD2-9FEE-214C-ACA0-C3917FC9417E}" name="Authors" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{6C75F284-F966-7441-AFD8-CDBB0A9803B1}" name="Year" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{A01AD45C-1B6A-AE42-99A0-9712C5E3E192}" name="Journal Title" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{CD4DE00F-B729-DD46-8F9B-2A8CA3DE0BC2}" name="Journal Importance" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{A1D818FA-9230-2141-81C0-50EDB8019EBD}" name="Abstract" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{396306FC-5B14-914C-9BE1-5305DC8B03FA}" name="Link" dataDxfId="3" dataCellStyle="Hyperlink"/>
+    <tableColumn id="9" xr3:uid="{83E9F2DB-5A6C-B642-B4AC-190170490909}" name="Reviewed?" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{2C0717B9-48DC-1545-BEB4-3FAAFA0BD037}" name="VCTheory" displayName="VCTheory" ref="A1:I28" totalsRowShown="0" dataDxfId="68">
+  <autoFilter ref="A1:I28" xr:uid="{F5A9A02E-BD4A-BB42-9BBA-32FC0C2447E8}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{B95F0992-9842-EE4F-9B0A-816E94F39B69}" name="Paper Title" dataDxfId="67"/>
+    <tableColumn id="13" xr3:uid="{8C764070-1671-7B4A-BDE9-595A7A56C9B3}" name="Topic" dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{DDB30B63-EEF2-3B4F-BE3D-29F36FA87651}" name="Authors" dataDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{1C8DDEE0-2997-E843-A575-5E6FEA47499F}" name="Year" dataDxfId="64"/>
+    <tableColumn id="4" xr3:uid="{4A18AFA9-BE70-1345-A4A0-710E14F15C74}" name="Journal Title" dataDxfId="63"/>
+    <tableColumn id="5" xr3:uid="{B6A9D77E-3C61-C542-B8D3-04E55556D03E}" name="Journal Importance" dataDxfId="62"/>
+    <tableColumn id="6" xr3:uid="{BF854912-6FF3-8845-957C-E27FB31495FD}" name="Abstract" dataDxfId="61"/>
+    <tableColumn id="11" xr3:uid="{00B57B48-105F-AC40-98C8-349FB96920FE}" name="Link" dataDxfId="60"/>
+    <tableColumn id="12" xr3:uid="{80230E1F-6CB1-6547-B78F-8342F2FD62E4}" name="Reviewed?" dataDxfId="59"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A30AD82-02A7-6745-A2CA-934FA2D6ABD4}" name="Support" displayName="Support" ref="A1:L18" totalsRowShown="0" dataDxfId="58">
   <autoFilter ref="A1:L18" xr:uid="{6A30AD82-02A7-6745-A2CA-934FA2D6ABD4}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L18">
     <sortCondition descending="1" ref="C1:C18"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{A616AEE6-C6DE-3848-B3E0-6002397B9882}" name="Paper Title" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{FF60328E-A314-FD4E-820F-3DB20EB3439C}" name="Authors" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{CBBF5768-3F3B-6540-A093-4FD23CD75C72}" name="Year" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{01171707-AA15-DD41-B524-CDE7D67FF738}" name="Journal Title" dataDxfId="36"/>
-    <tableColumn id="8" xr3:uid="{11C89D04-6481-D540-AA96-61DAC7AF4A34}" name="Journal Importance" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{AB646E0C-5A77-1444-B818-4CEB6E7B9BFA}" name="Abstract" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{A321187A-382D-FE46-806D-75FA9604EB6B}" name="DOI" dataDxfId="34" dataCellStyle="Hyperlink"/>
-    <tableColumn id="11" xr3:uid="{0512DC86-6CE5-CB45-B301-2161DBBC1236}" name="Insights for Thesis" dataDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{B6492819-882E-6E43-A300-8E723AE7BF33}" name="Outcomes" dataDxfId="32"/>
-    <tableColumn id="13" xr3:uid="{FAC6D398-1FDC-6944-9A7E-34C28ECDAA8B}" name="Relevance" dataDxfId="31"/>
-    <tableColumn id="14" xr3:uid="{F7655086-4881-9D4F-BDBF-0FB8DE110B27}" name="Link" dataDxfId="30" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{3A688F49-F3F4-B549-83D0-B0942C7EE14B}" name="Reviewed?" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{A616AEE6-C6DE-3848-B3E0-6002397B9882}" name="Paper Title" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{FF60328E-A314-FD4E-820F-3DB20EB3439C}" name="Authors" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{CBBF5768-3F3B-6540-A093-4FD23CD75C72}" name="Year" dataDxfId="55"/>
+    <tableColumn id="4" xr3:uid="{01171707-AA15-DD41-B524-CDE7D67FF738}" name="Journal Title" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{11C89D04-6481-D540-AA96-61DAC7AF4A34}" name="Journal Importance" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{AB646E0C-5A77-1444-B818-4CEB6E7B9BFA}" name="Abstract" dataDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{A321187A-382D-FE46-806D-75FA9604EB6B}" name="DOI" dataDxfId="51" dataCellStyle="Hyperlink"/>
+    <tableColumn id="11" xr3:uid="{0512DC86-6CE5-CB45-B301-2161DBBC1236}" name="Insights for Thesis" dataDxfId="50"/>
+    <tableColumn id="12" xr3:uid="{B6492819-882E-6E43-A300-8E723AE7BF33}" name="Outcomes" dataDxfId="49"/>
+    <tableColumn id="13" xr3:uid="{FAC6D398-1FDC-6944-9A7E-34C28ECDAA8B}" name="Relevance" dataDxfId="48"/>
+    <tableColumn id="14" xr3:uid="{F7655086-4881-9D4F-BDBF-0FB8DE110B27}" name="Link" dataDxfId="47" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{3A688F49-F3F4-B549-83D0-B0942C7EE14B}" name="Reviewed?" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium17" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6B0EF1A4-B632-064C-B047-AFD93614047D}" name="Ecosystem" displayName="Ecosystem" ref="A1:L14" totalsRowShown="0" dataDxfId="13">
-  <autoFilter ref="A1:L14" xr:uid="{6B0EF1A4-B632-064C-B047-AFD93614047D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L14">
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6B0EF1A4-B632-064C-B047-AFD93614047D}" name="Ecosystem" displayName="Ecosystem" ref="A1:K22" totalsRowShown="0" dataDxfId="45">
+  <autoFilter ref="A1:K22" xr:uid="{6B0EF1A4-B632-064C-B047-AFD93614047D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K14">
     <sortCondition descending="1" ref="C1:C14"/>
   </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{DDA40927-D99D-7944-ABBB-E062EAC00CB0}" name="Paper Title" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{7063D636-C85B-3548-A015-8D7C939D4FA5}" name="Authors" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{0A4B399A-AD2E-3048-B417-A6AB46292C0E}" name="Year" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{3ED340CA-2C59-CE48-BDF0-D7CD1022D6AA}" name="Journal Title" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{6613DB95-863F-B043-ABF2-28DACB82C976}" name="Journal Importance" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{CFA5C437-782F-2146-99F8-88849AC4D708}" name="Abstract" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{2C7F3A04-CCDB-D144-A543-AB8BA33557A9}" name="DOI" dataDxfId="7" dataCellStyle="Hyperlink"/>
-    <tableColumn id="8" xr3:uid="{3BA165FD-1D1B-A345-AA35-D599109FCC87}" name="Insights for Thesis" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{E3BC98A8-DF66-6B4E-8276-EBF6B58FA40E}" name="Outcomes" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{D0CB5091-71CC-C248-9A19-F90F8F2E8297}" name="Relevance" dataDxfId="4"/>
-    <tableColumn id="14" xr3:uid="{C927F29E-2777-C84F-A9EA-3EA05CD3B954}" name="Link" dataDxfId="3" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{FF6D7400-F425-4C42-9BBF-ADFBE98D0F07}" name="Reviewed?" dataDxfId="2"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{DDA40927-D99D-7944-ABBB-E062EAC00CB0}" name="Paper Title" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{7063D636-C85B-3548-A015-8D7C939D4FA5}" name="Authors" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{0A4B399A-AD2E-3048-B417-A6AB46292C0E}" name="Year" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{3ED340CA-2C59-CE48-BDF0-D7CD1022D6AA}" name="Journal Title" dataDxfId="41"/>
+    <tableColumn id="10" xr3:uid="{6613DB95-863F-B043-ABF2-28DACB82C976}" name="Journal Importance" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{CFA5C437-782F-2146-99F8-88849AC4D708}" name="Abstract" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{3BA165FD-1D1B-A345-AA35-D599109FCC87}" name="Insights for Thesis" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{E3BC98A8-DF66-6B4E-8276-EBF6B58FA40E}" name="Outcomes" dataDxfId="37"/>
+    <tableColumn id="13" xr3:uid="{D0CB5091-71CC-C248-9A19-F90F8F2E8297}" name="Relevance" dataDxfId="36"/>
+    <tableColumn id="14" xr3:uid="{C927F29E-2777-C84F-A9EA-3EA05CD3B954}" name="Link" dataDxfId="35" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{FF6D7400-F425-4C42-9BBF-ADFBE98D0F07}" name="Reviewed?" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BDB057D3-C952-D345-8F2C-B84814345F7C}" name="Network" displayName="Network" ref="A1:L21" totalsRowShown="0" dataDxfId="28">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BDB057D3-C952-D345-8F2C-B84814345F7C}" name="Network" displayName="Network" ref="A1:L21" totalsRowShown="0" dataDxfId="33">
   <autoFilter ref="A1:L21" xr:uid="{BDB057D3-C952-D345-8F2C-B84814345F7C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L21">
     <sortCondition descending="1" ref="C1:C21"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{CF32DED6-F460-BC4E-8425-9A38061898F6}" name="Paper Title" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{CCB95980-EAA8-D249-8BBC-397525A2F450}" name="Authors" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{037E5B70-94CF-D440-816F-4E3CB4C9BD23}" name="Year" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{1E353C60-E639-2940-9E11-2CA96BECA2DB}" name="Journal Title" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{4F321EEF-3C49-F549-99B7-4791D31958FF}" name="Journal Importance" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{C27CEDF0-021E-AD4C-AC46-79A57416DDAD}" name="Abstract" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{5A1165FC-0522-0E42-9695-D8A474BA3183}" name="DOI" dataDxfId="22" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{0BFB5501-86F2-9343-A561-78081AAC3D16}" name="Insights for Thesis" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{46301428-00AB-1B40-B9BD-76F9077E5805}" name="Outcomes" dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{405179D8-608B-E04F-9EFF-3BFD48149919}" name="Relevance" dataDxfId="19"/>
-    <tableColumn id="14" xr3:uid="{9C55F2EE-8819-AB4B-BBE8-87A1890AB86E}" name="Link" dataDxfId="18" dataCellStyle="Hyperlink"/>
-    <tableColumn id="9" xr3:uid="{EC72141A-19AA-6848-B1E6-106BFB0309A1}" name="Reviewed?" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{CF32DED6-F460-BC4E-8425-9A38061898F6}" name="Paper Title" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{CCB95980-EAA8-D249-8BBC-397525A2F450}" name="Authors" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{037E5B70-94CF-D440-816F-4E3CB4C9BD23}" name="Year" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{1E353C60-E639-2940-9E11-2CA96BECA2DB}" name="Journal Title" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{4F321EEF-3C49-F549-99B7-4791D31958FF}" name="Journal Importance" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{C27CEDF0-021E-AD4C-AC46-79A57416DDAD}" name="Abstract" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{5A1165FC-0522-0E42-9695-D8A474BA3183}" name="DOI" dataDxfId="26" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{0BFB5501-86F2-9343-A561-78081AAC3D16}" name="Insights for Thesis" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{46301428-00AB-1B40-B9BD-76F9077E5805}" name="Outcomes" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{405179D8-608B-E04F-9EFF-3BFD48149919}" name="Relevance" dataDxfId="23"/>
+    <tableColumn id="14" xr3:uid="{9C55F2EE-8819-AB4B-BBE8-87A1890AB86E}" name="Link" dataDxfId="22" dataCellStyle="Hyperlink"/>
+    <tableColumn id="9" xr3:uid="{EC72141A-19AA-6848-B1E6-106BFB0309A1}" name="Reviewed?" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{86F5C17F-65E7-A747-A730-2845D6297FFF}" name="Table9" displayName="Table9" ref="A1:J7" totalsRowShown="0" dataDxfId="11">
+  <autoFilter ref="A1:J7" xr:uid="{86F5C17F-65E7-A747-A730-2845D6297FFF}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{A9C5428B-4718-FF44-9FCD-0C711AC5D2EB}" name="Paper Title" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{4F22ED0F-90ED-084C-875B-D2ACFA43F0C3}" name="Authors" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{448BD838-743C-174E-8313-8B23A5A82284}" name="Topic" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{85D89CB4-8644-2B4C-AAB0-593299A9A7C6}" name="Year" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{25ECED98-A760-E94C-A8F8-8AC0125F71D1}" name="Journal Title" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{4281CF60-E364-5443-9F66-E8CC243CAFA8}" name="Journal Importance" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{7B7FE905-1B9C-5C41-84E4-BF149FCE16FA}" name="Abstract" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{0689C985-F189-B648-8024-CDA0BFD5E584}" name="Relevance" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{953D64E1-58A3-7F44-A196-F2DE65180622}" name="Link" dataDxfId="13" dataCellStyle="Hyperlink"/>
+    <tableColumn id="12" xr3:uid="{D7A66561-7B50-6B46-90CA-B3315F9B5D59}" name="Reviewed?" dataDxfId="12"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -3851,14 +5325,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{838C02D4-FEA1-2A47-B8BA-8639EEFFB0CC}">
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.5" customWidth="1"/>
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="5" width="29.5" customWidth="1"/>
-    <col min="6" max="6" width="52.1640625" customWidth="1"/>
+    <col min="6" max="6" width="97.83203125" customWidth="1"/>
     <col min="7" max="7" width="33.1640625" customWidth="1"/>
     <col min="8" max="8" width="45.1640625" customWidth="1"/>
     <col min="9" max="9" width="39.6640625" customWidth="1"/>
@@ -3883,7 +5357,7 @@
         <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
@@ -3916,10 +5390,10 @@
         <v>113</v>
       </c>
       <c r="P1" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" s="1" customFormat="1" ht="323" x14ac:dyDescent="0.2">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" s="1" customFormat="1" ht="306" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>24</v>
       </c>
@@ -3933,7 +5407,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>28</v>
@@ -3954,7 +5428,7 @@
         <v>117</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
@@ -3971,7 +5445,7 @@
         <v>100</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>101</v>
@@ -3992,7 +5466,7 @@
         <v>137</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="340" x14ac:dyDescent="0.2">
@@ -4009,7 +5483,7 @@
         <v>88</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>89</v>
@@ -4028,7 +5502,7 @@
         <v>133</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
@@ -4036,7 +5510,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="C5" s="5">
         <v>2024</v>
@@ -4045,7 +5519,7 @@
         <v>16</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>17</v>
@@ -4066,7 +5540,7 @@
         <v>115</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="356" x14ac:dyDescent="0.2">
@@ -4083,7 +5557,7 @@
         <v>41</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>42</v>
@@ -4119,7 +5593,7 @@
         <v>54</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>55</v>
@@ -4155,7 +5629,7 @@
         <v>84</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>86</v>
@@ -4177,7 +5651,7 @@
       </c>
       <c r="P8" s="5"/>
     </row>
-    <row r="9" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>91</v>
       </c>
@@ -4191,7 +5665,7 @@
         <v>93</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>94</v>
@@ -4225,7 +5699,7 @@
         <v>105</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>106</v>
@@ -4259,7 +5733,7 @@
         <v>64</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>65</v>
@@ -4280,7 +5754,7 @@
         <v>126</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="289" x14ac:dyDescent="0.2">
@@ -4295,7 +5769,7 @@
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>60</v>
@@ -4315,7 +5789,7 @@
       </c>
       <c r="P12" s="5"/>
     </row>
-    <row r="13" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>23</v>
       </c>
@@ -4329,7 +5803,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>21</v>
@@ -4365,7 +5839,7 @@
         <v>110</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>111</v>
@@ -4386,7 +5860,7 @@
         <v>139</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="221" x14ac:dyDescent="0.2">
@@ -4403,7 +5877,7 @@
         <v>32</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>33</v>
@@ -4423,7 +5897,7 @@
       </c>
       <c r="P15" s="5"/>
     </row>
-    <row r="16" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>134</v>
       </c>
@@ -4437,10 +5911,10 @@
         <v>97</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>95</v>
@@ -4459,7 +5933,7 @@
       </c>
       <c r="P16" s="5"/>
     </row>
-    <row r="17" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>72</v>
       </c>
@@ -4471,10 +5945,10 @@
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -4505,10 +5979,10 @@
         <v>26</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>14</v>
@@ -4529,10 +6003,10 @@
     </row>
     <row r="19" spans="1:16" ht="388" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="C19" s="5">
         <v>2019</v>
@@ -4541,13 +6015,13 @@
         <v>262</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -4559,7 +6033,7 @@
         <v>2</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="P19" s="5"/>
     </row>
@@ -4575,7 +6049,7 @@
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>59</v>
@@ -4594,30 +6068,30 @@
         <v>124</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="404" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="C21" s="5">
         <v>2018</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -4629,10 +6103,10 @@
         <v>2</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="P21" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="388" x14ac:dyDescent="0.2">
@@ -4649,7 +6123,7 @@
         <v>69</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>70</v>
@@ -4670,7 +6144,7 @@
         <v>127</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="221" x14ac:dyDescent="0.2">
@@ -4685,7 +6159,7 @@
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>36</v>
@@ -4701,7 +6175,7 @@
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="5" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="N23" s="5">
         <v>3</v>
@@ -4710,27 +6184,27 @@
         <v>119</v>
       </c>
       <c r="P23" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="323" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="C24" s="5">
         <v>2009</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -4744,7 +6218,7 @@
       </c>
       <c r="O24" s="5"/>
       <c r="P24" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="255" x14ac:dyDescent="0.2">
@@ -4761,7 +6235,7 @@
         <v>49</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>50</v>
@@ -4782,15 +6256,15 @@
         <v>123</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="289" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="C26" s="5">
         <v>2008</v>
@@ -4799,10 +6273,10 @@
         <v>235</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
@@ -4815,10 +6289,10 @@
         <v>3</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="P26" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="272" x14ac:dyDescent="0.2">
@@ -4835,7 +6309,7 @@
         <v>46</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>45</v>
@@ -4844,7 +6318,7 @@
         <v>47</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
@@ -4858,12 +6332,12 @@
         <v>121</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>76</v>
@@ -4875,7 +6349,7 @@
         <v>49</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>77</v>
@@ -4896,27 +6370,27 @@
         <v>130</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="323" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="C29" s="5">
         <v>2003</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
@@ -4929,10 +6403,10 @@
         <v>1</v>
       </c>
       <c r="O29" s="8" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="P29" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
@@ -4949,7 +6423,7 @@
         <v>80</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>81</v>
@@ -4971,22 +6445,22 @@
     </row>
     <row r="31" spans="1:16" ht="323" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="C31" s="5">
         <v>2001</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
@@ -4999,15 +6473,15 @@
         <v>2</v>
       </c>
       <c r="O31" s="8" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="P31" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="289" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>74</v>
@@ -5015,7 +6489,7 @@
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>75</v>
@@ -5037,227 +6511,421 @@
     </row>
     <row r="33" spans="1:16" ht="238" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="C33" s="28">
+        <v>602</v>
+      </c>
+      <c r="C33" s="5">
         <v>2006</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>80</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
-      <c r="K33" s="29"/>
+      <c r="K33" s="11"/>
       <c r="L33" s="5"/>
       <c r="M33" s="5"/>
       <c r="N33" s="5">
         <v>2</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="P33" s="5"/>
     </row>
     <row r="34" spans="1:16" ht="289" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>617</v>
-      </c>
-      <c r="C34" s="28">
+        <v>606</v>
+      </c>
+      <c r="C34" s="5">
         <v>2018</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
-      <c r="K34" s="29"/>
+      <c r="K34" s="11"/>
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
       <c r="N34" s="5">
         <v>2</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="P34" s="5"/>
     </row>
     <row r="35" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>621</v>
-      </c>
-      <c r="C35" s="28">
+        <v>610</v>
+      </c>
+      <c r="C35" s="5">
         <v>2005</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
-      <c r="K35" s="29"/>
+      <c r="K35" s="11"/>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
       <c r="N35" s="5">
         <v>2</v>
       </c>
       <c r="O35" s="8" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="P35" s="5"/>
     </row>
     <row r="36" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>626</v>
-      </c>
-      <c r="C36" s="28">
+        <v>615</v>
+      </c>
+      <c r="C36" s="5">
         <v>2002</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
-      <c r="K36" s="29"/>
+      <c r="K36" s="11"/>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
       <c r="N36" s="5">
         <v>1</v>
       </c>
       <c r="O36" s="8" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="P36" s="5"/>
     </row>
     <row r="37" spans="1:16" ht="388" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>631</v>
-      </c>
-      <c r="C37" s="28">
+        <v>620</v>
+      </c>
+      <c r="C37" s="5">
         <v>2006</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
-      <c r="K37" s="29"/>
+      <c r="K37" s="11"/>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
       <c r="N37" s="5">
         <v>2</v>
       </c>
       <c r="O37" s="8" t="s">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="P37" s="5"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A38" s="5"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
+    <row r="38" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
+        <v>855</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="C38" s="5">
+        <v>2010</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>857</v>
+      </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
-      <c r="K38" s="29"/>
+      <c r="K38" s="11"/>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
+      <c r="O38" s="8" t="s">
+        <v>858</v>
+      </c>
       <c r="P38" s="5"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
+    <row r="39" spans="1:16" ht="204" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
+        <v>859</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="C39" s="5">
+        <v>2007</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>861</v>
+      </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
-      <c r="K39" s="29"/>
+      <c r="K39" s="11"/>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
-      <c r="O39" s="5"/>
+      <c r="O39" s="8" t="s">
+        <v>862</v>
+      </c>
       <c r="P39" s="5"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
+    <row r="40" spans="1:16" ht="306" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="C40" s="5">
+        <v>2005</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>865</v>
+      </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
-      <c r="K40" s="29"/>
+      <c r="K40" s="11"/>
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
+      <c r="O40" s="8" t="s">
+        <v>866</v>
+      </c>
       <c r="P40" s="5"/>
+    </row>
+    <row r="41" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
+        <v>870</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="C41" s="32"/>
+      <c r="D41" s="5" t="s">
+        <v>867</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="33"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="P41" s="5"/>
+    </row>
+    <row r="42" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+      <c r="A42" s="5" t="s">
+        <v>877</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>878</v>
+      </c>
+      <c r="C42" s="32">
+        <v>2015</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>879</v>
+      </c>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="8" t="s">
+        <v>880</v>
+      </c>
+      <c r="P42" s="5"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="33"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A44" s="5"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="33"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A45" s="5"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="33"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A46" s="5"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="33"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A47" s="5"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="33"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5307,10 +6975,15 @@
     <hyperlink ref="O35" r:id="rId44" xr:uid="{F472CD50-7CE9-C344-972C-6F502714E7F5}"/>
     <hyperlink ref="O36" r:id="rId45" xr:uid="{C0B647A1-10C5-BA46-B92F-E1F17C6ADC7E}"/>
     <hyperlink ref="O37" r:id="rId46" xr:uid="{02E2DF65-E6DD-714D-B0DE-019E6AADC004}"/>
+    <hyperlink ref="O38" r:id="rId47" xr:uid="{6D476616-2260-E248-80F2-FCDF3A55E8D3}"/>
+    <hyperlink ref="O39" r:id="rId48" xr:uid="{C7D054F1-2F94-3E45-8CB4-548EF707FBAE}"/>
+    <hyperlink ref="O40" r:id="rId49" xr:uid="{93E23DF4-8481-1340-B308-15974252E9AF}"/>
+    <hyperlink ref="O41" r:id="rId50" xr:uid="{F9F3864F-E611-A346-88F0-7C256642A2FC}"/>
+    <hyperlink ref="O42" r:id="rId51" xr:uid="{FF1C1552-26CB-F746-A6A3-53F6DB14C917}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId47"/>
+    <tablePart r:id="rId52"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -5348,11 +7021,214 @@
               </x14:cfvo>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>N2:N40</xm:sqref>
+          <xm:sqref>N2:N47</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EB5083B-93D3-2C47-B0A2-2D8EBB565AE4}">
+  <dimension ref="B2:K13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4.33203125" style="12" customWidth="1"/>
+    <col min="2" max="2" width="27.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.83203125" style="12"/>
+    <col min="5" max="5" width="27.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:11" ht="27" x14ac:dyDescent="0.35">
+      <c r="B2" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+    </row>
+    <row r="3" spans="2:11" ht="4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+    </row>
+    <row r="4" spans="2:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="B4" s="27" t="s">
+        <v>515</v>
+      </c>
+      <c r="C4" s="28"/>
+      <c r="E4" s="27" t="s">
+        <v>522</v>
+      </c>
+      <c r="F4" s="29"/>
+      <c r="G4" s="28"/>
+      <c r="I4" s="27" t="s">
+        <v>554</v>
+      </c>
+      <c r="J4" s="29"/>
+      <c r="K4" s="24"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B5" s="15" t="s">
+        <v>556</v>
+      </c>
+      <c r="C5" s="16">
+        <f>ROWS(Proximity[])</f>
+        <v>46</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>523</v>
+      </c>
+      <c r="F5" s="12">
+        <f>COUNTIF(Proximity[Relevance],3) + COUNTIF(Success[Relevance],3) + COUNTIF(Support[Relevance],3) + COUNTIF(Ecosystem[Relevance],3) + COUNTIF(Network[Relevance],3)</f>
+        <v>55</v>
+      </c>
+      <c r="G5" s="21">
+        <f>F5/$C$13</f>
+        <v>0.25821596244131456</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>555</v>
+      </c>
+      <c r="J5" s="12">
+        <f>COUNTIF(Proximity[Reviewed?],"DONE") + COUNTIF(Success[Reviewed?],"DONE") + COUNTIF(Support[Reviewed?],"DONE") + COUNTIF(Ecosystem[Reviewed?],"DONE") + COUNTIF(Network[Reviewed?],"DONE")</f>
+        <v>29</v>
+      </c>
+      <c r="K5" s="21">
+        <f>J5/$C$13</f>
+        <v>0.13615023474178403</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B6" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="C6" s="16">
+        <f>ROWS(Success[])</f>
+        <v>27</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="F6" s="12">
+        <f>COUNTIF(Proximity[Relevance],2) + COUNTIF(Success[Relevance],2) + COUNTIF(Support[Relevance],2) + COUNTIF(Ecosystem[Relevance],2) + COUNTIF(Network[Relevance],2)</f>
+        <v>40</v>
+      </c>
+      <c r="G6" s="21">
+        <f t="shared" ref="G6:G7" si="0">F6/$C$13</f>
+        <v>0.18779342723004694</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>553</v>
+      </c>
+      <c r="J6" s="22">
+        <f>C13-J5</f>
+        <v>184</v>
+      </c>
+      <c r="K6" s="23">
+        <f>J6/$C$13</f>
+        <v>0.863849765258216</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B7" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="C7" s="16">
+        <f>ROWS(Support[])</f>
+        <v>17</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>525</v>
+      </c>
+      <c r="F7" s="22">
+        <f>COUNTIF(Proximity[Relevance],1) + COUNTIF(Success[Relevance],1) + COUNTIF(Support[Relevance],1) + COUNTIF(Ecosystem[Relevance],1) + COUNTIF(Network[Relevance],1)</f>
+        <v>18</v>
+      </c>
+      <c r="G7" s="23">
+        <f t="shared" si="0"/>
+        <v>8.4507042253521125E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B8" s="15" t="s">
+        <v>826</v>
+      </c>
+      <c r="C8" s="16">
+        <f>ROWS(VentureCapital[])</f>
+        <v>50</v>
+      </c>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="31"/>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B9" s="15" t="s">
+        <v>923</v>
+      </c>
+      <c r="C9" s="16">
+        <f>ROWS(StartupFinancing[])</f>
+        <v>5</v>
+      </c>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="31"/>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B10" s="15" t="s">
+        <v>827</v>
+      </c>
+      <c r="C10" s="16">
+        <f>ROWS(VCTheory[])</f>
+        <v>27</v>
+      </c>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="31"/>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B11" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="C11" s="16">
+        <f>ROWS(Ecosystem[])</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="17" t="s">
+        <v>520</v>
+      </c>
+      <c r="C12" s="18">
+        <f>ROWS(Network[])</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="19" t="s">
+        <v>521</v>
+      </c>
+      <c r="C13" s="20">
+        <f>SUM(C5:C12)</f>
+        <v>213</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="I4:J4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5365,7 +7241,7 @@
     <col min="2" max="2" width="28.1640625" customWidth="1"/>
     <col min="3" max="3" width="22.1640625" customWidth="1"/>
     <col min="4" max="5" width="18.1640625" customWidth="1"/>
-    <col min="6" max="6" width="50.1640625" customWidth="1"/>
+    <col min="6" max="6" width="80.1640625" customWidth="1"/>
     <col min="7" max="7" width="29" customWidth="1"/>
     <col min="8" max="9" width="27" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
@@ -5386,7 +7262,7 @@
         <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -5395,10 +7271,10 @@
         <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
@@ -5407,7 +7283,7 @@
         <v>113</v>
       </c>
       <c r="L1" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
@@ -5424,7 +7300,7 @@
         <v>144</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>145</v>
@@ -5442,7 +7318,7 @@
       </c>
       <c r="L2" s="5"/>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="388" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="356" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>148</v>
       </c>
@@ -5456,7 +7332,7 @@
         <v>150</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>151</v>
@@ -5473,10 +7349,10 @@
         <v>153</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="255" x14ac:dyDescent="0.2">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>154</v>
       </c>
@@ -5490,14 +7366,14 @@
         <v>20</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>155</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5">
@@ -5522,7 +7398,7 @@
         <v>165</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>166</v>
@@ -5539,25 +7415,25 @@
         <v>168</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="289" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="C6" s="5">
         <v>2024</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -5566,11 +7442,11 @@
         <v>2</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="404" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>158</v>
       </c>
@@ -5584,7 +7460,7 @@
         <v>160</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>161</v>
@@ -5600,7 +7476,7 @@
       </c>
       <c r="L7" s="5"/>
     </row>
-    <row r="8" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="372" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>169</v>
       </c>
@@ -5614,7 +7490,7 @@
         <v>171</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>172</v>
@@ -5631,10 +7507,10 @@
         <v>174</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="372" x14ac:dyDescent="0.2">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="323" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>175</v>
       </c>
@@ -5648,7 +7524,7 @@
         <v>88</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>177</v>
@@ -5666,7 +7542,7 @@
       </c>
       <c r="L9" s="5"/>
     </row>
-    <row r="10" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="356" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>180</v>
       </c>
@@ -5680,7 +7556,7 @@
         <v>97</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>182</v>
@@ -5697,7 +7573,7 @@
         <v>184</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
@@ -5712,7 +7588,7 @@
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>187</v>
@@ -5742,7 +7618,7 @@
         <v>191</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>192</v>
@@ -5772,7 +7648,7 @@
         <v>196</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>197</v>
@@ -5789,7 +7665,7 @@
         <v>199</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="221" x14ac:dyDescent="0.2">
@@ -5806,7 +7682,7 @@
         <v>319</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>318</v>
@@ -5823,10 +7699,10 @@
         <v>321</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="289" x14ac:dyDescent="0.2">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>206</v>
       </c>
@@ -5840,7 +7716,7 @@
         <v>171</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>208</v>
@@ -5857,10 +7733,10 @@
         <v>210</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="356" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>200</v>
       </c>
@@ -5874,7 +7750,7 @@
         <v>202</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>203</v>
@@ -5892,7 +7768,7 @@
       </c>
       <c r="L16" s="5"/>
     </row>
-    <row r="17" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="388" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>211</v>
       </c>
@@ -5904,7 +7780,7 @@
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>213</v>
@@ -5920,7 +7796,7 @@
       </c>
       <c r="L17" s="5"/>
     </row>
-    <row r="18" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="356" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>305</v>
       </c>
@@ -5934,7 +7810,7 @@
         <v>307</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>308</v>
@@ -5952,7 +7828,7 @@
       </c>
       <c r="L18" s="5"/>
     </row>
-    <row r="19" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="356" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>311</v>
       </c>
@@ -5966,7 +7842,7 @@
         <v>290</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>313</v>
@@ -5983,10 +7859,10 @@
         <v>315</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="272" x14ac:dyDescent="0.2">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="221" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>300</v>
       </c>
@@ -6000,7 +7876,7 @@
         <v>301</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>302</v>
@@ -6030,7 +7906,7 @@
         <v>223</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>225</v>
@@ -6047,7 +7923,7 @@
         <v>226</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="340" x14ac:dyDescent="0.2">
@@ -6064,7 +7940,7 @@
         <v>217</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>218</v>
@@ -6096,7 +7972,7 @@
         <v>296</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>297</v>
@@ -6114,7 +7990,7 @@
       </c>
       <c r="L23" s="5"/>
     </row>
-    <row r="24" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="221" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>282</v>
       </c>
@@ -6128,7 +8004,7 @@
         <v>283</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>285</v>
@@ -6146,7 +8022,7 @@
       </c>
       <c r="L24" s="5"/>
     </row>
-    <row r="25" spans="1:12" ht="272" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>288</v>
       </c>
@@ -6160,7 +8036,7 @@
         <v>290</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>291</v>
@@ -6177,10 +8053,10 @@
         <v>293</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="404" x14ac:dyDescent="0.2">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="255" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>276</v>
       </c>
@@ -6210,7 +8086,7 @@
       </c>
       <c r="L26" s="5"/>
     </row>
-    <row r="27" spans="1:12" ht="404" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="289" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>270</v>
       </c>
@@ -6224,7 +8100,7 @@
         <v>272</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>273</v>
@@ -6242,7 +8118,7 @@
       </c>
       <c r="L27" s="5"/>
     </row>
-    <row r="28" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="388" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>227</v>
       </c>
@@ -6343,6 +8219,2147 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{637BB0C1-D456-264E-8BF7-AD0468881253}">
+  <dimension ref="A1:I51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="34.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" customWidth="1"/>
+    <col min="5" max="5" width="19.1640625" customWidth="1"/>
+    <col min="6" max="6" width="19.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="82.1640625" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="112" x14ac:dyDescent="0.2">
+      <c r="A2" s="25" t="s">
+        <v>626</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>708</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>627</v>
+      </c>
+      <c r="D2" s="25">
+        <v>2001</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>628</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>629</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>709</v>
+      </c>
+      <c r="I2" s="25"/>
+    </row>
+    <row r="3" spans="1:9" ht="144" x14ac:dyDescent="0.2">
+      <c r="A3" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>708</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>631</v>
+      </c>
+      <c r="D3" s="25">
+        <v>1990</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>632</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="I3" s="25"/>
+    </row>
+    <row r="4" spans="1:9" ht="128" x14ac:dyDescent="0.2">
+      <c r="A4" s="25" t="s">
+        <v>633</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25" t="s">
+        <v>634</v>
+      </c>
+      <c r="D4" s="25">
+        <v>2005</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>635</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="I4" s="25"/>
+    </row>
+    <row r="5" spans="1:9" ht="320" x14ac:dyDescent="0.2">
+      <c r="A5" s="25" t="s">
+        <v>636</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>708</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>637</v>
+      </c>
+      <c r="D5" s="25">
+        <v>1996</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>638</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="I5" s="25"/>
+    </row>
+    <row r="6" spans="1:9" ht="256" x14ac:dyDescent="0.2">
+      <c r="A6" s="25" t="s">
+        <v>639</v>
+      </c>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25" t="s">
+        <v>640</v>
+      </c>
+      <c r="D6" s="25">
+        <v>2005</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>475</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>641</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="I6" s="25"/>
+    </row>
+    <row r="7" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="25" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25" t="s">
+        <v>642</v>
+      </c>
+      <c r="D7" s="25">
+        <v>2011</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>600</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="I7" s="25"/>
+    </row>
+    <row r="8" spans="1:9" ht="304" x14ac:dyDescent="0.2">
+      <c r="A8" s="25" t="s">
+        <v>643</v>
+      </c>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25" t="s">
+        <v>644</v>
+      </c>
+      <c r="D8" s="25">
+        <v>2016</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>596</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>645</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>715</v>
+      </c>
+      <c r="I8" s="25"/>
+    </row>
+    <row r="9" spans="1:9" ht="208" x14ac:dyDescent="0.2">
+      <c r="A9" s="25" t="s">
+        <v>646</v>
+      </c>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25" t="s">
+        <v>647</v>
+      </c>
+      <c r="D9" s="25">
+        <v>2000</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>648</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>649</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="I9" s="25"/>
+    </row>
+    <row r="10" spans="1:9" ht="144" x14ac:dyDescent="0.2">
+      <c r="A10" s="25" t="s">
+        <v>650</v>
+      </c>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="D10" s="25">
+        <v>2014</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>652</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>653</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>717</v>
+      </c>
+      <c r="I10" s="25"/>
+    </row>
+    <row r="11" spans="1:9" ht="128" x14ac:dyDescent="0.2">
+      <c r="A11" s="25" t="s">
+        <v>654</v>
+      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25" t="s">
+        <v>655</v>
+      </c>
+      <c r="D11" s="25">
+        <v>1998</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>656</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="I11" s="25"/>
+    </row>
+    <row r="12" spans="1:9" ht="128" x14ac:dyDescent="0.2">
+      <c r="A12" s="25" t="s">
+        <v>657</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>708</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>658</v>
+      </c>
+      <c r="D12" s="25">
+        <v>2000</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>659</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>660</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="I12" s="25"/>
+    </row>
+    <row r="13" spans="1:9" ht="144" x14ac:dyDescent="0.2">
+      <c r="A13" s="25" t="s">
+        <v>661</v>
+      </c>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25" t="s">
+        <v>662</v>
+      </c>
+      <c r="D13" s="25">
+        <v>2008</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>663</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="I13" s="25"/>
+    </row>
+    <row r="14" spans="1:9" ht="208" x14ac:dyDescent="0.2">
+      <c r="A14" s="25" t="s">
+        <v>664</v>
+      </c>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25" t="s">
+        <v>665</v>
+      </c>
+      <c r="D14" s="25">
+        <v>2010</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>666</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="I14" s="25"/>
+    </row>
+    <row r="15" spans="1:9" ht="144" x14ac:dyDescent="0.2">
+      <c r="A15" s="25" t="s">
+        <v>669</v>
+      </c>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25" t="s">
+        <v>668</v>
+      </c>
+      <c r="D15" s="25">
+        <v>1995</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>475</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>667</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="I15" s="25"/>
+    </row>
+    <row r="16" spans="1:9" ht="224" x14ac:dyDescent="0.2">
+      <c r="A16" s="25" t="s">
+        <v>670</v>
+      </c>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25" t="s">
+        <v>671</v>
+      </c>
+      <c r="D16" s="25">
+        <v>2012</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>672</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="I16" s="25"/>
+    </row>
+    <row r="17" spans="1:9" ht="272" x14ac:dyDescent="0.2">
+      <c r="A17" s="25" t="s">
+        <v>673</v>
+      </c>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25" t="s">
+        <v>674</v>
+      </c>
+      <c r="D17" s="25">
+        <v>2006</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>675</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="I17" s="25"/>
+    </row>
+    <row r="18" spans="1:9" ht="128" x14ac:dyDescent="0.2">
+      <c r="A18" s="25" t="s">
+        <v>676</v>
+      </c>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25" t="s">
+        <v>474</v>
+      </c>
+      <c r="D18" s="25">
+        <v>2012</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>475</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>677</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="I18" s="25"/>
+    </row>
+    <row r="19" spans="1:9" ht="160" x14ac:dyDescent="0.2">
+      <c r="A19" s="25" t="s">
+        <v>678</v>
+      </c>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25" t="s">
+        <v>679</v>
+      </c>
+      <c r="D19" s="25">
+        <v>2002</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>468</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G19" s="25" t="s">
+        <v>680</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="I19" s="25"/>
+    </row>
+    <row r="20" spans="1:9" ht="176" x14ac:dyDescent="0.2">
+      <c r="A20" s="25" t="s">
+        <v>681</v>
+      </c>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25" t="s">
+        <v>682</v>
+      </c>
+      <c r="D20" s="25">
+        <v>2011</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25" t="s">
+        <v>683</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="I20" s="25"/>
+    </row>
+    <row r="21" spans="1:9" ht="240" x14ac:dyDescent="0.2">
+      <c r="A21" s="25" t="s">
+        <v>684</v>
+      </c>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25" t="s">
+        <v>685</v>
+      </c>
+      <c r="D21" s="25">
+        <v>2005</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25" t="s">
+        <v>686</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="I21" s="25"/>
+    </row>
+    <row r="22" spans="1:9" ht="256" x14ac:dyDescent="0.2">
+      <c r="A22" s="25" t="s">
+        <v>687</v>
+      </c>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25" t="s">
+        <v>688</v>
+      </c>
+      <c r="D22" s="25">
+        <v>2017</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>689</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G22" s="25" t="s">
+        <v>690</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="I22" s="25"/>
+    </row>
+    <row r="23" spans="1:9" ht="256" x14ac:dyDescent="0.2">
+      <c r="A23" s="25" t="s">
+        <v>691</v>
+      </c>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25" t="s">
+        <v>692</v>
+      </c>
+      <c r="D23" s="25">
+        <v>2015</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>693</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="I23" s="25"/>
+    </row>
+    <row r="24" spans="1:9" ht="192" x14ac:dyDescent="0.2">
+      <c r="A24" s="26" t="s">
+        <v>694</v>
+      </c>
+      <c r="B24" s="26"/>
+      <c r="C24" s="25" t="s">
+        <v>695</v>
+      </c>
+      <c r="D24" s="25">
+        <v>2018</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25" t="s">
+        <v>696</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="I24" s="25"/>
+    </row>
+    <row r="25" spans="1:9" ht="256" x14ac:dyDescent="0.2">
+      <c r="A25" s="25" t="s">
+        <v>260</v>
+      </c>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25" t="s">
+        <v>472</v>
+      </c>
+      <c r="D25" s="25">
+        <v>2011</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="F25" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G25" s="25" t="s">
+        <v>697</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="I25" s="25"/>
+    </row>
+    <row r="26" spans="1:9" ht="102" x14ac:dyDescent="0.2">
+      <c r="A26" s="25" t="s">
+        <v>698</v>
+      </c>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25" t="s">
+        <v>699</v>
+      </c>
+      <c r="D26" s="25">
+        <v>2001</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>700</v>
+      </c>
+      <c r="F26" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G26" s="25"/>
+      <c r="H26" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="I26" s="25"/>
+    </row>
+    <row r="27" spans="1:9" ht="256" x14ac:dyDescent="0.2">
+      <c r="A27" s="25" t="s">
+        <v>701</v>
+      </c>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25" t="s">
+        <v>702</v>
+      </c>
+      <c r="D27" s="25">
+        <v>2004</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G27" s="25" t="s">
+        <v>703</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="I27" s="25"/>
+    </row>
+    <row r="28" spans="1:9" ht="304" x14ac:dyDescent="0.2">
+      <c r="A28" s="25" t="s">
+        <v>704</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>708</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>705</v>
+      </c>
+      <c r="D28" s="25">
+        <v>1998</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="F28" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G28" s="25" t="s">
+        <v>706</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="I28" s="25"/>
+    </row>
+    <row r="29" spans="1:9" ht="112" x14ac:dyDescent="0.2">
+      <c r="A29" s="25" t="s">
+        <v>394</v>
+      </c>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25" t="s">
+        <v>395</v>
+      </c>
+      <c r="D29" s="25">
+        <v>1994</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>396</v>
+      </c>
+      <c r="F29" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G29" s="25" t="s">
+        <v>795</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>796</v>
+      </c>
+      <c r="I29" s="25"/>
+    </row>
+    <row r="30" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A30" s="25" t="s">
+        <v>797</v>
+      </c>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25" t="s">
+        <v>798</v>
+      </c>
+      <c r="D30" s="25">
+        <v>2000</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="F30" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G30" s="25" t="s">
+        <v>799</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="I30" s="25"/>
+    </row>
+    <row r="31" spans="1:9" ht="380" x14ac:dyDescent="0.2">
+      <c r="A31" s="25" t="s">
+        <v>803</v>
+      </c>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25" t="s">
+        <v>802</v>
+      </c>
+      <c r="D31" s="25">
+        <v>1985</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G31" s="25" t="s">
+        <v>801</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="I31" s="25"/>
+    </row>
+    <row r="32" spans="1:9" ht="192" x14ac:dyDescent="0.2">
+      <c r="A32" s="25" t="s">
+        <v>805</v>
+      </c>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25" t="s">
+        <v>806</v>
+      </c>
+      <c r="D32" s="25">
+        <v>1999</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F32" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G32" s="25" t="s">
+        <v>807</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="I32" s="25"/>
+    </row>
+    <row r="33" spans="1:9" ht="176" x14ac:dyDescent="0.2">
+      <c r="A33" s="25" t="s">
+        <v>809</v>
+      </c>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25" t="s">
+        <v>810</v>
+      </c>
+      <c r="D33" s="25">
+        <v>2011</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F33" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G33" s="25" t="s">
+        <v>811</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>812</v>
+      </c>
+      <c r="I33" s="25"/>
+    </row>
+    <row r="34" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A34" s="25" t="s">
+        <v>813</v>
+      </c>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25" t="s">
+        <v>814</v>
+      </c>
+      <c r="D34" s="25">
+        <v>1992</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="F34" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G34" s="25" t="s">
+        <v>815</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="I34" s="25"/>
+    </row>
+    <row r="35" spans="1:9" ht="144" x14ac:dyDescent="0.2">
+      <c r="A35" s="25" t="s">
+        <v>423</v>
+      </c>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="D35" s="25">
+        <v>2007</v>
+      </c>
+      <c r="E35" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F35" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G35" s="25" t="s">
+        <v>817</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>818</v>
+      </c>
+      <c r="I35" s="25"/>
+    </row>
+    <row r="36" spans="1:9" ht="128" x14ac:dyDescent="0.2">
+      <c r="A36" s="25" t="s">
+        <v>820</v>
+      </c>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25" t="s">
+        <v>821</v>
+      </c>
+      <c r="D36" s="25">
+        <v>2010</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="F36" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G36" s="25" t="s">
+        <v>822</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="I36" s="25"/>
+    </row>
+    <row r="37" spans="1:9" ht="176" x14ac:dyDescent="0.2">
+      <c r="A37" s="25" t="s">
+        <v>823</v>
+      </c>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25" t="s">
+        <v>824</v>
+      </c>
+      <c r="D37" s="25">
+        <v>2011</v>
+      </c>
+      <c r="E37" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="F37" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G37" s="25" t="s">
+        <v>825</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="I37" s="25"/>
+    </row>
+    <row r="38" spans="1:9" ht="112" x14ac:dyDescent="0.2">
+      <c r="A38" s="25" t="s">
+        <v>829</v>
+      </c>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25" t="s">
+        <v>830</v>
+      </c>
+      <c r="D38" s="25">
+        <v>2017</v>
+      </c>
+      <c r="E38" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="F38" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G38" s="25" t="s">
+        <v>831</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="I38" s="25"/>
+    </row>
+    <row r="39" spans="1:9" ht="128" x14ac:dyDescent="0.2">
+      <c r="A39" s="25" t="s">
+        <v>833</v>
+      </c>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25" t="s">
+        <v>834</v>
+      </c>
+      <c r="D39" s="25">
+        <v>1995</v>
+      </c>
+      <c r="E39" s="25" t="s">
+        <v>475</v>
+      </c>
+      <c r="F39" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G39" s="25" t="s">
+        <v>836</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>837</v>
+      </c>
+      <c r="I39" s="25"/>
+    </row>
+    <row r="40" spans="1:9" ht="144" x14ac:dyDescent="0.2">
+      <c r="A40" s="25" t="s">
+        <v>835</v>
+      </c>
+      <c r="B40" s="25"/>
+      <c r="C40" s="25" t="s">
+        <v>840</v>
+      </c>
+      <c r="D40" s="25">
+        <v>2007</v>
+      </c>
+      <c r="E40" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="F40" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G40" s="25" t="s">
+        <v>839</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>838</v>
+      </c>
+      <c r="I40" s="25"/>
+    </row>
+    <row r="41" spans="1:9" ht="192" x14ac:dyDescent="0.2">
+      <c r="A41" s="25" t="s">
+        <v>842</v>
+      </c>
+      <c r="B41" s="25"/>
+      <c r="C41" s="25" t="s">
+        <v>688</v>
+      </c>
+      <c r="D41" s="25">
+        <v>2006</v>
+      </c>
+      <c r="E41" s="25" t="s">
+        <v>689</v>
+      </c>
+      <c r="F41" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G41" s="25" t="s">
+        <v>841</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>843</v>
+      </c>
+      <c r="I41" s="25"/>
+    </row>
+    <row r="42" spans="1:9" ht="176" x14ac:dyDescent="0.2">
+      <c r="A42" s="25" t="s">
+        <v>844</v>
+      </c>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25" t="s">
+        <v>845</v>
+      </c>
+      <c r="D42" s="25">
+        <v>1989</v>
+      </c>
+      <c r="E42" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="F42" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G42" s="25" t="s">
+        <v>846</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>847</v>
+      </c>
+      <c r="I42" s="25"/>
+    </row>
+    <row r="43" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A43" s="25" t="s">
+        <v>848</v>
+      </c>
+      <c r="B43" s="25"/>
+      <c r="C43" s="25" t="s">
+        <v>849</v>
+      </c>
+      <c r="D43" s="25">
+        <v>1989</v>
+      </c>
+      <c r="E43" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="F43" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G43" s="25" t="s">
+        <v>850</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>851</v>
+      </c>
+      <c r="I43" s="25"/>
+    </row>
+    <row r="44" spans="1:9" ht="128" x14ac:dyDescent="0.2">
+      <c r="A44" s="25" t="s">
+        <v>852</v>
+      </c>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25" t="s">
+        <v>853</v>
+      </c>
+      <c r="D44" s="25">
+        <v>2004</v>
+      </c>
+      <c r="E44" s="25" t="s">
+        <v>475</v>
+      </c>
+      <c r="F44" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G44" s="25" t="s">
+        <v>854</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>886</v>
+      </c>
+      <c r="I44" s="25"/>
+    </row>
+    <row r="45" spans="1:9" ht="208" x14ac:dyDescent="0.2">
+      <c r="A45" s="25" t="s">
+        <v>881</v>
+      </c>
+      <c r="B45" s="25"/>
+      <c r="C45" s="25" t="s">
+        <v>882</v>
+      </c>
+      <c r="D45" s="25">
+        <v>2014</v>
+      </c>
+      <c r="E45" s="25" t="s">
+        <v>883</v>
+      </c>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25" t="s">
+        <v>884</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>885</v>
+      </c>
+      <c r="I45" s="25"/>
+    </row>
+    <row r="46" spans="1:9" ht="224" x14ac:dyDescent="0.2">
+      <c r="A46" s="5" t="s">
+        <v>916</v>
+      </c>
+      <c r="B46" s="25"/>
+      <c r="C46" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="D46" s="25">
+        <v>2020</v>
+      </c>
+      <c r="E46" s="25" t="s">
+        <v>917</v>
+      </c>
+      <c r="F46" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G46" s="25" t="s">
+        <v>918</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>914</v>
+      </c>
+      <c r="I46" s="25"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A47" s="25"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="25"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A48" s="25"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="25"/>
+      <c r="I48" s="25"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A49" s="25"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="25"/>
+      <c r="H49" s="25"/>
+      <c r="I49" s="25"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A50" s="25"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="25"/>
+      <c r="I50" s="25"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A51" s="25"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="25"/>
+      <c r="H51" s="25"/>
+      <c r="I51" s="25"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{8FC75F97-7131-8643-902F-521611E7CE51}"/>
+    <hyperlink ref="H3" r:id="rId2" xr:uid="{2A70E3BB-2696-D64A-9349-78C01F4C205F}"/>
+    <hyperlink ref="H4" r:id="rId3" xr:uid="{754C8A31-5C36-3544-AA8A-969EE4D95563}"/>
+    <hyperlink ref="H5" r:id="rId4" xr:uid="{0C06C21C-2242-7D4A-87B5-59558A9C28E2}"/>
+    <hyperlink ref="H6" r:id="rId5" xr:uid="{AADDD2F6-D5D7-4E40-9CF4-409A0B38457F}"/>
+    <hyperlink ref="H7" r:id="rId6" xr:uid="{4E185D3A-E1DE-A041-86C1-4E6CF1707C4E}"/>
+    <hyperlink ref="H9" r:id="rId7" xr:uid="{C53E06EF-7974-344E-88E1-33783CFA800D}"/>
+    <hyperlink ref="H10" r:id="rId8" xr:uid="{37E3F1D7-E75F-E744-B7E6-D8A37A1C98B4}"/>
+    <hyperlink ref="H11" r:id="rId9" xr:uid="{692CE8E1-5913-7141-B795-754D0484BD4C}"/>
+    <hyperlink ref="H12" r:id="rId10" xr:uid="{F02DE70E-1CD9-904D-938E-4EB5D39CBE29}"/>
+    <hyperlink ref="H13" r:id="rId11" xr:uid="{EAD0C5EC-DEFC-484E-B85A-189206C6D7C4}"/>
+    <hyperlink ref="H14" r:id="rId12" xr:uid="{1DC03100-9A48-B24E-8BA2-56CBF77E8AF7}"/>
+    <hyperlink ref="H15" r:id="rId13" xr:uid="{0F717A85-5CB6-2F45-A496-3C69EA8D274E}"/>
+    <hyperlink ref="H16" r:id="rId14" xr:uid="{D63010FE-51C1-7543-A009-24EAE95F9D1D}"/>
+    <hyperlink ref="H17" r:id="rId15" xr:uid="{CC40BB20-38FB-AE45-BF6F-42C738D6E064}"/>
+    <hyperlink ref="H18" r:id="rId16" xr:uid="{80ED226C-6338-9943-B4F4-EEFB6499FDE7}"/>
+    <hyperlink ref="H19" r:id="rId17" xr:uid="{45B39431-41B0-B540-B6F8-108A17993068}"/>
+    <hyperlink ref="H20" r:id="rId18" xr:uid="{5A79FEA0-255D-FC4D-898F-9937A22525A3}"/>
+    <hyperlink ref="H21" r:id="rId19" xr:uid="{09F4EAE0-FC7F-6F4A-93F0-87D4A412884D}"/>
+    <hyperlink ref="H22" r:id="rId20" xr:uid="{50B4B2C6-8C90-714B-A28C-60AD9A474D92}"/>
+    <hyperlink ref="H23" r:id="rId21" xr:uid="{8D6E9EED-1033-A643-BFEB-6D935EED6079}"/>
+    <hyperlink ref="H24" r:id="rId22" xr:uid="{F850BD7D-6BC9-FA44-8954-A254CEDF97AF}"/>
+    <hyperlink ref="H25" r:id="rId23" xr:uid="{99D64504-726C-274C-8B85-ACED689E1EF6}"/>
+    <hyperlink ref="H26" r:id="rId24" xr:uid="{A798D0C0-61A2-7C4E-B7DF-F7728A17D474}"/>
+    <hyperlink ref="H27" r:id="rId25" xr:uid="{534D43CF-74D4-C640-BBD5-7AA6B9D9C598}"/>
+    <hyperlink ref="H28" r:id="rId26" xr:uid="{CE18D1C8-6A39-C64D-806A-D394C5C971D9}"/>
+    <hyperlink ref="H29" r:id="rId27" xr:uid="{DFB6E1EF-7167-8644-A271-B1B0458C8A3C}"/>
+    <hyperlink ref="H30" r:id="rId28" xr:uid="{090A7428-D486-7B42-8919-93840838EB56}"/>
+    <hyperlink ref="H31" r:id="rId29" xr:uid="{325990BA-9C70-5748-A8D4-06CE20B46BDB}"/>
+    <hyperlink ref="H32" r:id="rId30" xr:uid="{F2447C03-E205-C443-BD48-A3A7A59980EA}"/>
+    <hyperlink ref="H33" r:id="rId31" xr:uid="{89880AD9-6285-EB40-8938-C76587A31B54}"/>
+    <hyperlink ref="H34" r:id="rId32" xr:uid="{C171743F-DB9D-D545-A3CE-6D830951CD76}"/>
+    <hyperlink ref="H35" r:id="rId33" xr:uid="{BFE7DDA0-688B-444C-BF15-21954ABACD6C}"/>
+    <hyperlink ref="H36" r:id="rId34" xr:uid="{4990FA16-D1DB-0D4F-936E-343A1E110AC8}"/>
+    <hyperlink ref="H37" r:id="rId35" xr:uid="{F723176E-58C4-BF44-8DDC-D3F4FD317B2B}"/>
+    <hyperlink ref="H38" r:id="rId36" xr:uid="{E48EAC2C-B8A2-E64D-90A5-B52471F00441}"/>
+    <hyperlink ref="H39" r:id="rId37" xr:uid="{261F1F58-C51F-D147-9F5C-CEFAC8AC2BAB}"/>
+    <hyperlink ref="H40" r:id="rId38" xr:uid="{0E85EC50-B227-C142-AD0D-C5BF3D4C9013}"/>
+    <hyperlink ref="H41" r:id="rId39" xr:uid="{AD8BCD96-7911-114E-BFAB-5ABC45E2ABF4}"/>
+    <hyperlink ref="H42" r:id="rId40" xr:uid="{2FFB2C49-32D7-9143-9950-9F7C5EC032D7}"/>
+    <hyperlink ref="H43" r:id="rId41" xr:uid="{F904FBC9-03C2-E641-A8FF-83E4F33D7C84}"/>
+    <hyperlink ref="H45" r:id="rId42" xr:uid="{3B6F4692-ED19-4A48-B2E2-920F2360A197}"/>
+    <hyperlink ref="H44" r:id="rId43" xr:uid="{9CA8BB6C-1E6F-AC40-B6E3-27C56E53EA3B}"/>
+    <hyperlink ref="H46" r:id="rId44" xr:uid="{D83BFAB3-73D5-3F4F-813D-369914587592}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId45"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB94BA12-FB7F-7A49-9723-53ECDB474001}">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="22.5" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="48.6640625" customWidth="1"/>
+    <col min="8" max="8" width="32.83203125" customWidth="1"/>
+    <col min="9" max="9" width="31.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="34" t="s">
+        <v>707</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="35" t="s">
+        <v>595</v>
+      </c>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" s="36" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A2" s="37" t="s">
+        <v>888</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>890</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>889</v>
+      </c>
+      <c r="D2" s="37">
+        <v>1994</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>594</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>891</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>887</v>
+      </c>
+      <c r="I2" s="37"/>
+    </row>
+    <row r="3" spans="1:9" ht="306" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>892</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>893</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2019</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>894</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>896</v>
+      </c>
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:9" ht="306" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>898</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>899</v>
+      </c>
+      <c r="D4" s="5">
+        <v>2014</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>900</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:9" ht="187" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>904</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>898</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>905</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2000</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" ht="187" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>904</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>898</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>905</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2000</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>902</v>
+      </c>
+      <c r="I6" s="5"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{90530027-7F34-004D-831E-BA66498DCC2D}"/>
+    <hyperlink ref="H3" r:id="rId2" xr:uid="{DBA18814-8147-2249-B54B-585AF0172FE0}"/>
+    <hyperlink ref="H4" r:id="rId3" xr:uid="{9EA9FD3F-F4A8-D940-B83B-2F6EBE3C3FD0}"/>
+    <hyperlink ref="H5" r:id="rId4" xr:uid="{80A12AF7-CDA3-484C-B294-D4851D1E8A6C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId5"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAA08AD4-4841-984A-8D38-C62A98950899}">
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="34.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" customWidth="1"/>
+    <col min="5" max="5" width="19.1640625" customWidth="1"/>
+    <col min="6" max="6" width="19.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="68.5" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="224" x14ac:dyDescent="0.2">
+      <c r="A2" s="25" t="s">
+        <v>735</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>736</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>737</v>
+      </c>
+      <c r="D2" s="25">
+        <v>1990</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>738</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="I2" s="25"/>
+    </row>
+    <row r="3" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A3" s="25" t="s">
+        <v>740</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>736</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>741</v>
+      </c>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>742</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="I3" s="25"/>
+    </row>
+    <row r="4" spans="1:9" ht="288" x14ac:dyDescent="0.2">
+      <c r="A4" s="25" t="s">
+        <v>744</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>736</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>745</v>
+      </c>
+      <c r="D4" s="25">
+        <v>1983</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>475</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>746</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="I4" s="25"/>
+    </row>
+    <row r="5" spans="1:9" ht="102" x14ac:dyDescent="0.2">
+      <c r="A5" s="25" t="s">
+        <v>748</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>736</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>749</v>
+      </c>
+      <c r="D5" s="25">
+        <v>1981</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>700</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G5" s="25"/>
+      <c r="H5" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="I5" s="25"/>
+    </row>
+    <row r="6" spans="1:9" ht="119" x14ac:dyDescent="0.2">
+      <c r="A6" s="25" t="s">
+        <v>751</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>736</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>752</v>
+      </c>
+      <c r="D6" s="25">
+        <v>1970</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>753</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G6" s="25"/>
+      <c r="H6" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="I6" s="25"/>
+    </row>
+    <row r="7" spans="1:9" ht="102" x14ac:dyDescent="0.2">
+      <c r="A7" s="25" t="s">
+        <v>755</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>736</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>756</v>
+      </c>
+      <c r="D7" s="25">
+        <v>1984</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>757</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G7" s="25"/>
+      <c r="H7" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="I7" s="25"/>
+    </row>
+    <row r="8" spans="1:9" ht="272" x14ac:dyDescent="0.2">
+      <c r="A8" s="25" t="s">
+        <v>759</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>736</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>760</v>
+      </c>
+      <c r="D8" s="25">
+        <v>1976</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>761</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="I8" s="25"/>
+    </row>
+    <row r="9" spans="1:9" ht="192" x14ac:dyDescent="0.2">
+      <c r="A9" s="25" t="s">
+        <v>763</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>736</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>764</v>
+      </c>
+      <c r="D9" s="25">
+        <v>1980</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>765</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>766</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="I9" s="25"/>
+    </row>
+    <row r="10" spans="1:9" ht="102" x14ac:dyDescent="0.2">
+      <c r="A10" s="25" t="s">
+        <v>771</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>736</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>770</v>
+      </c>
+      <c r="D10" s="25">
+        <v>1979</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>775</v>
+      </c>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25" t="s">
+        <v>769</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>768</v>
+      </c>
+      <c r="I10" s="25"/>
+    </row>
+    <row r="11" spans="1:9" ht="192" x14ac:dyDescent="0.2">
+      <c r="A11" s="25" t="s">
+        <v>772</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>736</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>699</v>
+      </c>
+      <c r="D11" s="25">
+        <v>2003</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>776</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>774</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="I11" s="25"/>
+    </row>
+    <row r="12" spans="1:9" ht="176" x14ac:dyDescent="0.2">
+      <c r="A12" s="25" t="s">
+        <v>777</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>779</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>778</v>
+      </c>
+      <c r="D12" s="25">
+        <v>1991</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>780</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>781</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>782</v>
+      </c>
+      <c r="I12" s="25"/>
+    </row>
+    <row r="13" spans="1:9" ht="119" x14ac:dyDescent="0.2">
+      <c r="A13" s="25" t="s">
+        <v>783</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>779</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>784</v>
+      </c>
+      <c r="D13" s="25">
+        <v>1984</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>397</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>786</v>
+      </c>
+      <c r="I13" s="25"/>
+    </row>
+    <row r="14" spans="1:9" ht="128" x14ac:dyDescent="0.2">
+      <c r="A14" s="25" t="s">
+        <v>787</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>779</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>788</v>
+      </c>
+      <c r="D14" s="25">
+        <v>1993</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>397</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>789</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="I14" s="25"/>
+    </row>
+    <row r="15" spans="1:9" ht="102" x14ac:dyDescent="0.2">
+      <c r="A15" s="25" t="s">
+        <v>791</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>779</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>792</v>
+      </c>
+      <c r="D15" s="25">
+        <v>2001</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>793</v>
+      </c>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="8" t="s">
+        <v>794</v>
+      </c>
+      <c r="I15" s="25"/>
+    </row>
+    <row r="16" spans="1:9" ht="320" x14ac:dyDescent="0.2">
+      <c r="A16" s="25" t="s">
+        <v>636</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>779</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>637</v>
+      </c>
+      <c r="D16" s="25">
+        <v>1996</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>638</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="I16" s="25"/>
+    </row>
+    <row r="17" spans="1:9" ht="208" x14ac:dyDescent="0.2">
+      <c r="A17" s="25" t="s">
+        <v>646</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>779</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>647</v>
+      </c>
+      <c r="D17" s="25">
+        <v>2000</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>648</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>649</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="I17" s="25"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="25"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="25"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="25"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="25"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="25"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="25"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="25"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="25"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="25"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="25"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="26"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="25"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="25"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="25"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" s="25"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="25"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" s="25"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="25"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" s="25"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="25"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" s="25"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" s="25"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{CB6B7FD4-DC8F-C840-AD8C-A525E007CE17}"/>
+    <hyperlink ref="H3" r:id="rId2" xr:uid="{7C3529FA-FDF5-214E-9E81-3029F19B0B5E}"/>
+    <hyperlink ref="H4" r:id="rId3" xr:uid="{54601CA7-7A12-124F-8142-76FAF8C54571}"/>
+    <hyperlink ref="H5" r:id="rId4" xr:uid="{3BF70562-9481-D547-B272-70FCF95C2239}"/>
+    <hyperlink ref="H6" r:id="rId5" xr:uid="{030488AC-6F95-CD4A-9B1F-A74DC46CAD1C}"/>
+    <hyperlink ref="H7" r:id="rId6" xr:uid="{13C75E8E-4902-934D-98B5-ACE406C3C426}"/>
+    <hyperlink ref="H8" r:id="rId7" xr:uid="{69FBD2AD-BD2B-D341-A681-8105E93B87A0}"/>
+    <hyperlink ref="H9" r:id="rId8" xr:uid="{97773067-4A53-304B-B571-EF2275ACF964}"/>
+    <hyperlink ref="H10" r:id="rId9" xr:uid="{CA419BEC-662C-234F-9546-5858B9B08DFF}"/>
+    <hyperlink ref="H11" r:id="rId10" xr:uid="{F995B862-252B-7E42-9FB3-1EA52DC70778}"/>
+    <hyperlink ref="H12" r:id="rId11" xr:uid="{DD0BBE71-B27E-8A45-93E7-591F449D7CED}"/>
+    <hyperlink ref="H13" r:id="rId12" xr:uid="{762D4D50-5C24-1D4F-ADD0-C66AF09784A4}"/>
+    <hyperlink ref="H14" r:id="rId13" xr:uid="{DD5F0160-71F4-7343-83D4-25B5386F6DA2}"/>
+    <hyperlink ref="H15" r:id="rId14" xr:uid="{CB180E1B-74DD-4845-8734-D3F27800FE16}"/>
+    <hyperlink ref="H16" r:id="rId15" xr:uid="{4C48FC3A-6006-7646-90A1-03D50F4415DC}"/>
+    <hyperlink ref="H17" r:id="rId16" xr:uid="{86DA54D2-3847-5D43-A5E9-0E6A3418DF17}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId17"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{536A550C-D311-0C42-8B53-D3917454C963}">
   <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -6350,7 +10367,7 @@
     <col min="1" max="1" width="31.6640625" customWidth="1"/>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
     <col min="4" max="5" width="43.5" customWidth="1"/>
-    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="6" max="6" width="72.6640625" customWidth="1"/>
     <col min="7" max="7" width="23.6640625" customWidth="1"/>
     <col min="8" max="8" width="25.5" customWidth="1"/>
     <col min="9" max="9" width="24.1640625" customWidth="1"/>
@@ -6372,7 +10389,7 @@
         <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -6381,10 +10398,10 @@
         <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
@@ -6393,30 +10410,30 @@
         <v>113</v>
       </c>
       <c r="L1" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="255" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="C2" s="5">
         <v>2023</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
@@ -6424,11 +10441,11 @@
         <v>1</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="L2" s="5"/>
     </row>
-    <row r="3" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="238" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>233</v>
       </c>
@@ -6442,7 +10459,7 @@
         <v>235</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>236</v>
@@ -6460,27 +10477,27 @@
       </c>
       <c r="L3" s="5"/>
     </row>
-    <row r="4" spans="1:12" ht="289" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="153" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="C4" s="5">
         <v>2020</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
@@ -6488,11 +10505,11 @@
         <v>3</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="L4" s="5"/>
     </row>
-    <row r="5" spans="1:12" ht="372" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="255" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>239</v>
       </c>
@@ -6506,7 +10523,7 @@
         <v>46</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>241</v>
@@ -6522,7 +10539,7 @@
       </c>
       <c r="L5" s="5"/>
     </row>
-    <row r="6" spans="1:12" ht="306" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>243</v>
       </c>
@@ -6536,7 +10553,7 @@
         <v>245</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>246</v>
@@ -6554,27 +10571,27 @@
       </c>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:12" ht="306" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="C7" s="5">
         <v>2016</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -6582,11 +10599,11 @@
         <v>3</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="L7" s="5"/>
     </row>
-    <row r="8" spans="1:12" ht="356" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>249</v>
       </c>
@@ -6600,7 +10617,7 @@
         <v>110</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>251</v>
@@ -6620,22 +10637,22 @@
     </row>
     <row r="9" spans="1:12" ht="255" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="C9" s="5">
         <v>2012</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="5"/>
@@ -6644,7 +10661,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="L9" s="5"/>
     </row>
@@ -6662,7 +10679,7 @@
         <v>257</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>256</v>
@@ -6685,7 +10702,7 @@
         <v>260</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="C11" s="5">
         <v>2011</v>
@@ -6694,7 +10711,7 @@
         <v>262</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>261</v>
@@ -6714,22 +10731,22 @@
     </row>
     <row r="12" spans="1:12" ht="323" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="C12" s="5">
         <v>2009</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="5"/>
@@ -6738,16 +10755,16 @@
         <v>3</v>
       </c>
       <c r="K12" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="L12" s="5"/>
+    </row>
+    <row r="13" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="L12" s="5"/>
-    </row>
-    <row r="13" spans="1:12" ht="404" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>489</v>
-      </c>
       <c r="B13" s="5" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="C13" s="5">
         <v>2009</v>
@@ -6756,13 +10773,13 @@
         <v>235</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -6770,13 +10787,13 @@
         <v>3</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="L13" s="5"/>
     </row>
-    <row r="14" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="306" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>265</v>
@@ -6788,7 +10805,7 @@
         <v>266</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>267</v>
@@ -6808,25 +10825,25 @@
     </row>
     <row r="15" spans="1:12" ht="238" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="C15" s="5">
         <v>2007</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
@@ -6834,31 +10851,31 @@
         <v>3</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="L15" s="5"/>
     </row>
-    <row r="16" spans="1:12" ht="306" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="153" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="C16" s="5">
         <v>2007</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
@@ -6866,16 +10883,16 @@
         <v>3</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="L16" s="5"/>
     </row>
-    <row r="17" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="C17" s="5">
         <v>2003</v>
@@ -6884,10 +10901,10 @@
         <v>397</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="5"/>
@@ -6896,30 +10913,30 @@
         <v>2</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="221" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="C18" s="5">
         <v>1999</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="5"/>
@@ -6928,10 +10945,10 @@
         <v>3</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
@@ -7037,9 +11054,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73C9E597-FF64-4A4E-8508-2E5949A63CAC}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.33203125" customWidth="1"/>
@@ -7056,7 +11073,7 @@
     <col min="13" max="13" width="39.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
@@ -7070,63 +11087,57 @@
         <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>11</v>
+        <v>429</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="L1" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="306" x14ac:dyDescent="0.2">
+      <c r="K1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="306" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="C2" s="5">
         <v>2019</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>517</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="G2" s="5"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5">
+      <c r="I2" s="5">
         <v>3</v>
       </c>
-      <c r="K2" s="8" t="s">
-        <v>518</v>
-      </c>
-      <c r="L2" s="5"/>
-    </row>
-    <row r="3" spans="1:12" ht="289" x14ac:dyDescent="0.2">
+      <c r="J2" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="K2" s="5"/>
+    </row>
+    <row r="3" spans="1:11" ht="272" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>416</v>
       </c>
@@ -7140,30 +11151,27 @@
         <v>69</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="G3" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5">
+        <v>3</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5">
-        <v>3</v>
-      </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" ht="153" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="L3" s="5"/>
-    </row>
-    <row r="4" spans="1:12" ht="153" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>420</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>421</v>
       </c>
       <c r="C4" s="5">
         <v>2017</v>
@@ -7172,30 +11180,27 @@
         <v>245</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F4" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5">
+        <v>3</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>423</v>
-      </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5">
-        <v>3</v>
-      </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="L4" s="5"/>
-    </row>
-    <row r="5" spans="1:12" ht="187" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>426</v>
-      </c>
       <c r="B5" s="5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C5" s="5">
         <v>2017</v>
@@ -7204,30 +11209,27 @@
         <v>290</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="G5" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="1:11" ht="221" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>428</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5">
-        <v>3</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>429</v>
-      </c>
-      <c r="L5" s="5"/>
-    </row>
-    <row r="6" spans="1:12" ht="221" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>431</v>
       </c>
       <c r="C6" s="5">
         <v>2017</v>
@@ -7236,30 +11238,27 @@
         <v>64</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>432</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="G6" s="5"/>
       <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5">
+      <c r="I6" s="5">
         <v>3</v>
       </c>
-      <c r="K6" s="8" t="s">
-        <v>438</v>
-      </c>
-      <c r="L6" s="5"/>
-    </row>
-    <row r="7" spans="1:12" ht="272" x14ac:dyDescent="0.2">
+      <c r="J6" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="1:11" ht="272" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C7" s="5">
         <v>2017</v>
@@ -7268,62 +11267,56 @@
         <v>64</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>442</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5">
+      <c r="I7" s="5">
         <v>3</v>
       </c>
-      <c r="K7" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="L7" s="5"/>
-    </row>
-    <row r="8" spans="1:12" ht="272" x14ac:dyDescent="0.2">
+      <c r="J7" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="1:11" ht="272" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C8" s="5">
         <v>2016</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>448</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="G8" s="5"/>
       <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5">
+      <c r="I8" s="5">
         <v>2</v>
       </c>
-      <c r="K8" s="8" t="s">
-        <v>449</v>
-      </c>
-      <c r="L8" s="5"/>
-    </row>
-    <row r="9" spans="1:12" ht="306" x14ac:dyDescent="0.2">
+      <c r="J8" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="1:11" ht="306" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="C9" s="5">
         <v>2015</v>
@@ -7332,30 +11325,27 @@
         <v>343</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>453</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5">
+      <c r="I9" s="5">
         <v>2</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="L9" s="5"/>
-    </row>
-    <row r="10" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="J9" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:11" ht="221" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="C10" s="5">
         <v>2014</v>
@@ -7364,62 +11354,56 @@
         <v>262</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>458</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="G10" s="5"/>
       <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5">
+      <c r="I10" s="5">
         <v>3</v>
       </c>
-      <c r="K10" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="L10" s="5"/>
-    </row>
-    <row r="11" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+      <c r="J10" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="1:11" ht="187" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="C11" s="5">
         <v>2013</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>464</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="G11" s="5"/>
       <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5">
+      <c r="I11" s="5">
         <v>3</v>
       </c>
-      <c r="K11" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="L11" s="5"/>
-    </row>
-    <row r="12" spans="1:12" ht="238" x14ac:dyDescent="0.2">
+      <c r="J11" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="1:11" ht="238" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="C12" s="5">
         <v>2004</v>
@@ -7428,110 +11412,247 @@
         <v>88</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="G12" s="8"/>
+        <v>459</v>
+      </c>
+      <c r="G12" s="5"/>
       <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5">
+      <c r="I12" s="5">
         <v>1</v>
       </c>
-      <c r="K12" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="L12" s="5"/>
-    </row>
-    <row r="13" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="J12" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:11" ht="221" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="C13" s="5">
         <v>2000</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>523</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="G13" s="5"/>
       <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5">
+      <c r="I13" s="5">
         <v>3</v>
       </c>
-      <c r="K13" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="L13" s="5"/>
-    </row>
-    <row r="14" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="J13" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:11" ht="136" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="C14" s="5">
         <v>1995</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="G14" s="8"/>
+        <v>464</v>
+      </c>
+      <c r="G14" s="5"/>
       <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5">
+      <c r="I14" s="5">
         <v>2</v>
       </c>
-      <c r="K14" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="L14" s="5"/>
+      <c r="J14" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="1:11" ht="255" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>920</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2019</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>921</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="8" t="s">
+        <v>922</v>
+      </c>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="1:11" ht="153" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>926</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2021</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>927</v>
+      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="8" t="s">
+        <v>924</v>
+      </c>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="1:11" ht="204" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>928</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>930</v>
+      </c>
+      <c r="C17" s="5">
+        <v>2017</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>932</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>929</v>
+      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="8" t="s">
+        <v>931</v>
+      </c>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1" xr:uid="{88D0A256-582C-1740-B747-81D4B0F163A5}"/>
-    <hyperlink ref="K3" r:id="rId2" xr:uid="{E6D8BD33-A939-1442-8647-C8362C2AE27D}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{597B4205-BC41-4743-ADE5-DDDF460FB4B7}"/>
-    <hyperlink ref="K4" r:id="rId4" xr:uid="{842691E2-7EAF-EF47-9C1B-F28D37C06B19}"/>
-    <hyperlink ref="G5" r:id="rId5" xr:uid="{4F4C93DD-8A14-504C-BA9A-BC9534951090}"/>
-    <hyperlink ref="K5" r:id="rId6" xr:uid="{6ADE2E15-CB0E-DF46-A93C-351BFA4B368B}"/>
-    <hyperlink ref="K6" r:id="rId7" xr:uid="{B42EE202-E0C0-8F49-A0FB-885D35489A34}"/>
-    <hyperlink ref="K7" r:id="rId8" xr:uid="{E312C5CB-6F1A-6846-AA05-431E8BDFA2E0}"/>
-    <hyperlink ref="K8" r:id="rId9" xr:uid="{0815EEF7-1B85-2E4F-9A10-2CC2EBBED651}"/>
-    <hyperlink ref="G9" r:id="rId10" xr:uid="{C86D56A9-EE17-8F47-89E4-36E2498ADCD9}"/>
-    <hyperlink ref="K9" r:id="rId11" xr:uid="{A1CEB55E-DD0E-8748-A0E3-A961B4426C26}"/>
-    <hyperlink ref="G10" r:id="rId12" xr:uid="{BD0677AD-7D3F-6548-9CAC-1D047233BDC7}"/>
-    <hyperlink ref="K10" r:id="rId13" xr:uid="{9EC1B994-E92F-2644-9484-03A94A752D4E}"/>
-    <hyperlink ref="G11" r:id="rId14" xr:uid="{CB1E753D-EF1E-354F-A5BC-022D1640302F}"/>
-    <hyperlink ref="K11" r:id="rId15" xr:uid="{85B0E369-2637-9540-8B5C-935C11BEDA7D}"/>
-    <hyperlink ref="K12" r:id="rId16" xr:uid="{C78E89F4-1C74-5144-B3E4-107276AF5977}"/>
-    <hyperlink ref="K14" r:id="rId17" xr:uid="{1F03A957-AE7A-2040-9E62-98CFD4C99C88}"/>
-    <hyperlink ref="K2" r:id="rId18" xr:uid="{F1FA5B79-3907-1D4C-A99F-FCBA27E332C6}"/>
-    <hyperlink ref="G13" r:id="rId19" xr:uid="{190FB587-31DD-5246-B8B2-F7EBDAD4FAF4}"/>
-    <hyperlink ref="K13" r:id="rId20" xr:uid="{951AE929-D624-B748-ABFD-9F32EF261D75}"/>
+    <hyperlink ref="J3" r:id="rId1" xr:uid="{E6D8BD33-A939-1442-8647-C8362C2AE27D}"/>
+    <hyperlink ref="J4" r:id="rId2" xr:uid="{842691E2-7EAF-EF47-9C1B-F28D37C06B19}"/>
+    <hyperlink ref="J5" r:id="rId3" xr:uid="{6ADE2E15-CB0E-DF46-A93C-351BFA4B368B}"/>
+    <hyperlink ref="J6" r:id="rId4" xr:uid="{B42EE202-E0C0-8F49-A0FB-885D35489A34}"/>
+    <hyperlink ref="J7" r:id="rId5" xr:uid="{E312C5CB-6F1A-6846-AA05-431E8BDFA2E0}"/>
+    <hyperlink ref="J8" r:id="rId6" xr:uid="{0815EEF7-1B85-2E4F-9A10-2CC2EBBED651}"/>
+    <hyperlink ref="J9" r:id="rId7" xr:uid="{A1CEB55E-DD0E-8748-A0E3-A961B4426C26}"/>
+    <hyperlink ref="J10" r:id="rId8" xr:uid="{9EC1B994-E92F-2644-9484-03A94A752D4E}"/>
+    <hyperlink ref="J11" r:id="rId9" xr:uid="{85B0E369-2637-9540-8B5C-935C11BEDA7D}"/>
+    <hyperlink ref="J12" r:id="rId10" xr:uid="{C78E89F4-1C74-5144-B3E4-107276AF5977}"/>
+    <hyperlink ref="J14" r:id="rId11" xr:uid="{1F03A957-AE7A-2040-9E62-98CFD4C99C88}"/>
+    <hyperlink ref="J2" r:id="rId12" xr:uid="{F1FA5B79-3907-1D4C-A99F-FCBA27E332C6}"/>
+    <hyperlink ref="J13" r:id="rId13" xr:uid="{951AE929-D624-B748-ABFD-9F32EF261D75}"/>
+    <hyperlink ref="J15" r:id="rId14" xr:uid="{3A1BA293-1254-DC45-9B67-3B540CD932A2}"/>
+    <hyperlink ref="J16" r:id="rId15" xr:uid="{85E1FD5F-04C7-1448-99FF-0FB1AA4547B6}"/>
+    <hyperlink ref="J17" r:id="rId16" xr:uid="{8AFDA8E9-1A9C-F04B-88BF-0171DF2DBA88}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId21"/>
+    <tablePart r:id="rId17"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -7550,7 +11671,7 @@
               </x14:cfvo>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>J2:J14</xm:sqref>
+          <xm:sqref>I2:I22</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -7558,7 +11679,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EB2E9E2-7914-4049-9832-CDEB1A045AD2}">
   <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -7566,7 +11687,7 @@
     <col min="1" max="1" width="42.6640625" customWidth="1"/>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
     <col min="4" max="5" width="35.33203125" customWidth="1"/>
-    <col min="6" max="6" width="44.5" customWidth="1"/>
+    <col min="6" max="6" width="69.5" customWidth="1"/>
     <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="32.83203125" customWidth="1"/>
     <col min="9" max="9" width="26.6640625" customWidth="1"/>
@@ -7588,7 +11709,7 @@
         <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -7597,10 +11718,10 @@
         <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
@@ -7609,7 +11730,7 @@
         <v>113</v>
       </c>
       <c r="L1" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="340" x14ac:dyDescent="0.2">
@@ -7626,10 +11747,10 @@
         <v>324</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>325</v>
@@ -7644,22 +11765,22 @@
       </c>
       <c r="L2" s="5"/>
     </row>
-    <row r="3" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="C3" s="5">
         <v>2019</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="5"/>
@@ -7668,7 +11789,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="L3" s="5"/>
     </row>
@@ -7686,7 +11807,7 @@
         <v>262</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>340</v>
@@ -7706,22 +11827,22 @@
     </row>
     <row r="5" spans="1:12" ht="372" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="C5" s="5">
         <v>2015</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="5"/>
@@ -7730,11 +11851,11 @@
         <v>3</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="238" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="153" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>331</v>
       </c>
@@ -7748,7 +11869,7 @@
         <v>245</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>333</v>
@@ -7778,7 +11899,7 @@
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>339</v>
@@ -7808,7 +11929,7 @@
         <v>343</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>344</v>
@@ -7826,7 +11947,7 @@
       </c>
       <c r="L8" s="5"/>
     </row>
-    <row r="9" spans="1:12" ht="356" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>347</v>
       </c>
@@ -7840,7 +11961,7 @@
         <v>349</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>350</v>
@@ -7872,7 +11993,7 @@
         <v>355</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>356</v>
@@ -7904,7 +12025,7 @@
         <v>110</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>361</v>
@@ -7920,7 +12041,7 @@
       </c>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" spans="1:12" ht="340" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="323" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>363</v>
       </c>
@@ -7934,7 +12055,7 @@
         <v>245</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>365</v>
@@ -7952,7 +12073,7 @@
       </c>
       <c r="L12" s="5"/>
     </row>
-    <row r="13" spans="1:12" ht="289" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>368</v>
       </c>
@@ -7966,7 +12087,7 @@
         <v>84</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>370</v>
@@ -7984,7 +12105,7 @@
       </c>
       <c r="L13" s="5"/>
     </row>
-    <row r="14" spans="1:12" ht="323" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>373</v>
       </c>
@@ -7998,7 +12119,7 @@
         <v>374</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>375</v>
@@ -8028,7 +12149,7 @@
         <v>380</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>381</v>
@@ -8046,7 +12167,7 @@
       </c>
       <c r="L15" s="5"/>
     </row>
-    <row r="16" spans="1:12" ht="404" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="238" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>384</v>
       </c>
@@ -8060,7 +12181,7 @@
         <v>386</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>387</v>
@@ -8090,7 +12211,7 @@
         <v>397</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>391</v>
@@ -8122,7 +12243,7 @@
         <v>396</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>398</v>
@@ -8140,7 +12261,7 @@
       </c>
       <c r="L18" s="5"/>
     </row>
-    <row r="19" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>406</v>
       </c>
@@ -8154,7 +12275,7 @@
         <v>110</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>408</v>
@@ -8186,7 +12307,7 @@
         <v>413</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>414</v>
@@ -8202,7 +12323,7 @@
       </c>
       <c r="L20" s="5"/>
     </row>
-    <row r="21" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>401</v>
       </c>
@@ -8216,7 +12337,7 @@
         <v>110</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>403</v>
@@ -8295,169 +12416,165 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EB5083B-93D3-2C47-B0A2-2D8EBB565AE4}">
-  <dimension ref="B2:K10"/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91F67A8E-FF27-944F-897E-BD41F7AC8244}">
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" style="12" customWidth="1"/>
-    <col min="2" max="2" width="27.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.83203125" style="12"/>
-    <col min="5" max="5" width="27.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.83203125" style="12"/>
+    <col min="1" max="1" width="28.5" customWidth="1"/>
+    <col min="2" max="3" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="27.83203125" customWidth="1"/>
+    <col min="6" max="6" width="19.1640625" customWidth="1"/>
+    <col min="7" max="7" width="47.33203125" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="27.6640625" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="27" x14ac:dyDescent="0.35">
-      <c r="B2" s="14" t="s">
-        <v>527</v>
-      </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-    </row>
-    <row r="3" spans="2:11" ht="4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-    </row>
-    <row r="4" spans="2:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="B4" s="25" t="s">
-        <v>526</v>
-      </c>
-      <c r="C4" s="26"/>
-      <c r="E4" s="25" t="s">
-        <v>533</v>
-      </c>
-      <c r="F4" s="27"/>
-      <c r="G4" s="26"/>
-      <c r="I4" s="25" t="s">
-        <v>565</v>
-      </c>
-      <c r="J4" s="27"/>
-      <c r="K4" s="24"/>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="15" t="s">
-        <v>567</v>
-      </c>
-      <c r="C5" s="16">
-        <f>ROWS(Proximity[])</f>
-        <v>39</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>534</v>
-      </c>
-      <c r="F5" s="12">
-        <f>COUNTIF(Proximity[Relevance],3) + COUNTIF(Success[Relevance],3) + COUNTIF(Support[Relevance],3) + COUNTIF(Ecosystem[Relevance],3) + COUNTIF(Network[Relevance],3)</f>
-        <v>55</v>
-      </c>
-      <c r="G5" s="21">
-        <f>F5/$C$10</f>
-        <v>0.47413793103448276</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>566</v>
-      </c>
-      <c r="J5" s="12">
-        <f>COUNTIF(Proximity[Reviewed?],"DONE") + COUNTIF(Success[Reviewed?],"DONE") + COUNTIF(Support[Reviewed?],"DONE") + COUNTIF(Ecosystem[Reviewed?],"DONE") + COUNTIF(Network[Reviewed?],"DONE")</f>
-        <v>29</v>
-      </c>
-      <c r="K5" s="21">
-        <f>J5/$C$10</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="15" t="s">
-        <v>528</v>
-      </c>
-      <c r="C6" s="16">
-        <f>ROWS(Success[])</f>
-        <v>27</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>535</v>
-      </c>
-      <c r="F6" s="12">
-        <f>COUNTIF(Proximity[Relevance],2) + COUNTIF(Success[Relevance],2) + COUNTIF(Support[Relevance],2) + COUNTIF(Ecosystem[Relevance],2) + COUNTIF(Network[Relevance],2)</f>
-        <v>40</v>
-      </c>
-      <c r="G6" s="21">
-        <f t="shared" ref="G6:G7" si="0">F6/$C$10</f>
-        <v>0.34482758620689657</v>
-      </c>
-      <c r="I6" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="J6" s="22">
-        <f>C10-J5</f>
-        <v>87</v>
-      </c>
-      <c r="K6" s="23">
-        <f>J6/$C$10</f>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B7" s="15" t="s">
-        <v>529</v>
-      </c>
-      <c r="C7" s="16">
-        <f>ROWS(Support[])</f>
-        <v>17</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>536</v>
-      </c>
-      <c r="F7" s="22">
-        <f>COUNTIF(Proximity[Relevance],1) + COUNTIF(Success[Relevance],1) + COUNTIF(Support[Relevance],1) + COUNTIF(Ecosystem[Relevance],1) + COUNTIF(Network[Relevance],1)</f>
-        <v>18</v>
-      </c>
-      <c r="G7" s="23">
-        <f t="shared" si="0"/>
-        <v>0.15517241379310345</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B8" s="15" t="s">
-        <v>530</v>
-      </c>
-      <c r="C8" s="16">
-        <f>ROWS(Ecosystem[])</f>
+    <row r="1" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="34" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="17" t="s">
-        <v>531</v>
-      </c>
-      <c r="C9" s="18">
-        <f>ROWS(Network[])</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="19" t="s">
+      <c r="B1" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>707</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="35" t="s">
+        <v>595</v>
+      </c>
+      <c r="G1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="J1" s="36" t="s">
         <v>532</v>
       </c>
-      <c r="C10" s="20">
-        <f>SUM(C5:C9)</f>
-        <v>116</v>
-      </c>
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A2" s="37" t="s">
+        <v>872</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>874</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>875</v>
+      </c>
+      <c r="D2" s="37">
+        <v>2020</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>290</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>594</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>876</v>
+      </c>
+      <c r="H2" s="37"/>
+      <c r="I2" s="9" t="s">
+        <v>873</v>
+      </c>
+      <c r="J2" s="37"/>
+    </row>
+    <row r="3" spans="1:10" ht="272" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>910</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2018</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>912</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="8" t="s">
+        <v>913</v>
+      </c>
+      <c r="J3" s="5"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="5"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="I4:J4"/>
-  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{C331B32A-AA90-474F-BD73-17C9DBDDE766}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{91783BA4-297D-8147-8DF5-1E031E02BF37}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/docs/working_documents/Research_Overview.xlsx
+++ b/docs/working_documents/Research_Overview.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/janlinzner/Projects/Master-Thesis-Spatial-Proximity-Venture-Capital/docs/working_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0720FCB-B29B-8A44-98D7-615E6F8E8ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7CF9B70-A424-B94A-9CF4-1F334D483AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="6" xr2:uid="{AB2802A1-B2D6-D448-8853-2C20DC0DE37E}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{AB2802A1-B2D6-D448-8853-2C20DC0DE37E}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximity" sheetId="1" r:id="rId1"/>
@@ -2952,9 +2952,6 @@
     <t>Assessing the Contribution of Venture Capital to Innovation</t>
   </si>
   <si>
-    <t>Samuel Kortum, Josh LernerJosh Lerner</t>
-  </si>
-  <si>
     <t>RAND Journal of Economics</t>
   </si>
   <si>
@@ -3894,6 +3891,9 @@
   </si>
   <si>
     <t>strategic entrepreneurship journal</t>
+  </si>
+  <si>
+    <t>Samuel Kortum, Josh Lerner</t>
   </si>
 </sst>
 </file>
@@ -4091,7 +4091,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -4145,6 +4145,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4154,27 +4155,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4182,45 +4162,6 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="110">
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -4265,6 +4206,9 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4520,6 +4464,42 @@
         <name val="Aptos Display"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4883,126 +4863,126 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{DA3DAF49-133B-4342-B1F1-A669623B84B7}" name="StartupFinancing" displayName="StartupFinancing" ref="A1:I6" totalsRowShown="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{DA3DAF49-133B-4342-B1F1-A669623B84B7}" name="StartupFinancing" displayName="StartupFinancing" ref="A1:I6" totalsRowShown="0" dataDxfId="68">
   <autoFilter ref="A1:I6" xr:uid="{DA3DAF49-133B-4342-B1F1-A669623B84B7}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{D8161E5E-71F1-1946-B4E1-B30528D422AA}" name="Paper Title" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{45133EC8-77DB-BC45-8846-B40214F1638C}" name="Topic" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{7EC44AD2-9FEE-214C-ACA0-C3917FC9417E}" name="Authors" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{6C75F284-F966-7441-AFD8-CDBB0A9803B1}" name="Year" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{A01AD45C-1B6A-AE42-99A0-9712C5E3E192}" name="Journal Title" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{CD4DE00F-B729-DD46-8F9B-2A8CA3DE0BC2}" name="Journal Importance" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{A1D818FA-9230-2141-81C0-50EDB8019EBD}" name="Abstract" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{396306FC-5B14-914C-9BE1-5305DC8B03FA}" name="Link" dataDxfId="3" dataCellStyle="Hyperlink"/>
-    <tableColumn id="9" xr3:uid="{83E9F2DB-5A6C-B642-B4AC-190170490909}" name="Reviewed?" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{D8161E5E-71F1-1946-B4E1-B30528D422AA}" name="Paper Title" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{45133EC8-77DB-BC45-8846-B40214F1638C}" name="Topic" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{7EC44AD2-9FEE-214C-ACA0-C3917FC9417E}" name="Authors" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{6C75F284-F966-7441-AFD8-CDBB0A9803B1}" name="Year" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{A01AD45C-1B6A-AE42-99A0-9712C5E3E192}" name="Journal Title" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{CD4DE00F-B729-DD46-8F9B-2A8CA3DE0BC2}" name="Journal Importance" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{A1D818FA-9230-2141-81C0-50EDB8019EBD}" name="Abstract" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{396306FC-5B14-914C-9BE1-5305DC8B03FA}" name="Link" dataDxfId="60" dataCellStyle="Hyperlink"/>
+    <tableColumn id="9" xr3:uid="{83E9F2DB-5A6C-B642-B4AC-190170490909}" name="Reviewed?" dataDxfId="59"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{2C0717B9-48DC-1545-BEB4-3FAAFA0BD037}" name="VCTheory" displayName="VCTheory" ref="A1:I28" totalsRowShown="0" dataDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{2C0717B9-48DC-1545-BEB4-3FAAFA0BD037}" name="VCTheory" displayName="VCTheory" ref="A1:I28" totalsRowShown="0" dataDxfId="58">
   <autoFilter ref="A1:I28" xr:uid="{F5A9A02E-BD4A-BB42-9BBA-32FC0C2447E8}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{B95F0992-9842-EE4F-9B0A-816E94F39B69}" name="Paper Title" dataDxfId="67"/>
-    <tableColumn id="13" xr3:uid="{8C764070-1671-7B4A-BDE9-595A7A56C9B3}" name="Topic" dataDxfId="66"/>
-    <tableColumn id="2" xr3:uid="{DDB30B63-EEF2-3B4F-BE3D-29F36FA87651}" name="Authors" dataDxfId="65"/>
-    <tableColumn id="3" xr3:uid="{1C8DDEE0-2997-E843-A575-5E6FEA47499F}" name="Year" dataDxfId="64"/>
-    <tableColumn id="4" xr3:uid="{4A18AFA9-BE70-1345-A4A0-710E14F15C74}" name="Journal Title" dataDxfId="63"/>
-    <tableColumn id="5" xr3:uid="{B6A9D77E-3C61-C542-B8D3-04E55556D03E}" name="Journal Importance" dataDxfId="62"/>
-    <tableColumn id="6" xr3:uid="{BF854912-6FF3-8845-957C-E27FB31495FD}" name="Abstract" dataDxfId="61"/>
-    <tableColumn id="11" xr3:uid="{00B57B48-105F-AC40-98C8-349FB96920FE}" name="Link" dataDxfId="60"/>
-    <tableColumn id="12" xr3:uid="{80230E1F-6CB1-6547-B78F-8342F2FD62E4}" name="Reviewed?" dataDxfId="59"/>
+    <tableColumn id="1" xr3:uid="{B95F0992-9842-EE4F-9B0A-816E94F39B69}" name="Paper Title" dataDxfId="57"/>
+    <tableColumn id="13" xr3:uid="{8C764070-1671-7B4A-BDE9-595A7A56C9B3}" name="Topic" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{DDB30B63-EEF2-3B4F-BE3D-29F36FA87651}" name="Authors" dataDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{1C8DDEE0-2997-E843-A575-5E6FEA47499F}" name="Year" dataDxfId="54"/>
+    <tableColumn id="4" xr3:uid="{4A18AFA9-BE70-1345-A4A0-710E14F15C74}" name="Journal Title" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{B6A9D77E-3C61-C542-B8D3-04E55556D03E}" name="Journal Importance" dataDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{BF854912-6FF3-8845-957C-E27FB31495FD}" name="Abstract" dataDxfId="51"/>
+    <tableColumn id="11" xr3:uid="{00B57B48-105F-AC40-98C8-349FB96920FE}" name="Link" dataDxfId="50"/>
+    <tableColumn id="12" xr3:uid="{80230E1F-6CB1-6547-B78F-8342F2FD62E4}" name="Reviewed?" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A30AD82-02A7-6745-A2CA-934FA2D6ABD4}" name="Support" displayName="Support" ref="A1:L18" totalsRowShown="0" dataDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A30AD82-02A7-6745-A2CA-934FA2D6ABD4}" name="Support" displayName="Support" ref="A1:L18" totalsRowShown="0" dataDxfId="48">
   <autoFilter ref="A1:L18" xr:uid="{6A30AD82-02A7-6745-A2CA-934FA2D6ABD4}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L18">
     <sortCondition descending="1" ref="C1:C18"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{A616AEE6-C6DE-3848-B3E0-6002397B9882}" name="Paper Title" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{FF60328E-A314-FD4E-820F-3DB20EB3439C}" name="Authors" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{CBBF5768-3F3B-6540-A093-4FD23CD75C72}" name="Year" dataDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{01171707-AA15-DD41-B524-CDE7D67FF738}" name="Journal Title" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{11C89D04-6481-D540-AA96-61DAC7AF4A34}" name="Journal Importance" dataDxfId="53"/>
-    <tableColumn id="5" xr3:uid="{AB646E0C-5A77-1444-B818-4CEB6E7B9BFA}" name="Abstract" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{A321187A-382D-FE46-806D-75FA9604EB6B}" name="DOI" dataDxfId="51" dataCellStyle="Hyperlink"/>
-    <tableColumn id="11" xr3:uid="{0512DC86-6CE5-CB45-B301-2161DBBC1236}" name="Insights for Thesis" dataDxfId="50"/>
-    <tableColumn id="12" xr3:uid="{B6492819-882E-6E43-A300-8E723AE7BF33}" name="Outcomes" dataDxfId="49"/>
-    <tableColumn id="13" xr3:uid="{FAC6D398-1FDC-6944-9A7E-34C28ECDAA8B}" name="Relevance" dataDxfId="48"/>
-    <tableColumn id="14" xr3:uid="{F7655086-4881-9D4F-BDBF-0FB8DE110B27}" name="Link" dataDxfId="47" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{3A688F49-F3F4-B549-83D0-B0942C7EE14B}" name="Reviewed?" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{A616AEE6-C6DE-3848-B3E0-6002397B9882}" name="Paper Title" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{FF60328E-A314-FD4E-820F-3DB20EB3439C}" name="Authors" dataDxfId="46"/>
+    <tableColumn id="3" xr3:uid="{CBBF5768-3F3B-6540-A093-4FD23CD75C72}" name="Year" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{01171707-AA15-DD41-B524-CDE7D67FF738}" name="Journal Title" dataDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{11C89D04-6481-D540-AA96-61DAC7AF4A34}" name="Journal Importance" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{AB646E0C-5A77-1444-B818-4CEB6E7B9BFA}" name="Abstract" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{A321187A-382D-FE46-806D-75FA9604EB6B}" name="DOI" dataDxfId="41" dataCellStyle="Hyperlink"/>
+    <tableColumn id="11" xr3:uid="{0512DC86-6CE5-CB45-B301-2161DBBC1236}" name="Insights for Thesis" dataDxfId="40"/>
+    <tableColumn id="12" xr3:uid="{B6492819-882E-6E43-A300-8E723AE7BF33}" name="Outcomes" dataDxfId="39"/>
+    <tableColumn id="13" xr3:uid="{FAC6D398-1FDC-6944-9A7E-34C28ECDAA8B}" name="Relevance" dataDxfId="38"/>
+    <tableColumn id="14" xr3:uid="{F7655086-4881-9D4F-BDBF-0FB8DE110B27}" name="Link" dataDxfId="37" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{3A688F49-F3F4-B549-83D0-B0942C7EE14B}" name="Reviewed?" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium17" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6B0EF1A4-B632-064C-B047-AFD93614047D}" name="Ecosystem" displayName="Ecosystem" ref="A1:K22" totalsRowShown="0" dataDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6B0EF1A4-B632-064C-B047-AFD93614047D}" name="Ecosystem" displayName="Ecosystem" ref="A1:K22" totalsRowShown="0" dataDxfId="35">
   <autoFilter ref="A1:K22" xr:uid="{6B0EF1A4-B632-064C-B047-AFD93614047D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K14">
     <sortCondition descending="1" ref="C1:C14"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{DDA40927-D99D-7944-ABBB-E062EAC00CB0}" name="Paper Title" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{7063D636-C85B-3548-A015-8D7C939D4FA5}" name="Authors" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{0A4B399A-AD2E-3048-B417-A6AB46292C0E}" name="Year" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{3ED340CA-2C59-CE48-BDF0-D7CD1022D6AA}" name="Journal Title" dataDxfId="41"/>
-    <tableColumn id="10" xr3:uid="{6613DB95-863F-B043-ABF2-28DACB82C976}" name="Journal Importance" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{CFA5C437-782F-2146-99F8-88849AC4D708}" name="Abstract" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{3BA165FD-1D1B-A345-AA35-D599109FCC87}" name="Insights for Thesis" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{E3BC98A8-DF66-6B4E-8276-EBF6B58FA40E}" name="Outcomes" dataDxfId="37"/>
-    <tableColumn id="13" xr3:uid="{D0CB5091-71CC-C248-9A19-F90F8F2E8297}" name="Relevance" dataDxfId="36"/>
-    <tableColumn id="14" xr3:uid="{C927F29E-2777-C84F-A9EA-3EA05CD3B954}" name="Link" dataDxfId="35" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{FF6D7400-F425-4C42-9BBF-ADFBE98D0F07}" name="Reviewed?" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{DDA40927-D99D-7944-ABBB-E062EAC00CB0}" name="Paper Title" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{7063D636-C85B-3548-A015-8D7C939D4FA5}" name="Authors" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{0A4B399A-AD2E-3048-B417-A6AB46292C0E}" name="Year" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{3ED340CA-2C59-CE48-BDF0-D7CD1022D6AA}" name="Journal Title" dataDxfId="31"/>
+    <tableColumn id="10" xr3:uid="{6613DB95-863F-B043-ABF2-28DACB82C976}" name="Journal Importance" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{CFA5C437-782F-2146-99F8-88849AC4D708}" name="Abstract" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{3BA165FD-1D1B-A345-AA35-D599109FCC87}" name="Insights for Thesis" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{E3BC98A8-DF66-6B4E-8276-EBF6B58FA40E}" name="Outcomes" dataDxfId="27"/>
+    <tableColumn id="13" xr3:uid="{D0CB5091-71CC-C248-9A19-F90F8F2E8297}" name="Relevance" dataDxfId="26"/>
+    <tableColumn id="14" xr3:uid="{C927F29E-2777-C84F-A9EA-3EA05CD3B954}" name="Link" dataDxfId="25" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{FF6D7400-F425-4C42-9BBF-ADFBE98D0F07}" name="Reviewed?" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BDB057D3-C952-D345-8F2C-B84814345F7C}" name="Network" displayName="Network" ref="A1:L21" totalsRowShown="0" dataDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BDB057D3-C952-D345-8F2C-B84814345F7C}" name="Network" displayName="Network" ref="A1:L21" totalsRowShown="0" dataDxfId="23">
   <autoFilter ref="A1:L21" xr:uid="{BDB057D3-C952-D345-8F2C-B84814345F7C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L21">
     <sortCondition descending="1" ref="C1:C21"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{CF32DED6-F460-BC4E-8425-9A38061898F6}" name="Paper Title" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{CCB95980-EAA8-D249-8BBC-397525A2F450}" name="Authors" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{037E5B70-94CF-D440-816F-4E3CB4C9BD23}" name="Year" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{1E353C60-E639-2940-9E11-2CA96BECA2DB}" name="Journal Title" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{4F321EEF-3C49-F549-99B7-4791D31958FF}" name="Journal Importance" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{C27CEDF0-021E-AD4C-AC46-79A57416DDAD}" name="Abstract" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{5A1165FC-0522-0E42-9695-D8A474BA3183}" name="DOI" dataDxfId="26" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{0BFB5501-86F2-9343-A561-78081AAC3D16}" name="Insights for Thesis" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{46301428-00AB-1B40-B9BD-76F9077E5805}" name="Outcomes" dataDxfId="24"/>
-    <tableColumn id="13" xr3:uid="{405179D8-608B-E04F-9EFF-3BFD48149919}" name="Relevance" dataDxfId="23"/>
-    <tableColumn id="14" xr3:uid="{9C55F2EE-8819-AB4B-BBE8-87A1890AB86E}" name="Link" dataDxfId="22" dataCellStyle="Hyperlink"/>
-    <tableColumn id="9" xr3:uid="{EC72141A-19AA-6848-B1E6-106BFB0309A1}" name="Reviewed?" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{CF32DED6-F460-BC4E-8425-9A38061898F6}" name="Paper Title" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{CCB95980-EAA8-D249-8BBC-397525A2F450}" name="Authors" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{037E5B70-94CF-D440-816F-4E3CB4C9BD23}" name="Year" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{1E353C60-E639-2940-9E11-2CA96BECA2DB}" name="Journal Title" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{4F321EEF-3C49-F549-99B7-4791D31958FF}" name="Journal Importance" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{C27CEDF0-021E-AD4C-AC46-79A57416DDAD}" name="Abstract" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{5A1165FC-0522-0E42-9695-D8A474BA3183}" name="DOI" dataDxfId="16" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{0BFB5501-86F2-9343-A561-78081AAC3D16}" name="Insights for Thesis" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{46301428-00AB-1B40-B9BD-76F9077E5805}" name="Outcomes" dataDxfId="14"/>
+    <tableColumn id="13" xr3:uid="{405179D8-608B-E04F-9EFF-3BFD48149919}" name="Relevance" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{9C55F2EE-8819-AB4B-BBE8-87A1890AB86E}" name="Link" dataDxfId="12" dataCellStyle="Hyperlink"/>
+    <tableColumn id="9" xr3:uid="{EC72141A-19AA-6848-B1E6-106BFB0309A1}" name="Reviewed?" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{86F5C17F-65E7-A747-A730-2845D6297FFF}" name="Table9" displayName="Table9" ref="A1:J7" totalsRowShown="0" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{86F5C17F-65E7-A747-A730-2845D6297FFF}" name="Table9" displayName="Table9" ref="A1:J7" totalsRowShown="0" dataDxfId="10">
   <autoFilter ref="A1:J7" xr:uid="{86F5C17F-65E7-A747-A730-2845D6297FFF}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A9C5428B-4718-FF44-9FCD-0C711AC5D2EB}" name="Paper Title" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{4F22ED0F-90ED-084C-875B-D2ACFA43F0C3}" name="Authors" dataDxfId="19"/>
-    <tableColumn id="13" xr3:uid="{448BD838-743C-174E-8313-8B23A5A82284}" name="Topic" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{85D89CB4-8644-2B4C-AAB0-593299A9A7C6}" name="Year" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{25ECED98-A760-E94C-A8F8-8AC0125F71D1}" name="Journal Title" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{4281CF60-E364-5443-9F66-E8CC243CAFA8}" name="Journal Importance" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{7B7FE905-1B9C-5C41-84E4-BF149FCE16FA}" name="Abstract" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{0689C985-F189-B648-8024-CDA0BFD5E584}" name="Relevance" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{953D64E1-58A3-7F44-A196-F2DE65180622}" name="Link" dataDxfId="13" dataCellStyle="Hyperlink"/>
-    <tableColumn id="12" xr3:uid="{D7A66561-7B50-6B46-90CA-B3315F9B5D59}" name="Reviewed?" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{A9C5428B-4718-FF44-9FCD-0C711AC5D2EB}" name="Paper Title" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{4F22ED0F-90ED-084C-875B-D2ACFA43F0C3}" name="Authors" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{448BD838-743C-174E-8313-8B23A5A82284}" name="Topic" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{85D89CB4-8644-2B4C-AAB0-593299A9A7C6}" name="Year" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{25ECED98-A760-E94C-A8F8-8AC0125F71D1}" name="Journal Title" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{4281CF60-E364-5443-9F66-E8CC243CAFA8}" name="Journal Importance" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{7B7FE905-1B9C-5C41-84E4-BF149FCE16FA}" name="Abstract" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{0689C985-F189-B648-8024-CDA0BFD5E584}" name="Relevance" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{953D64E1-58A3-7F44-A196-F2DE65180622}" name="Link" dataDxfId="1" dataCellStyle="Hyperlink"/>
+    <tableColumn id="12" xr3:uid="{D7A66561-7B50-6B46-90CA-B3315F9B5D59}" name="Reviewed?" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5393,7 +5373,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="1" customFormat="1" ht="306" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" s="1" customFormat="1" ht="170" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>24</v>
       </c>
@@ -5431,7 +5411,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="221" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>98</v>
       </c>
@@ -5469,7 +5449,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="340" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="255" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>90</v>
       </c>
@@ -5505,7 +5485,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="306" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
@@ -5543,7 +5523,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="356" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="187" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>39</v>
       </c>
@@ -5615,7 +5595,7 @@
       </c>
       <c r="P7" s="5"/>
     </row>
-    <row r="8" spans="1:16" ht="340" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" ht="187" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>82</v>
       </c>
@@ -5685,7 +5665,7 @@
       </c>
       <c r="P9" s="5"/>
     </row>
-    <row r="10" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="289" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>103</v>
       </c>
@@ -5757,7 +5737,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="289" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" ht="153" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>140</v>
       </c>
@@ -5825,7 +5805,7 @@
       </c>
       <c r="P13" s="5"/>
     </row>
-    <row r="14" spans="1:16" ht="306" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" ht="153" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>108</v>
       </c>
@@ -5863,7 +5843,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="221" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>30</v>
       </c>
@@ -5965,7 +5945,7 @@
       </c>
       <c r="P17" s="5"/>
     </row>
-    <row r="18" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" ht="255" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>9</v>
       </c>
@@ -6001,7 +5981,7 @@
       </c>
       <c r="P18" s="5"/>
     </row>
-    <row r="19" spans="1:16" ht="388" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" ht="204" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>559</v>
       </c>
@@ -6109,7 +6089,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="388" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" ht="204" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>67</v>
       </c>
@@ -6187,7 +6167,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="323" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" ht="170" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>539</v>
       </c>
@@ -6259,7 +6239,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="289" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" ht="170" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>588</v>
       </c>
@@ -6335,7 +6315,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>549</v>
       </c>
@@ -6409,7 +6389,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" ht="356" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>141</v>
       </c>
@@ -6443,7 +6423,7 @@
       </c>
       <c r="P30" s="5"/>
     </row>
-    <row r="31" spans="1:16" ht="323" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" ht="170" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>499</v>
       </c>
@@ -6479,7 +6459,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="289" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" ht="153" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>552</v>
       </c>
@@ -6509,7 +6489,7 @@
       </c>
       <c r="P32" s="5"/>
     </row>
-    <row r="33" spans="1:16" ht="238" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>601</v>
       </c>
@@ -6577,7 +6557,7 @@
       </c>
       <c r="P34" s="5"/>
     </row>
-    <row r="35" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>609</v>
       </c>
@@ -6611,7 +6591,7 @@
       </c>
       <c r="P35" s="5"/>
     </row>
-    <row r="36" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" ht="272" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>614</v>
       </c>
@@ -6645,7 +6625,7 @@
       </c>
       <c r="P36" s="5"/>
     </row>
-    <row r="37" spans="1:16" ht="388" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" ht="204" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>619</v>
       </c>
@@ -6679,12 +6659,12 @@
       </c>
       <c r="P37" s="5"/>
     </row>
-    <row r="38" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" ht="356" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
+        <v>854</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>855</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>856</v>
       </c>
       <c r="C38" s="5">
         <v>2010</v>
@@ -6696,7 +6676,7 @@
         <v>594</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -6707,16 +6687,16 @@
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
       <c r="O38" s="8" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="P38" s="5"/>
     </row>
     <row r="39" spans="1:16" ht="204" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>859</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>860</v>
       </c>
       <c r="C39" s="5">
         <v>2007</v>
@@ -6728,7 +6708,7 @@
         <v>594</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
@@ -6739,16 +6719,16 @@
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
       <c r="O39" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="P39" s="5"/>
     </row>
     <row r="40" spans="1:16" ht="306" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>863</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>864</v>
       </c>
       <c r="C40" s="5">
         <v>2005</v>
@@ -6760,7 +6740,7 @@
         <v>594</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
@@ -6771,48 +6751,48 @@
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
       <c r="O40" s="8" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="P40" s="5"/>
     </row>
     <row r="41" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B41" s="5" t="s">
+        <v>867</v>
+      </c>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="F41" s="5" t="s">
         <v>868</v>
-      </c>
-      <c r="C41" s="32"/>
-      <c r="D41" s="5" t="s">
-        <v>867</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>594</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>869</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
-      <c r="K41" s="33"/>
+      <c r="K41" s="11"/>
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
       <c r="O41" s="8" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="P41" s="5"/>
     </row>
     <row r="42" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
+        <v>876</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>877</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>878</v>
-      </c>
-      <c r="C42" s="32">
+      <c r="C42" s="5">
         <v>2015</v>
       </c>
       <c r="D42" s="5" t="s">
@@ -6822,25 +6802,25 @@
         <v>594</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
-      <c r="K42" s="33"/>
+      <c r="K42" s="11"/>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
       <c r="O42" s="8" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="P42" s="5"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
-      <c r="C43" s="32"/>
+      <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
@@ -6848,7 +6828,7 @@
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
-      <c r="K43" s="33"/>
+      <c r="K43" s="11"/>
       <c r="L43" s="5"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
@@ -6858,7 +6838,7 @@
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
-      <c r="C44" s="32"/>
+      <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
@@ -6866,7 +6846,7 @@
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
-      <c r="K44" s="33"/>
+      <c r="K44" s="11"/>
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
@@ -6876,7 +6856,7 @@
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
-      <c r="C45" s="32"/>
+      <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
@@ -6884,7 +6864,7 @@
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
-      <c r="K45" s="33"/>
+      <c r="K45" s="11"/>
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
@@ -6894,7 +6874,7 @@
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
-      <c r="C46" s="32"/>
+      <c r="C46" s="5"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
@@ -6902,7 +6882,7 @@
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
-      <c r="K46" s="33"/>
+      <c r="K46" s="11"/>
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
@@ -6912,7 +6892,7 @@
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
-      <c r="C47" s="32"/>
+      <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -6920,7 +6900,7 @@
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
-      <c r="K47" s="33"/>
+      <c r="K47" s="11"/>
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
@@ -7062,19 +7042,19 @@
       <c r="F3" s="13"/>
     </row>
     <row r="4" spans="2:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="28" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="28"/>
-      <c r="E4" s="27" t="s">
+      <c r="C4" s="29"/>
+      <c r="E4" s="28" t="s">
         <v>522</v>
       </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="28"/>
-      <c r="I4" s="27" t="s">
+      <c r="F4" s="30"/>
+      <c r="G4" s="29"/>
+      <c r="I4" s="28" t="s">
         <v>554</v>
       </c>
-      <c r="J4" s="29"/>
+      <c r="J4" s="30"/>
       <c r="K4" s="24"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
@@ -7161,39 +7141,33 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="15" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C8" s="16">
         <f>ROWS(VentureCapital[])</f>
         <v>50</v>
       </c>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="31"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="15" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C9" s="16">
         <f>ROWS(StartupFinancing[])</f>
         <v>5</v>
       </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="31"/>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="15" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C10" s="16">
         <f>ROWS(VCTheory[])</f>
         <v>27</v>
       </c>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="31"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="15" t="s">
@@ -8238,7 +8212,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -8267,7 +8241,7 @@
         <v>626</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C2" s="25" t="s">
         <v>627</v>
@@ -8285,7 +8259,7 @@
         <v>629</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="I2" s="25"/>
     </row>
@@ -8294,7 +8268,7 @@
         <v>630</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C3" s="25" t="s">
         <v>631</v>
@@ -8312,7 +8286,7 @@
         <v>632</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="I3" s="25"/>
     </row>
@@ -8337,16 +8311,16 @@
         <v>635</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="I4" s="25"/>
     </row>
-    <row r="5" spans="1:9" ht="320" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="256" x14ac:dyDescent="0.2">
       <c r="A5" s="25" t="s">
         <v>636</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C5" s="25" t="s">
         <v>637</v>
@@ -8364,7 +8338,7 @@
         <v>638</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="I5" s="25"/>
     </row>
@@ -8389,7 +8363,7 @@
         <v>641</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="I6" s="25"/>
     </row>
@@ -8414,11 +8388,11 @@
         <v>256</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I7" s="25"/>
     </row>
-    <row r="8" spans="1:9" ht="304" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="256" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="s">
         <v>643</v>
       </c>
@@ -8439,7 +8413,7 @@
         <v>645</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I8" s="25"/>
     </row>
@@ -8464,7 +8438,7 @@
         <v>649</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I9" s="25"/>
     </row>
@@ -8489,7 +8463,7 @@
         <v>653</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="I10" s="25"/>
     </row>
@@ -8514,44 +8488,44 @@
         <v>656</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="I11" s="25"/>
     </row>
-    <row r="12" spans="1:9" ht="128" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="112" x14ac:dyDescent="0.2">
       <c r="A12" s="25" t="s">
         <v>657</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>658</v>
+        <v>932</v>
       </c>
       <c r="D12" s="25">
         <v>2000</v>
       </c>
       <c r="E12" s="25" t="s">
+        <v>658</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G12" s="25" t="s">
         <v>659</v>
       </c>
-      <c r="F12" s="25" t="s">
-        <v>594</v>
-      </c>
-      <c r="G12" s="25" t="s">
+      <c r="H12" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="I12" s="25"/>
+    </row>
+    <row r="13" spans="1:9" ht="112" x14ac:dyDescent="0.2">
+      <c r="A13" s="25" t="s">
         <v>660</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>719</v>
-      </c>
-      <c r="I12" s="25"/>
-    </row>
-    <row r="13" spans="1:9" ht="144" x14ac:dyDescent="0.2">
-      <c r="A13" s="25" t="s">
-        <v>661</v>
       </c>
       <c r="B13" s="25"/>
       <c r="C13" s="25" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D13" s="25">
         <v>2008</v>
@@ -8563,20 +8537,20 @@
         <v>594</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9" ht="208" x14ac:dyDescent="0.2">
       <c r="A14" s="25" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B14" s="25"/>
       <c r="C14" s="25" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D14" s="25">
         <v>2010</v>
@@ -8588,20 +8562,20 @@
         <v>594</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9" ht="144" x14ac:dyDescent="0.2">
       <c r="A15" s="25" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B15" s="25"/>
       <c r="C15" s="25" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D15" s="25">
         <v>1995</v>
@@ -8613,20 +8587,20 @@
         <v>594</v>
       </c>
       <c r="G15" s="25" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="I15" s="25"/>
     </row>
     <row r="16" spans="1:9" ht="224" x14ac:dyDescent="0.2">
       <c r="A16" s="25" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B16" s="25"/>
       <c r="C16" s="25" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D16" s="25">
         <v>2012</v>
@@ -8638,20 +8612,20 @@
         <v>594</v>
       </c>
       <c r="G16" s="25" t="s">
+        <v>671</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="I16" s="25"/>
+    </row>
+    <row r="17" spans="1:9" ht="224" x14ac:dyDescent="0.2">
+      <c r="A17" s="25" t="s">
         <v>672</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>723</v>
-      </c>
-      <c r="I16" s="25"/>
-    </row>
-    <row r="17" spans="1:9" ht="272" x14ac:dyDescent="0.2">
-      <c r="A17" s="25" t="s">
-        <v>673</v>
       </c>
       <c r="B17" s="25"/>
       <c r="C17" s="25" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D17" s="25">
         <v>2006</v>
@@ -8663,16 +8637,16 @@
         <v>594</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="I17" s="25"/>
     </row>
     <row r="18" spans="1:9" ht="128" x14ac:dyDescent="0.2">
       <c r="A18" s="25" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B18" s="25"/>
       <c r="C18" s="25" t="s">
@@ -8688,20 +8662,20 @@
         <v>594</v>
       </c>
       <c r="G18" s="25" t="s">
+        <v>676</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="I18" s="25"/>
+    </row>
+    <row r="19" spans="1:9" ht="128" x14ac:dyDescent="0.2">
+      <c r="A19" s="25" t="s">
         <v>677</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>725</v>
-      </c>
-      <c r="I18" s="25"/>
-    </row>
-    <row r="19" spans="1:9" ht="160" x14ac:dyDescent="0.2">
-      <c r="A19" s="25" t="s">
-        <v>678</v>
       </c>
       <c r="B19" s="25"/>
       <c r="C19" s="25" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D19" s="25">
         <v>2002</v>
@@ -8713,20 +8687,20 @@
         <v>594</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9" ht="176" x14ac:dyDescent="0.2">
       <c r="A20" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B20" s="25"/>
       <c r="C20" s="25" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D20" s="25">
         <v>2011</v>
@@ -8736,20 +8710,20 @@
       </c>
       <c r="F20" s="25"/>
       <c r="G20" s="25" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9" ht="240" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B21" s="25"/>
       <c r="C21" s="25" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D21" s="25">
         <v>2005</v>
@@ -8759,45 +8733,45 @@
       </c>
       <c r="F21" s="25"/>
       <c r="G21" s="25" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="I21" s="25"/>
     </row>
     <row r="22" spans="1:9" ht="256" x14ac:dyDescent="0.2">
       <c r="A22" s="25" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B22" s="25"/>
       <c r="C22" s="25" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D22" s="25">
         <v>2017</v>
       </c>
       <c r="E22" s="25" t="s">
+        <v>688</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G22" s="25" t="s">
         <v>689</v>
       </c>
-      <c r="F22" s="25" t="s">
-        <v>594</v>
-      </c>
-      <c r="G22" s="25" t="s">
-        <v>690</v>
-      </c>
       <c r="H22" s="8" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="I22" s="25"/>
     </row>
     <row r="23" spans="1:9" ht="256" x14ac:dyDescent="0.2">
       <c r="A23" s="25" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B23" s="25"/>
       <c r="C23" s="25" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D23" s="25">
         <v>2015</v>
@@ -8809,20 +8783,20 @@
         <v>594</v>
       </c>
       <c r="G23" s="25" t="s">
+        <v>692</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="I23" s="25"/>
+    </row>
+    <row r="24" spans="1:9" ht="160" x14ac:dyDescent="0.2">
+      <c r="A24" s="26" t="s">
         <v>693</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>730</v>
-      </c>
-      <c r="I23" s="25"/>
-    </row>
-    <row r="24" spans="1:9" ht="192" x14ac:dyDescent="0.2">
-      <c r="A24" s="26" t="s">
-        <v>694</v>
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="25" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D24" s="25">
         <v>2018</v>
@@ -8832,14 +8806,14 @@
       </c>
       <c r="F24" s="25"/>
       <c r="G24" s="25" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="I24" s="25"/>
     </row>
-    <row r="25" spans="1:9" ht="256" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="224" x14ac:dyDescent="0.2">
       <c r="A25" s="25" t="s">
         <v>260</v>
       </c>
@@ -8857,43 +8831,43 @@
         <v>594</v>
       </c>
       <c r="G25" s="25" t="s">
+        <v>696</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="I25" s="25"/>
+    </row>
+    <row r="26" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+      <c r="A26" s="25" t="s">
         <v>697</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>730</v>
-      </c>
-      <c r="I25" s="25"/>
-    </row>
-    <row r="26" spans="1:9" ht="102" x14ac:dyDescent="0.2">
-      <c r="A26" s="25" t="s">
-        <v>698</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D26" s="25">
         <v>2001</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F26" s="25" t="s">
         <v>594</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="8" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="I26" s="25"/>
     </row>
-    <row r="27" spans="1:9" ht="256" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="224" x14ac:dyDescent="0.2">
       <c r="A27" s="25" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B27" s="25"/>
       <c r="C27" s="25" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D27" s="25">
         <v>2004</v>
@@ -8905,22 +8879,22 @@
         <v>594</v>
       </c>
       <c r="G27" s="25" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="I27" s="25"/>
     </row>
     <row r="28" spans="1:9" ht="304" x14ac:dyDescent="0.2">
       <c r="A28" s="25" t="s">
+        <v>703</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>707</v>
+      </c>
+      <c r="C28" s="25" t="s">
         <v>704</v>
-      </c>
-      <c r="B28" s="25" t="s">
-        <v>708</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>705</v>
       </c>
       <c r="D28" s="25">
         <v>1998</v>
@@ -8932,10 +8906,10 @@
         <v>594</v>
       </c>
       <c r="G28" s="25" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="I28" s="25"/>
     </row>
@@ -8957,20 +8931,20 @@
         <v>594</v>
       </c>
       <c r="G29" s="25" t="s">
+        <v>794</v>
+      </c>
+      <c r="H29" s="8" t="s">
         <v>795</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>796</v>
       </c>
       <c r="I29" s="25"/>
     </row>
     <row r="30" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A30" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B30" s="25"/>
       <c r="C30" s="25" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D30" s="25">
         <v>2000</v>
@@ -8982,20 +8956,20 @@
         <v>594</v>
       </c>
       <c r="G30" s="25" t="s">
+        <v>798</v>
+      </c>
+      <c r="H30" s="8" t="s">
         <v>799</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>800</v>
       </c>
       <c r="I30" s="25"/>
     </row>
     <row r="31" spans="1:9" ht="380" x14ac:dyDescent="0.2">
       <c r="A31" s="25" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B31" s="25"/>
       <c r="C31" s="25" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D31" s="25">
         <v>1985</v>
@@ -9007,20 +8981,20 @@
         <v>594</v>
       </c>
       <c r="G31" s="25" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="I31" s="25"/>
     </row>
     <row r="32" spans="1:9" ht="192" x14ac:dyDescent="0.2">
       <c r="A32" s="25" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B32" s="25"/>
       <c r="C32" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D32" s="25">
         <v>1999</v>
@@ -9032,20 +9006,20 @@
         <v>594</v>
       </c>
       <c r="G32" s="25" t="s">
+        <v>806</v>
+      </c>
+      <c r="H32" s="8" t="s">
         <v>807</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>808</v>
       </c>
       <c r="I32" s="25"/>
     </row>
     <row r="33" spans="1:9" ht="176" x14ac:dyDescent="0.2">
       <c r="A33" s="25" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B33" s="25"/>
       <c r="C33" s="25" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D33" s="25">
         <v>2011</v>
@@ -9057,20 +9031,20 @@
         <v>594</v>
       </c>
       <c r="G33" s="25" t="s">
+        <v>810</v>
+      </c>
+      <c r="H33" s="8" t="s">
         <v>811</v>
       </c>
-      <c r="H33" s="8" t="s">
+      <c r="I33" s="25"/>
+    </row>
+    <row r="34" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A34" s="25" t="s">
         <v>812</v>
-      </c>
-      <c r="I33" s="25"/>
-    </row>
-    <row r="34" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A34" s="25" t="s">
-        <v>813</v>
       </c>
       <c r="B34" s="25"/>
       <c r="C34" s="25" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D34" s="25">
         <v>1992</v>
@@ -9082,14 +9056,14 @@
         <v>594</v>
       </c>
       <c r="G34" s="25" t="s">
+        <v>814</v>
+      </c>
+      <c r="H34" s="8" t="s">
         <v>815</v>
       </c>
-      <c r="H34" s="8" t="s">
-        <v>816</v>
-      </c>
       <c r="I34" s="25"/>
     </row>
-    <row r="35" spans="1:9" ht="144" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="160" x14ac:dyDescent="0.2">
       <c r="A35" s="25" t="s">
         <v>423</v>
       </c>
@@ -9107,20 +9081,20 @@
         <v>594</v>
       </c>
       <c r="G35" s="25" t="s">
+        <v>816</v>
+      </c>
+      <c r="H35" s="8" t="s">
         <v>817</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>818</v>
       </c>
       <c r="I35" s="25"/>
     </row>
     <row r="36" spans="1:9" ht="128" x14ac:dyDescent="0.2">
       <c r="A36" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B36" s="25"/>
       <c r="C36" s="25" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D36" s="25">
         <v>2010</v>
@@ -9132,20 +9106,20 @@
         <v>594</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="I36" s="25"/>
     </row>
     <row r="37" spans="1:9" ht="176" x14ac:dyDescent="0.2">
       <c r="A37" s="25" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B37" s="25"/>
       <c r="C37" s="25" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D37" s="25">
         <v>2011</v>
@@ -9157,20 +9131,20 @@
         <v>594</v>
       </c>
       <c r="G37" s="25" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="I37" s="25"/>
     </row>
     <row r="38" spans="1:9" ht="112" x14ac:dyDescent="0.2">
       <c r="A38" s="25" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B38" s="25"/>
       <c r="C38" s="25" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D38" s="25">
         <v>2017</v>
@@ -9182,20 +9156,20 @@
         <v>594</v>
       </c>
       <c r="G38" s="25" t="s">
+        <v>830</v>
+      </c>
+      <c r="H38" s="8" t="s">
         <v>831</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>832</v>
       </c>
       <c r="I38" s="25"/>
     </row>
     <row r="39" spans="1:9" ht="128" x14ac:dyDescent="0.2">
       <c r="A39" s="25" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B39" s="25"/>
       <c r="C39" s="25" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D39" s="25">
         <v>1995</v>
@@ -9207,20 +9181,20 @@
         <v>594</v>
       </c>
       <c r="G39" s="25" t="s">
+        <v>835</v>
+      </c>
+      <c r="H39" s="8" t="s">
         <v>836</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>837</v>
       </c>
       <c r="I39" s="25"/>
     </row>
     <row r="40" spans="1:9" ht="144" x14ac:dyDescent="0.2">
       <c r="A40" s="25" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B40" s="25"/>
       <c r="C40" s="25" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="D40" s="25">
         <v>2007</v>
@@ -9232,45 +9206,45 @@
         <v>594</v>
       </c>
       <c r="G40" s="25" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="I40" s="25"/>
     </row>
     <row r="41" spans="1:9" ht="192" x14ac:dyDescent="0.2">
       <c r="A41" s="25" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B41" s="25"/>
       <c r="C41" s="25" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D41" s="25">
         <v>2006</v>
       </c>
       <c r="E41" s="25" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F41" s="25" t="s">
         <v>594</v>
       </c>
       <c r="G41" s="25" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="I41" s="25"/>
     </row>
     <row r="42" spans="1:9" ht="176" x14ac:dyDescent="0.2">
       <c r="A42" s="25" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B42" s="25"/>
       <c r="C42" s="25" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="D42" s="25">
         <v>1989</v>
@@ -9282,20 +9256,20 @@
         <v>594</v>
       </c>
       <c r="G42" s="25" t="s">
+        <v>845</v>
+      </c>
+      <c r="H42" s="8" t="s">
         <v>846</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>847</v>
       </c>
       <c r="I42" s="25"/>
     </row>
     <row r="43" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A43" s="25" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B43" s="25"/>
       <c r="C43" s="25" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D43" s="25">
         <v>1989</v>
@@ -9307,20 +9281,20 @@
         <v>594</v>
       </c>
       <c r="G43" s="25" t="s">
+        <v>849</v>
+      </c>
+      <c r="H43" s="8" t="s">
         <v>850</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>851</v>
       </c>
       <c r="I43" s="25"/>
     </row>
     <row r="44" spans="1:9" ht="128" x14ac:dyDescent="0.2">
       <c r="A44" s="25" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B44" s="25"/>
       <c r="C44" s="25" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D44" s="25">
         <v>2004</v>
@@ -9332,58 +9306,58 @@
         <v>594</v>
       </c>
       <c r="G44" s="25" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="I44" s="25"/>
     </row>
     <row r="45" spans="1:9" ht="208" x14ac:dyDescent="0.2">
       <c r="A45" s="25" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B45" s="25"/>
       <c r="C45" s="25" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D45" s="25">
         <v>2014</v>
       </c>
       <c r="E45" s="25" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="F45" s="25"/>
       <c r="G45" s="25" t="s">
+        <v>883</v>
+      </c>
+      <c r="H45" s="8" t="s">
         <v>884</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>885</v>
       </c>
       <c r="I45" s="25"/>
     </row>
     <row r="46" spans="1:9" ht="224" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B46" s="25"/>
       <c r="C46" s="5" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D46" s="25">
         <v>2020</v>
       </c>
       <c r="E46" s="25" t="s">
+        <v>916</v>
+      </c>
+      <c r="F46" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G46" s="25" t="s">
         <v>917</v>
       </c>
-      <c r="F46" s="25" t="s">
-        <v>594</v>
-      </c>
-      <c r="G46" s="25" t="s">
-        <v>918</v>
-      </c>
       <c r="H46" s="8" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="I46" s="25"/>
     </row>
@@ -9513,70 +9487,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="34" t="s">
-        <v>707</v>
-      </c>
-      <c r="C1" s="35" t="s">
+      <c r="B1" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="H1" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="I1" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A2" s="37" t="s">
+    <row r="2" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>889</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>888</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="D2" s="5">
+        <v>1994</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>890</v>
       </c>
-      <c r="C2" s="37" t="s">
-        <v>889</v>
-      </c>
-      <c r="D2" s="37">
-        <v>1994</v>
-      </c>
-      <c r="E2" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="F2" s="37" t="s">
-        <v>594</v>
-      </c>
-      <c r="G2" s="37" t="s">
-        <v>891</v>
-      </c>
       <c r="H2" s="9" t="s">
-        <v>887</v>
-      </c>
-      <c r="I2" s="37"/>
+        <v>886</v>
+      </c>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" ht="306" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>894</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>892</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>895</v>
-      </c>
-      <c r="C3" s="38" t="s">
-        <v>893</v>
       </c>
       <c r="D3" s="5">
         <v>2019</v>
@@ -9588,47 +9562,47 @@
         <v>594</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9" ht="306" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>897</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>898</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>899</v>
       </c>
       <c r="D4" s="5">
         <v>2014</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" ht="187" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
+        <v>903</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>904</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>898</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>905</v>
       </c>
       <c r="D5" s="5">
         <v>2000</v>
@@ -9640,22 +9614,22 @@
         <v>594</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" ht="187" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
+        <v>903</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>904</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>898</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>905</v>
       </c>
       <c r="D6" s="5">
         <v>2000</v>
@@ -9665,10 +9639,10 @@
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I6" s="5"/>
     </row>
@@ -9706,7 +9680,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -9732,13 +9706,13 @@
     </row>
     <row r="2" spans="1:9" ht="224" x14ac:dyDescent="0.2">
       <c r="A2" s="25" t="s">
+        <v>734</v>
+      </c>
+      <c r="B2" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="C2" s="25" t="s">
         <v>736</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>737</v>
       </c>
       <c r="D2" s="25">
         <v>1990</v>
@@ -9750,22 +9724,22 @@
         <v>594</v>
       </c>
       <c r="G2" s="25" t="s">
+        <v>737</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>738</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>739</v>
       </c>
       <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A3" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>735</v>
+      </c>
+      <c r="C3" s="25" t="s">
         <v>740</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>736</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>741</v>
       </c>
       <c r="D3" s="25"/>
       <c r="E3" s="25"/>
@@ -9773,22 +9747,22 @@
         <v>594</v>
       </c>
       <c r="G3" s="25" t="s">
+        <v>741</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>742</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>743</v>
       </c>
       <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9" ht="288" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="s">
+        <v>743</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>735</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>744</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>736</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>745</v>
       </c>
       <c r="D4" s="25">
         <v>1983</v>
@@ -9800,97 +9774,97 @@
         <v>594</v>
       </c>
       <c r="G4" s="25" t="s">
+        <v>745</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>746</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>747</v>
       </c>
       <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A5" s="25" t="s">
+        <v>747</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>735</v>
+      </c>
+      <c r="C5" s="25" t="s">
         <v>748</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>736</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>749</v>
       </c>
       <c r="D5" s="25">
         <v>1981</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F5" s="25" t="s">
         <v>594</v>
       </c>
       <c r="G5" s="25"/>
       <c r="H5" s="8" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9" ht="119" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="s">
+        <v>750</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>735</v>
+      </c>
+      <c r="C6" s="25" t="s">
         <v>751</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>736</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>752</v>
       </c>
       <c r="D6" s="25">
         <v>1970</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F6" s="25" t="s">
         <v>594</v>
       </c>
       <c r="G6" s="25"/>
       <c r="H6" s="8" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="25" t="s">
+        <v>754</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>735</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>755</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>736</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>756</v>
       </c>
       <c r="D7" s="25">
         <v>1984</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="F7" s="25" t="s">
         <v>594</v>
       </c>
       <c r="G7" s="25"/>
       <c r="H7" s="8" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="I7" s="25"/>
     </row>
     <row r="8" spans="1:9" ht="272" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="s">
+        <v>758</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>735</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>759</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>736</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>760</v>
       </c>
       <c r="D8" s="25">
         <v>1976</v>
@@ -9902,128 +9876,128 @@
         <v>594</v>
       </c>
       <c r="G8" s="25" t="s">
+        <v>760</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>761</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>762</v>
       </c>
       <c r="I8" s="25"/>
     </row>
     <row r="9" spans="1:9" ht="192" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
+        <v>762</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>735</v>
+      </c>
+      <c r="C9" s="25" t="s">
         <v>763</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>736</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>764</v>
       </c>
       <c r="D9" s="25">
         <v>1980</v>
       </c>
       <c r="E9" s="25" t="s">
+        <v>764</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G9" s="25" t="s">
         <v>765</v>
       </c>
-      <c r="F9" s="25" t="s">
-        <v>594</v>
-      </c>
-      <c r="G9" s="25" t="s">
+      <c r="H9" s="8" t="s">
         <v>766</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>767</v>
       </c>
       <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A10" s="25" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D10" s="25">
         <v>1979</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F10" s="25"/>
       <c r="G10" s="25" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="I10" s="25"/>
     </row>
     <row r="11" spans="1:9" ht="192" x14ac:dyDescent="0.2">
       <c r="A11" s="25" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D11" s="25">
         <v>2003</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F11" s="25" t="s">
         <v>594</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="I11" s="25"/>
     </row>
     <row r="12" spans="1:9" ht="176" x14ac:dyDescent="0.2">
       <c r="A12" s="25" t="s">
+        <v>776</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>778</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>777</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>779</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>778</v>
       </c>
       <c r="D12" s="25">
         <v>1991</v>
       </c>
       <c r="E12" s="25" t="s">
+        <v>779</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="G12" s="25" t="s">
         <v>780</v>
       </c>
-      <c r="F12" s="25" t="s">
-        <v>594</v>
-      </c>
-      <c r="G12" s="25" t="s">
+      <c r="H12" s="8" t="s">
         <v>781</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>782</v>
       </c>
       <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:9" ht="119" x14ac:dyDescent="0.2">
       <c r="A13" s="25" t="s">
+        <v>782</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>778</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>783</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>779</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>784</v>
       </c>
       <c r="D13" s="25">
         <v>1984</v>
@@ -10035,22 +10009,22 @@
         <v>594</v>
       </c>
       <c r="G13" s="25" t="s">
+        <v>784</v>
+      </c>
+      <c r="H13" s="8" t="s">
         <v>785</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>786</v>
       </c>
       <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9" ht="128" x14ac:dyDescent="0.2">
       <c r="A14" s="25" t="s">
+        <v>786</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>778</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>787</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>779</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>788</v>
       </c>
       <c r="D14" s="25">
         <v>1993</v>
@@ -10062,42 +10036,42 @@
         <v>594</v>
       </c>
       <c r="G14" s="25" t="s">
+        <v>788</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>789</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>790</v>
       </c>
       <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A15" s="25" t="s">
+        <v>790</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>778</v>
+      </c>
+      <c r="C15" s="25" t="s">
         <v>791</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>779</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>792</v>
       </c>
       <c r="D15" s="25">
         <v>2001</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F15" s="25"/>
       <c r="G15" s="25"/>
       <c r="H15" s="8" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="I15" s="25"/>
     </row>
-    <row r="16" spans="1:9" ht="320" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="304" x14ac:dyDescent="0.2">
       <c r="A16" s="25" t="s">
         <v>636</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C16" s="25" t="s">
         <v>637</v>
@@ -10115,7 +10089,7 @@
         <v>638</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="I16" s="25"/>
     </row>
@@ -10124,7 +10098,7 @@
         <v>646</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C17" s="25" t="s">
         <v>647</v>
@@ -10142,7 +10116,7 @@
         <v>649</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I17" s="25"/>
     </row>
@@ -11487,10 +11461,10 @@
     </row>
     <row r="15" spans="1:11" ht="255" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>919</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>920</v>
       </c>
       <c r="C15" s="5">
         <v>2019</v>
@@ -11502,22 +11476,22 @@
         <v>594</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="8" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="K15" s="5"/>
     </row>
     <row r="16" spans="1:11" ht="153" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
+        <v>924</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>925</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>926</v>
       </c>
       <c r="C16" s="5">
         <v>2021</v>
@@ -11529,40 +11503,40 @@
         <v>594</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="8" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="K16" s="5"/>
     </row>
     <row r="17" spans="1:11" ht="204" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C17" s="5">
         <v>2017</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>594</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="8" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="K17" s="5"/>
     </row>
@@ -11825,7 +11799,7 @@
       </c>
       <c r="L4" s="5"/>
     </row>
-    <row r="5" spans="1:12" ht="372" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>578</v>
       </c>
@@ -11915,7 +11889,7 @@
       </c>
       <c r="L7" s="5"/>
     </row>
-    <row r="8" spans="1:12" ht="272" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>341</v>
       </c>
@@ -12041,7 +12015,7 @@
       </c>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" spans="1:12" ht="323" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>363</v>
       </c>
@@ -12135,7 +12109,7 @@
       </c>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:12" ht="289" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>378</v>
       </c>
@@ -12229,7 +12203,7 @@
       </c>
       <c r="L17" s="5"/>
     </row>
-    <row r="18" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>394</v>
       </c>
@@ -12261,7 +12235,7 @@
       </c>
       <c r="L18" s="5"/>
     </row>
-    <row r="19" spans="1:12" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="356" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>406</v>
       </c>
@@ -12323,7 +12297,7 @@
       </c>
       <c r="L20" s="5"/>
     </row>
-    <row r="21" spans="1:12" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>401</v>
       </c>
@@ -12432,97 +12406,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="35" t="s">
-        <v>707</v>
-      </c>
-      <c r="D1" s="35" t="s">
+      <c r="C1" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="G1" s="35" t="s">
+      <c r="G1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="I1" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="J1" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>874</v>
+      </c>
+      <c r="D2" s="5">
+        <v>2020</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="9" t="s">
         <v>872</v>
       </c>
-      <c r="B2" s="37" t="s">
-        <v>874</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>875</v>
-      </c>
-      <c r="D2" s="37">
-        <v>2020</v>
-      </c>
-      <c r="E2" s="37" t="s">
-        <v>290</v>
-      </c>
-      <c r="F2" s="37" t="s">
-        <v>594</v>
-      </c>
-      <c r="G2" s="37" t="s">
-        <v>876</v>
-      </c>
-      <c r="H2" s="37"/>
-      <c r="I2" s="9" t="s">
-        <v>873</v>
-      </c>
-      <c r="J2" s="37"/>
+      <c r="J2" s="5"/>
     </row>
     <row r="3" spans="1:10" ht="272" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>908</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>909</v>
-      </c>
-      <c r="C3" s="32" t="s">
-        <v>910</v>
       </c>
       <c r="D3" s="5">
         <v>2018</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>597</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="8" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="J3" s="5"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
-      <c r="C4" s="32"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -12534,7 +12508,7 @@
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
-      <c r="C5" s="32"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -12546,7 +12520,7 @@
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
-      <c r="C6" s="32"/>
+      <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -12558,7 +12532,7 @@
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
-      <c r="C7" s="32"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
